--- a/data/ready_stocks/td-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/td-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D353"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -452,7 +452,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -494,7 +494,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -508,7 +508,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v/>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -592,7 +592,7 @@
         <v/>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -620,7 +620,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -662,7 +662,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -676,7 +676,7 @@
         <v/>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -684,13 +684,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B21" t="str">
-        <v>TDPPKKamillaOSN33</v>
+        <v>TDPPKKamillaComp33</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -698,7 +698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B22" t="str">
-        <v>TDPPKLegkoeDihanieComp33</v>
+        <v>TDPPKKamillaOSN33</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -712,13 +712,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B23" t="str">
-        <v>TDPPKMeditaciaComp33</v>
+        <v>TDPPKLegkoeDihanieComp33</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -726,13 +726,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B24" t="str">
-        <v>TDPPKMeditaciaOsn33</v>
+        <v>TDPPKMeditaciaComp33</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -740,13 +740,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B25" t="str">
-        <v>TDPPKMgnoveniyaOsn33</v>
+        <v>TDPPKMeditaciaOsn33</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -754,13 +754,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B26" t="str">
-        <v>TDPPKpremier220PrometOSN</v>
+        <v>TDPPKMgnoveniyaOsn33</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -768,13 +768,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B27" t="str">
-        <v>TDPPKRapsodiaOsn33</v>
+        <v>TDPPKpremier220PrometOSN</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -782,7 +782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B28" t="str">
-        <v>TDPPKRomanComp33</v>
+        <v>TDPPKRapsodiaOsn33</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -796,13 +796,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B29" t="str">
-        <v>TDPPKRomanOsn33</v>
+        <v>TDPPKRomanComp33</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -810,13 +810,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B30" t="str">
-        <v>TDPPKSalomeyaComp33</v>
+        <v>TDPPKRomanOsn33</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -824,13 +824,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B31" t="str">
-        <v>TDPPKSalomeyaOsn33</v>
+        <v>TDPPKSalomeyaComp33</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -838,13 +838,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B32" t="str">
-        <v>TDPPKTanecVetraOsn33</v>
+        <v>TDPPKSalomeyaOsn33</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -852,7 +852,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B33" t="str">
-        <v>TDPPKTobiasOsn33</v>
+        <v>TDPPKTanecVetraOsn33</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -866,13 +866,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B34" t="str">
-        <v>TDPPKVenzelKomp2</v>
+        <v>TDPPKTobiasOsn33</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -880,7 +880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B35" t="str">
-        <v>TDPPKVenzelOSN33</v>
+        <v>TDPPKVenzelKomp2</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -894,7 +894,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B36" t="str">
-        <v>TDPPKVesenKapOSN33</v>
+        <v>TDPPKVenzelOSN33</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -908,13 +908,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B37" t="str">
-        <v>TDPPKVetkiMimozKomp</v>
+        <v>TDPPKVesenKapOSN33</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -922,7 +922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B38" t="str">
-        <v>TDPPKZataivDihanieComp33</v>
+        <v>TDPPKVetkiMimozKomp</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B39" t="str">
-        <v>TDPPKZataivDihanieOSN33</v>
+        <v>TDPPKZataivDihanieComp33</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -950,13 +950,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B40" t="str">
-        <v>TDPPKLegkoeDihanieOsn33</v>
+        <v>TDPPKZataivDihanieOSN33</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -964,13 +964,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B41" t="str">
-        <v>TDPPKGabrielComp334</v>
+        <v>TDPPKAttikaOSN33</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -978,13 +978,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B42" t="str">
-        <v>TDPPKclassic220TanzaniaOsn</v>
+        <v>TDPPKLegkoeDihanieOsn33</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -992,13 +992,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B43" t="str">
-        <v>TDPPKMercLotosOsn</v>
+        <v>TDPPKGabrielComp334</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1006,7 +1006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B44" t="str">
-        <v>TDPPKRapsodiaComp33</v>
+        <v>TDPPKclassic220TanzaniaOsn</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1020,7 +1020,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B45" t="str">
-        <v>TDPPKTanecVetraComp33</v>
+        <v>TDPPKMercLotosOsn</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1034,13 +1034,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B46" t="str">
-        <v>TDPPKGetsbiComp33</v>
+        <v>TDPPKRapsodiaComp33</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1048,13 +1048,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B47" t="str">
-        <v>TDPPKNovolunieComp33</v>
+        <v>TDPPKTanecVetraComp33</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1062,13 +1062,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B48" t="str">
-        <v>TDPPKVesenKapComp33</v>
+        <v>TDPPKGetsbiComp33</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1076,13 +1076,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B49" t="str">
-        <v>TDPPKNovolunieOsn33</v>
+        <v>TDPPKNovolunieComp33</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1090,7 +1090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B50" t="str">
-        <v>TDPPKAdrianOSN33</v>
+        <v>TDPPKVesenKapComp33</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1104,7 +1104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B51" t="str">
-        <v>TDPPKKotofeiComp33</v>
+        <v>TDPPKNovolunieOsn33</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1118,13 +1118,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B52" t="str">
-        <v>TDPPKMagnoliyaOsn33</v>
+        <v>TDPPKAdrianOSN33</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1132,7 +1132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B53" t="str">
-        <v>TDPPKpremier220lidiaKomp</v>
+        <v>TDPPKKotofeiComp33</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1146,7 +1146,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B54" t="str">
-        <v>TDblack</v>
+        <v>TDPPKMagnoliyaOsn33</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1160,13 +1160,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B55" t="str">
-        <v>TDdarkGrafit</v>
+        <v>TDPPKpremier220lidiaKomp</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1174,13 +1174,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B56" t="str">
-        <v>TDgrey</v>
+        <v>TDblack</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1188,13 +1188,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B57" t="str">
-        <v>TDindigo</v>
+        <v>TDdarkGrafit</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1202,13 +1202,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B58" t="str">
-        <v>TDlightLiliac</v>
+        <v>TDgrey</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1216,13 +1216,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B59" t="str">
-        <v>TDlilov</v>
+        <v>TDindigo</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1230,7 +1230,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B60" t="str">
-        <v>TDmolochn</v>
+        <v>TDlightLiliac</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1244,13 +1244,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B61" t="str">
-        <v>TDmorskaya</v>
+        <v>TDlilov</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1258,13 +1258,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B62" t="str">
-        <v>TDotbel110</v>
+        <v>TDmolochn</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1272,13 +1272,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B63" t="str">
-        <v>TDplatina</v>
+        <v>TDmorskaya</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1286,13 +1286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B64" t="str">
-        <v>TDterrakot</v>
+        <v>TDotbel110</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1300,7 +1300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B65" t="str">
-        <v>TDPPKAttikaComp33</v>
+        <v>TDplatina</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1314,13 +1314,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B66" t="str">
-        <v>TDPPKBelStihOSN33</v>
+        <v>TDterrakot</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1328,13 +1328,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>TDPPKGetsbiOsn33</v>
+        <v>TDPPKAttikaComp33</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1342,13 +1342,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>TDPPKKotofeiOsn33</v>
+        <v>TDPPKBelStihOSN33</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1356,7 +1356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>TDPPKabstraciaCOMP33</v>
+        <v>TDPPKGetsbiOsn33</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1370,13 +1370,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>TDPPKEOS220Otbel</v>
+        <v>TDPPKKotofeiOsn33</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1384,13 +1384,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>TDPPKMagnoliyaComp33</v>
+        <v>TDPPKabstraciaCOMP33</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1398,13 +1398,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>TDPPKBelBuketKomp</v>
+        <v>TDPPKEOS220Otbel</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1412,13 +1412,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>TDPPKBelBuketOsn</v>
+        <v>TDPPKMagnoliyaComp33</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1426,7 +1426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>TDSPK220KamillaKOMP5</v>
+        <v>TDPPKBelBuketKomp</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1440,13 +1440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>TDSPK220SovershenstvoKOMP1</v>
+        <v>TDPPKBelBuketOsn</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -1454,7 +1454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>TDSPK220EdemOSN</v>
+        <v>TDSPK220KamillaKOMP5</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -1468,13 +1468,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>TDSPK220ZolotayaOSN</v>
+        <v>TDSPK220SovershenstvoKOMP1</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1482,13 +1482,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>TDSPK220AristokrOSN8</v>
+        <v>TDSPK220EdemOSN</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1496,13 +1496,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>TDSPK220SolnPticOSN</v>
+        <v>TDSPK220ZolotayaOSN</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1510,13 +1510,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>TDSPK220MusikVremOSN</v>
+        <v>TDSPK220AristokrOSN8</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -1524,13 +1524,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>TDSPK220ZolotayaKOMP</v>
+        <v>TDSPK220SolnPticOSN</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1538,13 +1538,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>TDSPK220AdagioOSN4</v>
+        <v>TDSPK220MusikVremOSN</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1552,13 +1552,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>TDSPK220AdamOSN2</v>
+        <v>TDSPK220ZolotayaKOMP</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1566,13 +1566,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>TDSPK220AilaKOMP3</v>
+        <v>TDSPK220AdagioOSN4</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1580,7 +1580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>TDSPK220AilaOSN3</v>
+        <v>TDSPK220AdamOSN2</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1594,7 +1594,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>TDSPK220AristokrKOMP4</v>
+        <v>TDSPK220AilaKOMP3</v>
       </c>
       <c r="C86" t="str">
         <v/>
@@ -1608,13 +1608,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>TDSPK220AristokrKOMP8</v>
+        <v>TDSPK220AilaOSN3</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1622,13 +1622,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>TDSPK220AristokrOSN4</v>
+        <v>TDSPK220AristokrKOMP4</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1636,7 +1636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>TDSPK220AsteriaOSN4</v>
+        <v>TDSPK220AristokrKOMP8</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1650,13 +1650,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>TDSPK220BalFlowersKOMP1</v>
+        <v>TDSPK220AristokrOSN4</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -1664,13 +1664,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>TDSPK220BalFlowersOSN1</v>
+        <v>TDSPK220AsteriaOSN4</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1678,7 +1678,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>TDSPK220BuketChuvstvKOMP2</v>
+        <v>TDSPK220BalFlowersKOMP1</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -1692,13 +1692,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>TDSPK220BuketChuvstvOSN2</v>
+        <v>TDSPK220BalFlowersOSN1</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1706,13 +1706,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>TDSPK220VitragiKOMP3</v>
+        <v>TDSPK220BuketChuvstvKOMP2</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1720,7 +1720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>TDSPK220VitragiOSN3</v>
+        <v>TDSPK220BuketChuvstvOSN2</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1734,13 +1734,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>TDSPK220VozdSharOSN2</v>
+        <v>TDSPK220VitragiKOMP3</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1748,13 +1748,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>TDSPK220MetamorphosaOSN2</v>
+        <v>TDSPK220VitragiOSN3</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1762,7 +1762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>TDSPK220PachuliKOMP1</v>
+        <v>TDSPK220VozdSharOSN2</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>TDSPK220HugOSN2</v>
+        <v>TDSPK220MetamorphosaOSN2</v>
       </c>
       <c r="C99" t="str">
         <v/>
@@ -1790,7 +1790,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>TDSPK220GabrielKOMP3</v>
+        <v>TDSPK220PachuliKOMP1</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -1804,7 +1804,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>TDSPK220GabrielOSN3</v>
+        <v>TDSPK220HugOSN2</v>
       </c>
       <c r="C101" t="str">
         <v/>
@@ -1818,13 +1818,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>TDSPK220DavidOSN4</v>
+        <v>TDSPK220GabrielKOMP3</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1832,7 +1832,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>TDSPK220ZataivDihanieKOMP6</v>
+        <v>TDSPK220GabrielOSN3</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -1846,13 +1846,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>TDSPK220ZataivDihanieOSN6</v>
+        <v>TDSPK220DavidOSN4</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1860,7 +1860,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>TDSPK220KamillaOSN5</v>
+        <v>TDSPK220ZataivDihanieKOMP6</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>TDSPK220CaribbeanOSN2</v>
+        <v>TDSPK220ZataivDihanieOSN6</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>TDSPK220KarolinaOSN3</v>
+        <v>TDSPK220KamillaOSN5</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1902,13 +1902,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>TDSPK220Kashmir1</v>
+        <v>TDSPK220CaribbeanOSN2</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -1916,7 +1916,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>TDSPK220LegkoeDihanieOSN5</v>
+        <v>TDSPK220KarolinaOSN3</v>
       </c>
       <c r="C109" t="str">
         <v/>
@@ -1930,13 +1930,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B110" t="str">
-        <v>TDSPK220LetniyZnoiOSN2</v>
+        <v>TDSPK220Kashmir1</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1944,13 +1944,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B111" t="str">
-        <v>TDSPK220Monochrome1</v>
+        <v>TDSPK220LegkoeDihanieOSN5</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1958,7 +1958,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B112" t="str">
-        <v>TDSPK220Monochrome7</v>
+        <v>TDSPK220LetniyZnoiOSN2</v>
       </c>
       <c r="C112" t="str">
         <v/>
@@ -1972,13 +1972,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B113" t="str">
-        <v>TDSPK220Monochrome8</v>
+        <v>TDSPK220Monochrome1</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1986,7 +1986,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B114" t="str">
-        <v>TDSPK220Monochrome12</v>
+        <v>TDSPK220Monochrome7</v>
       </c>
       <c r="C114" t="str">
         <v/>
@@ -2000,7 +2000,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B115" t="str">
-        <v>TDSPK220NostalgiKOMP4</v>
+        <v>TDSPK220Monochrome8</v>
       </c>
       <c r="C115" t="str">
         <v/>
@@ -2014,13 +2014,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B116" t="str">
-        <v>TDSPK220ObitelLoveOSN2</v>
+        <v>TDSPK220Monochrome12</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2028,13 +2028,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B117" t="str">
-        <v>TDSPK220OdaNejnostiKOMP2</v>
+        <v>TDSPK220NostalgiKOMP4</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2042,7 +2042,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B118" t="str">
-        <v>TDSPK220OdaNejnostiOSN2</v>
+        <v>TDSPK220ObitelLoveOSN2</v>
       </c>
       <c r="C118" t="str">
         <v/>
@@ -2056,13 +2056,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B119" t="str">
-        <v>TDSPK220Otbel120</v>
+        <v>TDSPK220OdaNejnostiKOMP2</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2070,7 +2070,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B120" t="str">
-        <v>TDSPK220OtbleskKOMP3</v>
+        <v>TDSPK220OdaNejnostiOSN2</v>
       </c>
       <c r="C120" t="str">
         <v/>
@@ -2084,7 +2084,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B121" t="str">
-        <v>TDSPK220HappyDaysOSN2</v>
+        <v>TDSPK220Otbel120</v>
       </c>
       <c r="C121" t="str">
         <v/>
@@ -2098,13 +2098,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B122" t="str">
-        <v>TDSPK220PachuliOSN1</v>
+        <v>TDSPK220OtbleskKOMP3</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2112,7 +2112,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B123" t="str">
-        <v>TDSPK220PotokKOMP3</v>
+        <v>TDSPK220HappyDaysOSN2</v>
       </c>
       <c r="C123" t="str">
         <v/>
@@ -2126,7 +2126,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B124" t="str">
-        <v>TDSPK220HappyDaysKOMP2</v>
+        <v>TDSPK220PachuliOSN1</v>
       </c>
       <c r="C124" t="str">
         <v/>
@@ -2140,13 +2140,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B125" t="str">
-        <v>TDSPK220PotokOSN3</v>
+        <v>TDSPK220PotokKOMP3</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2154,7 +2154,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B126" t="str">
-        <v>TDSPK220StepKOMP</v>
+        <v>TDSPK220HappyDaysKOMP2</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -2168,13 +2168,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B127" t="str">
-        <v>TDSPK220LegkoeDihanieKOMP5</v>
+        <v>TDSPK220PotokOSN3</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -2182,13 +2182,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B128" t="str">
-        <v>TDSPK220OtbleskOSN3</v>
+        <v>TDSPK220StepKOMP</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2196,7 +2196,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B129" t="str">
-        <v>TDSPK220StoneOSN2</v>
+        <v>TDSPK220LegkoeDihanieKOMP5</v>
       </c>
       <c r="C129" t="str">
         <v/>
@@ -2210,7 +2210,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B130" t="str">
-        <v>TDSPK220StoneKOMP2</v>
+        <v>TDSPK220OtbleskOSN3</v>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -2224,7 +2224,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B131" t="str">
-        <v>TDSPK220SoloKOMP1</v>
+        <v>TDSPK220StoneOSN2</v>
       </c>
       <c r="C131" t="str">
         <v/>
@@ -2238,7 +2238,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B132" t="str">
-        <v>TDSPK220EtudOSN5</v>
+        <v>TDSPK220StoneKOMP2</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -2252,7 +2252,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B133" t="str">
-        <v>TDSPK220BlossomDreamsOSN2</v>
+        <v>TDSPK220SoloKOMP1</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -2266,7 +2266,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B134" t="str">
-        <v>TDSPK220TanecVetraOSN1</v>
+        <v>TDSPK220EtudOSN5</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -2280,18 +2280,3070 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B135" t="str">
+        <v>TDSPK220BlossomDreamsOSN2</v>
+      </c>
+      <c r="C135" t="str">
+        <v/>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B136" t="str">
+        <v>TDSPK220TanecVetraOSN1</v>
+      </c>
+      <c r="C136" t="str">
+        <v/>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B137" t="str">
         <v>TDSPK220DavidKOMP3</v>
       </c>
-      <c r="C135" t="str">
-        <v/>
-      </c>
-      <c r="D135">
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B138" t="str">
+        <v>SSPK250-8-Gorchich</v>
+      </c>
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B139" t="str">
+        <v>SSPK250-8-Otbel</v>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B140" t="str">
+        <v>SSPK250-8-Ultramarine</v>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>SSPK250-8-RoseCream</v>
+      </c>
+      <c r="C141" t="str">
+        <v/>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B142" t="str">
+        <v>SSPK250-8-BrightBlue</v>
+      </c>
+      <c r="C142" t="str">
+        <v/>
+      </c>
+      <c r="D142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B143" t="str">
+        <v>SSPK250-8-DustyRose</v>
+      </c>
+      <c r="C143" t="str">
+        <v/>
+      </c>
+      <c r="D143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B144" t="str">
+        <v>SSPK250-8-Lavanda</v>
+      </c>
+      <c r="C144" t="str">
+        <v/>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B145" t="str">
+        <v>SSPK250-8-Terrakota</v>
+      </c>
+      <c r="C145" t="str">
+        <v/>
+      </c>
+      <c r="D145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>SSPK250-8-LightBlue</v>
+      </c>
+      <c r="C146" t="str">
+        <v/>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B147" t="str">
+        <v>SSPK250-8-KaruzoGreen</v>
+      </c>
+      <c r="C147" t="str">
+        <v/>
+      </c>
+      <c r="D147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B148" t="str">
+        <v>SSPK250-8-Lazurn</v>
+      </c>
+      <c r="C148" t="str">
+        <v/>
+      </c>
+      <c r="D148">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>SSPK250-8-KaruzoViolet</v>
+      </c>
+      <c r="C149" t="str">
+        <v/>
+      </c>
+      <c r="D149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B150" t="str">
+        <v>SSPK250-8-Coffee</v>
+      </c>
+      <c r="C150" t="str">
+        <v/>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B151" t="str">
+        <v>SSPK250-8-Verde</v>
+      </c>
+      <c r="C151" t="str">
+        <v/>
+      </c>
+      <c r="D151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B152" t="str">
+        <v>SSPK250-8-Persik</v>
+      </c>
+      <c r="C152" t="str">
+        <v/>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B153" t="str">
+        <v>SSPK250-8-Pink</v>
+      </c>
+      <c r="C153" t="str">
+        <v/>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B154" t="str">
+        <v>SSPK250-8-Jemjug</v>
+      </c>
+      <c r="C154" t="str">
+        <v/>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B155" t="str">
+        <v>SSPK250-8-Nebesn</v>
+      </c>
+      <c r="C155" t="str">
+        <v/>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B156" t="str">
+        <v>SSPK250-8-Grafit</v>
+      </c>
+      <c r="C156" t="str">
+        <v/>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B157" t="str">
+        <v>SSPK250-8-Blue</v>
+      </c>
+      <c r="C157" t="str">
+        <v/>
+      </c>
+      <c r="D157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B158" t="str">
+        <v>SSPK250-8-Grey</v>
+      </c>
+      <c r="C158" t="str">
+        <v/>
+      </c>
+      <c r="D158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B159" t="str">
+        <v>SSPK250-8-Chocolate</v>
+      </c>
+      <c r="C159" t="str">
+        <v/>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B160" t="str">
+        <v>SSPK250-8-Green</v>
+      </c>
+      <c r="C160" t="str">
+        <v/>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B161" t="str">
+        <v>SSPK250-8-Wine</v>
+      </c>
+      <c r="C161" t="str">
+        <v/>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B162" t="str">
+        <v>SSPK250-8-Black</v>
+      </c>
+      <c r="C162" t="str">
+        <v/>
+      </c>
+      <c r="D162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B163" t="str">
+        <v>SSPK250-8-Bejeviy</v>
+      </c>
+      <c r="C163" t="str">
+        <v/>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B164" t="str">
+        <v>SSPK250-8-Korall</v>
+      </c>
+      <c r="C164" t="str">
+        <v/>
+      </c>
+      <c r="D164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B165" t="str">
+        <v>TDSPK250DarkViolet</v>
+      </c>
+      <c r="C165" t="str">
+        <v/>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B166" t="str">
+        <v>TDSPK250Green</v>
+      </c>
+      <c r="C166" t="str">
+        <v/>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B167" t="str">
+        <v>TDSPK250Persikoviy</v>
+      </c>
+      <c r="C167" t="str">
+        <v/>
+      </c>
+      <c r="D167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B168" t="str">
+        <v>TDSPK250Lavanda</v>
+      </c>
+      <c r="C168" t="str">
+        <v/>
+      </c>
+      <c r="D168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B169" t="str">
+        <v>TDSPK250Coffee</v>
+      </c>
+      <c r="C169" t="str">
+        <v/>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B170" t="str">
+        <v>TDSPK250Bordo</v>
+      </c>
+      <c r="C170" t="str">
+        <v/>
+      </c>
+      <c r="D170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B171" t="str">
+        <v>TDSPK250LightLiliac</v>
+      </c>
+      <c r="C171" t="str">
+        <v/>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B172" t="str">
+        <v>TDSPK250Liliac</v>
+      </c>
+      <c r="C172" t="str">
+        <v/>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B173" t="str">
+        <v>TDSPK250Blue</v>
+      </c>
+      <c r="C173" t="str">
+        <v/>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B174" t="str">
+        <v>TDSPK250Choco</v>
+      </c>
+      <c r="C174" t="str">
+        <v/>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B175" t="str">
+        <v>TDSPK250Menthol</v>
+      </c>
+      <c r="C175" t="str">
+        <v/>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B176" t="str">
+        <v>TDSPK250Taup</v>
+      </c>
+      <c r="C176" t="str">
+        <v/>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B177" t="str">
+        <v>TDSPK250Platina</v>
+      </c>
+      <c r="C177" t="str">
+        <v/>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B178" t="str">
+        <v>TDSPK250White</v>
+      </c>
+      <c r="C178" t="str">
+        <v/>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B179" t="str">
+        <v>TDSPK250LightBlue</v>
+      </c>
+      <c r="C179" t="str">
+        <v/>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B180" t="str">
+        <v>TDSPK250PepelRose</v>
+      </c>
+      <c r="C180" t="str">
+        <v/>
+      </c>
+      <c r="D180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B181" t="str">
+        <v>TDSPK250Bejeviy</v>
+      </c>
+      <c r="C181" t="str">
+        <v/>
+      </c>
+      <c r="D181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B182" t="str">
+        <v>TDSPK250Jemjug</v>
+      </c>
+      <c r="C182" t="str">
+        <v/>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B183" t="str">
+        <v>TDSPK250LightGreen</v>
+      </c>
+      <c r="C183" t="str">
+        <v/>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B184" t="str">
+        <v>TDSPK250Gold</v>
+      </c>
+      <c r="C184" t="str">
+        <v/>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B185" t="str">
+        <v>TDSPK250Pink</v>
+      </c>
+      <c r="C185" t="str">
+        <v/>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B186" t="str">
+        <v>TDSPK250Kvarc</v>
+      </c>
+      <c r="C186" t="str">
+        <v/>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B187" t="str">
+        <v>TDSPK250ToplMilk</v>
+      </c>
+      <c r="C187" t="str">
+        <v/>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B188" t="str">
+        <v>TDSPK250GrafitGreen</v>
+      </c>
+      <c r="C188" t="str">
+        <v/>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B189" t="str">
+        <v>TDSPK250Sliva</v>
+      </c>
+      <c r="C189" t="str">
+        <v/>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B190" t="str">
+        <v>TDSPK220BuketChuvstvOSN2-8</v>
+      </c>
+      <c r="C190" t="str">
+        <v/>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B191" t="str">
+        <v>TDSPK220Monochrome8-8</v>
+      </c>
+      <c r="C191" t="str">
+        <v/>
+      </c>
+      <c r="D191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B192" t="str">
+        <v>TDSPK220Monochrome1-8</v>
+      </c>
+      <c r="C192" t="str">
+        <v/>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B193" t="str">
+        <v>TDSPK220AristokrOSN8-8</v>
+      </c>
+      <c r="C193" t="str">
+        <v/>
+      </c>
+      <c r="D193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B194" t="str">
+        <v>TDSPK220HappyDaysOSN2-8</v>
+      </c>
+      <c r="C194" t="str">
+        <v/>
+      </c>
+      <c r="D194">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B195" t="str">
+        <v>TDSPK220AilaKOMP3-8</v>
+      </c>
+      <c r="C195" t="str">
+        <v/>
+      </c>
+      <c r="D195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>TDSPK220Monochrome7-8</v>
+      </c>
+      <c r="C196" t="str">
+        <v/>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B197" t="str">
+        <v>TDSPK220PotokOSN3-8</v>
+      </c>
+      <c r="C197" t="str">
+        <v/>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B198" t="str">
+        <v>TDSPK220EdemKomp-8</v>
+      </c>
+      <c r="C198" t="str">
+        <v/>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B199" t="str">
+        <v>TDSPK220Monochrome12-8</v>
+      </c>
+      <c r="C199" t="str">
+        <v/>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B200" t="str">
+        <v>TDSPK220AsteriaOSN4-8</v>
+      </c>
+      <c r="C200" t="str">
+        <v/>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B201" t="str">
+        <v>TDSPK220HugOSN2-8</v>
+      </c>
+      <c r="C201" t="str">
+        <v/>
+      </c>
+      <c r="D201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B202" t="str">
+        <v>TDSPK220KamillaKOMP5-8</v>
+      </c>
+      <c r="C202" t="str">
+        <v/>
+      </c>
+      <c r="D202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B203" t="str">
+        <v>TDSPK220OttepelOSN-8</v>
+      </c>
+      <c r="C203" t="str">
+        <v/>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>TDSPK220ObitelLoveOSN2-8</v>
+      </c>
+      <c r="C204" t="str">
+        <v/>
+      </c>
+      <c r="D204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B205" t="str">
+        <v>TDSPK220OdaNejnostiOSN2-8</v>
+      </c>
+      <c r="C205" t="str">
+        <v/>
+      </c>
+      <c r="D205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B206" t="str">
+        <v>TDSPK220CaribbeanOSN2-8</v>
+      </c>
+      <c r="C206" t="str">
+        <v/>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B207" t="str">
+        <v>TDSPK220NaomiOSN-8</v>
+      </c>
+      <c r="C207" t="str">
+        <v/>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B208" t="str">
+        <v>TDSPK220LegkoeDihanieOSN5-8</v>
+      </c>
+      <c r="C208" t="str">
+        <v/>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B209" t="str">
+        <v>TDSPK220OdaNejnostiKOMP2-8</v>
+      </c>
+      <c r="C209" t="str">
+        <v/>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B210" t="str">
+        <v>TDSPK220AdonisOSN2-8</v>
+      </c>
+      <c r="C210" t="str">
+        <v/>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B211" t="str">
+        <v>TDSPK220StoneKOMP2-8</v>
+      </c>
+      <c r="C211" t="str">
+        <v/>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B212" t="str">
+        <v>TDSPK220NostalgiKOMP4-8</v>
+      </c>
+      <c r="C212" t="str">
+        <v/>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B213" t="str">
+        <v>TDSPK220PachuliKOMP1-8</v>
+      </c>
+      <c r="C213" t="str">
+        <v/>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>TDSPK220PachuliOSN1-8</v>
+      </c>
+      <c r="C214" t="str">
+        <v/>
+      </c>
+      <c r="D214">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>TDSPK220GabrielOSN3-8</v>
+      </c>
+      <c r="C215" t="str">
+        <v/>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>TDSPK220VitragiOSN3-8</v>
+      </c>
+      <c r="C216" t="str">
+        <v/>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B217" t="str">
+        <v>TDSPK220KarolinaOSN3-8</v>
+      </c>
+      <c r="C217" t="str">
+        <v/>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B218" t="str">
+        <v>TDSPK220DavidKOMP3-8</v>
+      </c>
+      <c r="C218" t="str">
+        <v/>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B219" t="str">
+        <v>TDSPK220StepKOMP-8</v>
+      </c>
+      <c r="C219" t="str">
+        <v/>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B220" t="str">
+        <v>TDSPK220Kashmir1-8</v>
+      </c>
+      <c r="C220" t="str">
+        <v/>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B221" t="str">
+        <v>TDSPK220SolnPticOSN-8</v>
+      </c>
+      <c r="C221" t="str">
+        <v/>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B222" t="str">
+        <v>TDSPK220LetniyZnoiOSN2-8</v>
+      </c>
+      <c r="C222" t="str">
+        <v/>
+      </c>
+      <c r="D222">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B223" t="str">
+        <v>TDSPK220BalFlowersKOMP1-8</v>
+      </c>
+      <c r="C223" t="str">
+        <v/>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B224" t="str">
+        <v>TDSPK220EtudKOMP7-8</v>
+      </c>
+      <c r="C224" t="str">
+        <v/>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B225" t="str">
+        <v>TDSPK220AristokrOSN4-8</v>
+      </c>
+      <c r="C225" t="str">
+        <v/>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B226" t="str">
+        <v>TDSPK220ZataivDihanieOSN6-8</v>
+      </c>
+      <c r="C226" t="str">
+        <v/>
+      </c>
+      <c r="D226">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B227" t="str">
+        <v>TDSPK220SoloKOMP1-8</v>
+      </c>
+      <c r="C227" t="str">
+        <v/>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B228" t="str">
+        <v>TDSPK220OtbleskKOMP3-8</v>
+      </c>
+      <c r="C228" t="str">
+        <v/>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B229" t="str">
+        <v>TDSPK220ZataivDihanieKOMP6-8</v>
+      </c>
+      <c r="C229" t="str">
+        <v/>
+      </c>
+      <c r="D229">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B230" t="str">
+        <v>TDSPK220TanecVetraOSN1-8</v>
+      </c>
+      <c r="C230" t="str">
+        <v/>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B231" t="str">
+        <v>TDSPK220PotokKOMP3-8</v>
+      </c>
+      <c r="C231" t="str">
+        <v/>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B232" t="str">
+        <v>TDSPK220VitragiKOMP3-8</v>
+      </c>
+      <c r="C232" t="str">
+        <v/>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B233" t="str">
+        <v>TDSPK220AdamOSN2-8</v>
+      </c>
+      <c r="C233" t="str">
+        <v/>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B234" t="str">
+        <v>TDSPK220MusikVremOSN-8</v>
+      </c>
+      <c r="C234" t="str">
+        <v/>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B235" t="str">
+        <v>TDSPK220SovershenstvoKOMP1-8</v>
+      </c>
+      <c r="C235" t="str">
+        <v/>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B236" t="str">
+        <v>TDSPK220LegkoeDihanieKOMP5-8</v>
+      </c>
+      <c r="C236" t="str">
+        <v/>
+      </c>
+      <c r="D236">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B237" t="str">
+        <v>TDSPK220StoneOSN2-8</v>
+      </c>
+      <c r="C237" t="str">
+        <v/>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B238" t="str">
+        <v>TDSPK220DavidOSN4-8</v>
+      </c>
+      <c r="C238" t="str">
+        <v/>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B239" t="str">
+        <v>TDSPK220KamillaOSN5-8</v>
+      </c>
+      <c r="C239" t="str">
+        <v/>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B240" t="str">
+        <v>TDSPK220AilaOSN3-8</v>
+      </c>
+      <c r="C240" t="str">
+        <v/>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B241" t="str">
+        <v>TDSPK220Otbel120-8</v>
+      </c>
+      <c r="C241" t="str">
+        <v/>
+      </c>
+      <c r="D241">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B242" t="str">
+        <v>TDSPK220OtbleskOSN3-8</v>
+      </c>
+      <c r="C242" t="str">
+        <v/>
+      </c>
+      <c r="D242">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B243" t="str">
+        <v>TDSPK220AristokrKOMP8-8</v>
+      </c>
+      <c r="C243" t="str">
+        <v/>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B244" t="str">
+        <v>TDSPK220BlossomDreamsOSN2-8</v>
+      </c>
+      <c r="C244" t="str">
+        <v/>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B245" t="str">
+        <v>TDSPK220BalFlowersOSN1-8</v>
+      </c>
+      <c r="C245" t="str">
+        <v/>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>TDSPK220MetamorphosaOSN2-8</v>
+      </c>
+      <c r="C246" t="str">
+        <v/>
+      </c>
+      <c r="D246">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B247" t="str">
+        <v>TDSPK220EdemOSN-8</v>
+      </c>
+      <c r="C247" t="str">
+        <v/>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B248" t="str">
+        <v>TDSPK220AdagioOSN4-8</v>
+      </c>
+      <c r="C248" t="str">
+        <v/>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B249" t="str">
+        <v>TDSPK220AristokrKOMP4-8</v>
+      </c>
+      <c r="C249" t="str">
+        <v/>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B250" t="str">
+        <v>TDSPK220BuketChuvstvKOMP2-8</v>
+      </c>
+      <c r="C250" t="str">
+        <v/>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B251" t="str">
+        <v>TDSPK220GabrielKOMP3-8</v>
+      </c>
+      <c r="C251" t="str">
+        <v/>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B252" t="str">
+        <v>TDSPK220EtudOSN5-8</v>
+      </c>
+      <c r="C252" t="str">
+        <v/>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B253" t="str">
+        <v>TDSPK220ZolotayaOSN-8</v>
+      </c>
+      <c r="C253" t="str">
+        <v/>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B254" t="str">
+        <v>TDSPK220ZolotayaKOMP-8</v>
+      </c>
+      <c r="C254" t="str">
+        <v/>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B255" t="str">
+        <v>TDSPK220VozdSharOSN2-8</v>
+      </c>
+      <c r="C255" t="str">
+        <v/>
+      </c>
+      <c r="D255">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B256" t="str">
+        <v>TDSPK220HappyDaysKOMP2-8</v>
+      </c>
+      <c r="C256" t="str">
+        <v/>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B257" t="str">
+        <v>TDP150AngelGuard</v>
+      </c>
+      <c r="C257" t="str">
+        <v/>
+      </c>
+      <c r="D257">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B258" t="str">
+        <v>TDP150Balerina</v>
+      </c>
+      <c r="C258" t="str">
+        <v/>
+      </c>
+      <c r="D258">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B259" t="str">
+        <v>TDP150BambukoviyMishka</v>
+      </c>
+      <c r="C259" t="str">
+        <v/>
+      </c>
+      <c r="D259">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B260" t="str">
+        <v>TDP150Bike</v>
+      </c>
+      <c r="C260" t="str">
+        <v/>
+      </c>
+      <c r="D260">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B261" t="str">
+        <v>TDP150Capybara</v>
+      </c>
+      <c r="C261" t="str">
+        <v/>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B262" t="str">
+        <v>TDP150Championat</v>
+      </c>
+      <c r="C262" t="str">
+        <v/>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B263" t="str">
+        <v>TDP150Charodeyki</v>
+      </c>
+      <c r="C263" t="str">
+        <v/>
+      </c>
+      <c r="D263">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B264" t="str">
+        <v>TDP150Dinosaurus</v>
+      </c>
+      <c r="C264" t="str">
+        <v/>
+      </c>
+      <c r="D264">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B265" t="str">
+        <v>TDP150DobroeUtro</v>
+      </c>
+      <c r="C265" t="str">
+        <v/>
+      </c>
+      <c r="D265">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B266" t="str">
+        <v>TDP150DorojniyPatrul</v>
+      </c>
+      <c r="C266" t="str">
+        <v/>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B267" t="str">
+        <v>TDP150Era</v>
+      </c>
+      <c r="C267" t="str">
+        <v/>
+      </c>
+      <c r="D267">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B268" t="str">
+        <v>TDP150Faline</v>
+      </c>
+      <c r="C268" t="str">
+        <v/>
+      </c>
+      <c r="D268">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B269" t="str">
+        <v>TDP150Gamer</v>
+      </c>
+      <c r="C269" t="str">
+        <v/>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B270" t="str">
+        <v>TDP150Gloss</v>
+      </c>
+      <c r="C270" t="str">
+        <v/>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B271" t="str">
+        <v>TDP150Gonki</v>
+      </c>
+      <c r="C271" t="str">
+        <v/>
+      </c>
+      <c r="D271">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B272" t="str">
+        <v>TDP150Graffiti</v>
+      </c>
+      <c r="C272" t="str">
+        <v/>
+      </c>
+      <c r="D272">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B273" t="str">
+        <v>TDP150Harley</v>
+      </c>
+      <c r="C273" t="str">
+        <v/>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B274" t="str">
+        <v>TDP150Hummer</v>
+      </c>
+      <c r="C274" t="str">
+        <v/>
+      </c>
+      <c r="D274">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B275" t="str">
+        <v>TDP150igrok</v>
+      </c>
+      <c r="C275" t="str">
+        <v/>
+      </c>
+      <c r="D275">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B276" t="str">
+        <v>TDP150JiteliLesa</v>
+      </c>
+      <c r="C276" t="str">
+        <v/>
+      </c>
+      <c r="D276">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B277" t="str">
+        <v>TDP150Kaktus</v>
+      </c>
+      <c r="C277" t="str">
+        <v/>
+      </c>
+      <c r="D277">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B278" t="str">
+        <v>TDP150Konstruktor</v>
+      </c>
+      <c r="C278" t="str">
+        <v/>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>TDP150Koshki</v>
+      </c>
+      <c r="C279" t="str">
+        <v/>
+      </c>
+      <c r="D279">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B280" t="str">
+        <v>TDP150Kotiki</v>
+      </c>
+      <c r="C280" t="str">
+        <v/>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B281" t="str">
+        <v>TDP150KrilatieKacheli</v>
+      </c>
+      <c r="C281" t="str">
+        <v/>
+      </c>
+      <c r="D281">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B282" t="str">
+        <v>TDP150LakomkaKOMP</v>
+      </c>
+      <c r="C282" t="str">
+        <v/>
+      </c>
+      <c r="D282">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B283" t="str">
+        <v>TDP150LesnieNimfi</v>
+      </c>
+      <c r="C283" t="str">
+        <v/>
+      </c>
+      <c r="D283">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B284" t="str">
+        <v>TDP150Love</v>
+      </c>
+      <c r="C284" t="str">
+        <v/>
+      </c>
+      <c r="D284">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B285" t="str">
+        <v>TDP150Manhattan</v>
+      </c>
+      <c r="C285" t="str">
+        <v/>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B286" t="str">
+        <v>TDP150Milashki3</v>
+      </c>
+      <c r="C286" t="str">
+        <v/>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>TDP150MirChudes</v>
+      </c>
+      <c r="C287" t="str">
+        <v/>
+      </c>
+      <c r="D287">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B288" t="str">
+        <v>TDP150MorskieObitateli</v>
+      </c>
+      <c r="C288" t="str">
+        <v/>
+      </c>
+      <c r="D288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B289" t="str">
+        <v>TDP150MoyaZaika</v>
+      </c>
+      <c r="C289" t="str">
+        <v/>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B290" t="str">
+        <v>TDP150Neon</v>
+      </c>
+      <c r="C290" t="str">
+        <v/>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B291" t="str">
+        <v>TDP150NochnieFonariki</v>
+      </c>
+      <c r="C291" t="str">
+        <v/>
+      </c>
+      <c r="D291">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B292" t="str">
+        <v>TDP150Ocean</v>
+      </c>
+      <c r="C292" t="str">
+        <v/>
+      </c>
+      <c r="D292">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B293" t="str">
+        <v>TDP150Otbelka</v>
+      </c>
+      <c r="C293" t="str">
+        <v/>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B294" t="str">
+        <v>TDP150OtVinta</v>
+      </c>
+      <c r="C294" t="str">
+        <v/>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B295" t="str">
+        <v>TDP150Pehotinec</v>
+      </c>
+      <c r="C295" t="str">
+        <v/>
+      </c>
+      <c r="D295">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B296" t="str">
+        <v>TDP150Pingvie</v>
+      </c>
+      <c r="C296" t="str">
+        <v/>
+      </c>
+      <c r="D296">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B297" t="str">
+        <v>TDP150Polet</v>
+      </c>
+      <c r="C297" t="str">
+        <v/>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B298" t="str">
+        <v>TDP150Polosatiki</v>
+      </c>
+      <c r="C298" t="str">
+        <v/>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B299" t="str">
+        <v>TDP150Princessa</v>
+      </c>
+      <c r="C299" t="str">
+        <v/>
+      </c>
+      <c r="D299">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B300" t="str">
+        <v>TDP150Retro</v>
+      </c>
+      <c r="C300" t="str">
+        <v/>
+      </c>
+      <c r="D300">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B301" t="str">
+        <v>TDP150Romantica</v>
+      </c>
+      <c r="C301" t="str">
+        <v/>
+      </c>
+      <c r="D301">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B302" t="str">
+        <v>TDP150Skorost</v>
+      </c>
+      <c r="C302" t="str">
+        <v/>
+      </c>
+      <c r="D302">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B303" t="str">
+        <v>TDP150SladkihSnov</v>
+      </c>
+      <c r="C303" t="str">
+        <v/>
+      </c>
+      <c r="D303">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B304" t="str">
+        <v>TDP150SonyaKOMP</v>
+      </c>
+      <c r="C304" t="str">
+        <v/>
+      </c>
+      <c r="D304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B305" t="str">
+        <v>TDP150SonyaOSNOV</v>
+      </c>
+      <c r="C305" t="str">
+        <v/>
+      </c>
+      <c r="D305">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B306" t="str">
+        <v>TDP150SovyataKOMP</v>
+      </c>
+      <c r="C306" t="str">
+        <v/>
+      </c>
+      <c r="D306">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B307" t="str">
+        <v>TDP150Sport2</v>
+      </c>
+      <c r="C307" t="str">
+        <v/>
+      </c>
+      <c r="D307">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B308" t="str">
+        <v>TDP150StreetArt</v>
+      </c>
+      <c r="C308" t="str">
+        <v/>
+      </c>
+      <c r="D308">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B309" t="str">
+        <v>TDP150StreetRace</v>
+      </c>
+      <c r="C309" t="str">
+        <v/>
+      </c>
+      <c r="D309">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B310" t="str">
+        <v>TDP150Sumerki</v>
+      </c>
+      <c r="C310" t="str">
+        <v/>
+      </c>
+      <c r="D310">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B311" t="str">
+        <v>TDP150SuperLady</v>
+      </c>
+      <c r="C311" t="str">
+        <v/>
+      </c>
+      <c r="D311">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B312" t="str">
+        <v>TDP150SvetliyAngel</v>
+      </c>
+      <c r="C312" t="str">
+        <v/>
+      </c>
+      <c r="D312">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B313" t="str">
+        <v>TDP150Tank</v>
+      </c>
+      <c r="C313" t="str">
+        <v/>
+      </c>
+      <c r="D313">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B314" t="str">
+        <v>TDP150Tirex</v>
+      </c>
+      <c r="C314" t="str">
+        <v/>
+      </c>
+      <c r="D314">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B315" t="str">
+        <v>TDP150TownHouse</v>
+      </c>
+      <c r="C315" t="str">
+        <v/>
+      </c>
+      <c r="D315">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B316" t="str">
+        <v>TDP150TsvetnieSni</v>
+      </c>
+      <c r="C316" t="str">
+        <v/>
+      </c>
+      <c r="D316">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B317" t="str">
+        <v>TDP150Ulibka</v>
+      </c>
+      <c r="C317" t="str">
+        <v/>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B318" t="str">
+        <v>TDP150Ultra</v>
+      </c>
+      <c r="C318" t="str">
+        <v/>
+      </c>
+      <c r="D318">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B319" t="str">
+        <v>TDP150VanillaSkyCOMP</v>
+      </c>
+      <c r="C319" t="str">
+        <v/>
+      </c>
+      <c r="D319">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B320" t="str">
+        <v>TDP150VanillaSkyOSN</v>
+      </c>
+      <c r="C320" t="str">
+        <v/>
+      </c>
+      <c r="D320">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B321" t="str">
+        <v>TDP150Volshebnici</v>
+      </c>
+      <c r="C321" t="str">
+        <v/>
+      </c>
+      <c r="D321">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B322" t="str">
+        <v>TDP150Zayushki</v>
+      </c>
+      <c r="C322" t="str">
+        <v/>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B323" t="str">
+        <v>TDP150ZvezdnayaPil</v>
+      </c>
+      <c r="C323" t="str">
+        <v/>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B324" t="str">
+        <v>TDP150ZvezdnoeNebo</v>
+      </c>
+      <c r="C324" t="str">
+        <v/>
+      </c>
+      <c r="D324">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B325" t="str">
+        <v>TDP150ZvezdochkaCOMP</v>
+      </c>
+      <c r="C325" t="str">
+        <v/>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B326" t="str">
+        <v>TV-Tigers1-195x165</v>
+      </c>
+      <c r="C326" t="str">
+        <v/>
+      </c>
+      <c r="D326">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B327" t="str">
+        <v>TV-Laguna1-195x165</v>
+      </c>
+      <c r="C327" t="str">
+        <v/>
+      </c>
+      <c r="D327">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B328" t="str">
+        <v>TV-Cherepashki1-195x165</v>
+      </c>
+      <c r="C328" t="str">
+        <v/>
+      </c>
+      <c r="D328">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B329" t="str">
+        <v>TV-Nektar1-195x165</v>
+      </c>
+      <c r="C329" t="str">
+        <v/>
+      </c>
+      <c r="D329">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B330" t="str">
+        <v>TV-NejniyDen1-195x165</v>
+      </c>
+      <c r="C330" t="str">
+        <v/>
+      </c>
+      <c r="D330">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B331" t="str">
+        <v>TV-LetnNoch1-195x165</v>
+      </c>
+      <c r="C331" t="str">
+        <v/>
+      </c>
+      <c r="D331">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B332" t="str">
+        <v>TV-SpelieFrukti1-195x165</v>
+      </c>
+      <c r="C332" t="str">
+        <v/>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B333" t="str">
+        <v>TV-Ailyn1-195x165</v>
+      </c>
+      <c r="C333" t="str">
+        <v/>
+      </c>
+      <c r="D333">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B334" t="str">
+        <v>TV-Pletenie2-195x165</v>
+      </c>
+      <c r="C334" t="str">
+        <v/>
+      </c>
+      <c r="D334">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B335" t="str">
+        <v>TV-NejnoeUtro1-195x165</v>
+      </c>
+      <c r="C335" t="str">
+        <v/>
+      </c>
+      <c r="D335">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B336" t="str">
+        <v>TV-OvoshKorzin1-195x165</v>
+      </c>
+      <c r="C336" t="str">
+        <v/>
+      </c>
+      <c r="D336">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B337" t="str">
+        <v>TV-KitayPeyzazh1-195x165</v>
+      </c>
+      <c r="C337" t="str">
+        <v/>
+      </c>
+      <c r="D337">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B338" t="str">
+        <v>TV-Ailyn2-195x165</v>
+      </c>
+      <c r="C338" t="str">
+        <v/>
+      </c>
+      <c r="D338">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B339" t="str">
+        <v>TV-Asia1-195x165</v>
+      </c>
+      <c r="C339" t="str">
+        <v/>
+      </c>
+      <c r="D339">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>TV-Kolyadki1-195x165</v>
+      </c>
+      <c r="C340" t="str">
+        <v/>
+      </c>
+      <c r="D340">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B341" t="str">
+        <v>TV-Elochka1-195x165</v>
+      </c>
+      <c r="C341" t="str">
+        <v/>
+      </c>
+      <c r="D341">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B342" t="str">
+        <v>TV-LimonKorzinka1-195x165</v>
+      </c>
+      <c r="C342" t="str">
+        <v/>
+      </c>
+      <c r="D342">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B343" t="str">
+        <v>TV-Elis1-195x165</v>
+      </c>
+      <c r="C343" t="str">
+        <v/>
+      </c>
+      <c r="D343">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B344" t="str">
+        <v>TV-EchoVesni1-195x165</v>
+      </c>
+      <c r="C344" t="str">
+        <v/>
+      </c>
+      <c r="D344">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B345" t="str">
+        <v>TV-Hutoryanka1-195x165</v>
+      </c>
+      <c r="C345" t="str">
+        <v/>
+      </c>
+      <c r="D345">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B346" t="str">
+        <v>TV-VesenMelody1-195x165</v>
+      </c>
+      <c r="C346" t="str">
+        <v/>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B347" t="str">
+        <v>TV-PodCvetomRozi1-195x165</v>
+      </c>
+      <c r="C347" t="str">
+        <v/>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B348" t="str">
+        <v>TV-Lavanda1-195x165</v>
+      </c>
+      <c r="C348" t="str">
+        <v/>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B349" t="str">
+        <v>TV-SlegkimParom1-195x165</v>
+      </c>
+      <c r="C349" t="str">
+        <v/>
+      </c>
+      <c r="D349">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B350" t="str">
+        <v>TV-Mayolika1-195x165</v>
+      </c>
+      <c r="C350" t="str">
+        <v/>
+      </c>
+      <c r="D350">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B351" t="str">
+        <v>TV-Tropicana1-195x165</v>
+      </c>
+      <c r="C351" t="str">
+        <v/>
+      </c>
+      <c r="D351">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B352" t="str">
+        <v>TV-Kolyadki2-195x165</v>
+      </c>
+      <c r="C352" t="str">
+        <v/>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B353" t="str">
+        <v>TV-LegkiyLepestok2-195x165</v>
+      </c>
+      <c r="C353" t="str">
+        <v/>
+      </c>
+      <c r="D353">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D353"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/td-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/td-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D353"/>
+  <dimension ref="A1:D377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4954,7 +4954,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B326" t="str">
-        <v>TV-Tigers1-195x165</v>
+        <v>TDPPKOchkiCOMP1</v>
       </c>
       <c r="C326" t="str">
         <v/>
@@ -4968,7 +4968,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B327" t="str">
-        <v>TV-Laguna1-195x165</v>
+        <v>TDPPKPolnochOSN1</v>
       </c>
       <c r="C327" t="str">
         <v/>
@@ -4982,7 +4982,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B328" t="str">
-        <v>TV-Cherepashki1-195x165</v>
+        <v>TDPPKPinkFlamingoOSN1</v>
       </c>
       <c r="C328" t="str">
         <v/>
@@ -4996,7 +4996,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B329" t="str">
-        <v>TV-Nektar1-195x165</v>
+        <v>TDPPKZacharovanFlowerOSN1</v>
       </c>
       <c r="C329" t="str">
         <v/>
@@ -5010,7 +5010,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B330" t="str">
-        <v>TV-NejniyDen1-195x165</v>
+        <v>TDPPKBananasOSN1</v>
       </c>
       <c r="C330" t="str">
         <v/>
@@ -5024,7 +5024,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B331" t="str">
-        <v>TV-LetnNoch1-195x165</v>
+        <v>TDPPKObnimashkiOSN1</v>
       </c>
       <c r="C331" t="str">
         <v/>
@@ -5038,7 +5038,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B332" t="str">
-        <v>TV-SpelieFrukti1-195x165</v>
+        <v>TDPPKPassiaOSN1</v>
       </c>
       <c r="C332" t="str">
         <v/>
@@ -5052,7 +5052,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B333" t="str">
-        <v>TV-Ailyn1-195x165</v>
+        <v>TDPPKKawaiCOMP1</v>
       </c>
       <c r="C333" t="str">
         <v/>
@@ -5066,7 +5066,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B334" t="str">
-        <v>TV-Pletenie2-195x165</v>
+        <v>TDPPKFelixCOMP1</v>
       </c>
       <c r="C334" t="str">
         <v/>
@@ -5080,13 +5080,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B335" t="str">
-        <v>TV-NejnoeUtro1-195x165</v>
+        <v>TDPPKBotanicCOMP1</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -5094,13 +5094,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B336" t="str">
-        <v>TV-OvoshKorzin1-195x165</v>
+        <v>TDPPKTvorchestvoCOMP1</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -5108,13 +5108,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B337" t="str">
-        <v>TV-KitayPeyzazh1-195x165</v>
+        <v>TDPPKCharlotteOSN2</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -5122,7 +5122,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B338" t="str">
-        <v>TV-Ailyn2-195x165</v>
+        <v>TDPPKHorizontOSN1</v>
       </c>
       <c r="C338" t="str">
         <v/>
@@ -5136,13 +5136,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B339" t="str">
-        <v>TV-Asia1-195x165</v>
+        <v>TDPPKMissandeyaOSN1</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -5150,13 +5150,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B340" t="str">
-        <v>TV-Kolyadki1-195x165</v>
+        <v>TDPPKProzrachVozdOSN1</v>
       </c>
       <c r="C340" t="str">
         <v/>
       </c>
       <c r="D340">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -5164,7 +5164,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B341" t="str">
-        <v>TV-Elochka1-195x165</v>
+        <v>TDPPKKorgiOSN1</v>
       </c>
       <c r="C341" t="str">
         <v/>
@@ -5178,13 +5178,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B342" t="str">
-        <v>TV-LimonKorzinka1-195x165</v>
+        <v>TDPPKBotanicaOSN1</v>
       </c>
       <c r="C342" t="str">
         <v/>
       </c>
       <c r="D342">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -5192,13 +5192,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B343" t="str">
-        <v>TV-Elis1-195x165</v>
+        <v>TDPPKFelixOSN1</v>
       </c>
       <c r="C343" t="str">
         <v/>
       </c>
       <c r="D343">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -5206,7 +5206,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B344" t="str">
-        <v>TV-EchoVesni1-195x165</v>
+        <v>TDPPKPlavnieLiniiOSN1</v>
       </c>
       <c r="C344" t="str">
         <v/>
@@ -5220,7 +5220,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B345" t="str">
-        <v>TV-Hutoryanka1-195x165</v>
+        <v>TDPPKOrionOSN4</v>
       </c>
       <c r="C345" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B346" t="str">
-        <v>TV-VesenMelody1-195x165</v>
+        <v>TDPPKMissandeyaCOMP1</v>
       </c>
       <c r="C346" t="str">
         <v/>
@@ -5248,7 +5248,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B347" t="str">
-        <v>TV-PodCvetomRozi1-195x165</v>
+        <v>TDPPKTvorchestvoOSN1</v>
       </c>
       <c r="C347" t="str">
         <v/>
@@ -5262,7 +5262,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B348" t="str">
-        <v>TV-Lavanda1-195x165</v>
+        <v>TDPPKKorgiCOMP1</v>
       </c>
       <c r="C348" t="str">
         <v/>
@@ -5276,7 +5276,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B349" t="str">
-        <v>TV-SlegkimParom1-195x165</v>
+        <v>TDPPKKawaiOSN1</v>
       </c>
       <c r="C349" t="str">
         <v/>
@@ -5290,7 +5290,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B350" t="str">
-        <v>TV-Mayolika1-195x165</v>
+        <v>TV-Tigers1-195x165</v>
       </c>
       <c r="C350" t="str">
         <v/>
@@ -5304,7 +5304,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B351" t="str">
-        <v>TV-Tropicana1-195x165</v>
+        <v>TV-Laguna1-195x165</v>
       </c>
       <c r="C351" t="str">
         <v/>
@@ -5318,13 +5318,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B352" t="str">
-        <v>TV-Kolyadki2-195x165</v>
+        <v>TV-Cherepashki1-195x165</v>
       </c>
       <c r="C352" t="str">
         <v/>
       </c>
       <c r="D352">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
@@ -5332,18 +5332,354 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B353" t="str">
+        <v>TV-Nektar1-195x165</v>
+      </c>
+      <c r="C353" t="str">
+        <v/>
+      </c>
+      <c r="D353">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B354" t="str">
+        <v>TV-NejniyDen1-195x165</v>
+      </c>
+      <c r="C354" t="str">
+        <v/>
+      </c>
+      <c r="D354">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B355" t="str">
+        <v>TV-LetnNoch1-195x165</v>
+      </c>
+      <c r="C355" t="str">
+        <v/>
+      </c>
+      <c r="D355">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B356" t="str">
+        <v>TV-SpelieFrukti1-195x165</v>
+      </c>
+      <c r="C356" t="str">
+        <v/>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B357" t="str">
+        <v>TV-Ailyn1-195x165</v>
+      </c>
+      <c r="C357" t="str">
+        <v/>
+      </c>
+      <c r="D357">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B358" t="str">
+        <v>TV-Pletenie2-195x165</v>
+      </c>
+      <c r="C358" t="str">
+        <v/>
+      </c>
+      <c r="D358">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B359" t="str">
+        <v>TV-NejnoeUtro1-195x165</v>
+      </c>
+      <c r="C359" t="str">
+        <v/>
+      </c>
+      <c r="D359">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B360" t="str">
+        <v>TV-OvoshKorzin1-195x165</v>
+      </c>
+      <c r="C360" t="str">
+        <v/>
+      </c>
+      <c r="D360">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B361" t="str">
+        <v>TV-KitayPeyzazh1-195x165</v>
+      </c>
+      <c r="C361" t="str">
+        <v/>
+      </c>
+      <c r="D361">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B362" t="str">
+        <v>TV-Ailyn2-195x165</v>
+      </c>
+      <c r="C362" t="str">
+        <v/>
+      </c>
+      <c r="D362">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B363" t="str">
+        <v>TV-Asia1-195x165</v>
+      </c>
+      <c r="C363" t="str">
+        <v/>
+      </c>
+      <c r="D363">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B364" t="str">
+        <v>TV-Kolyadki1-195x165</v>
+      </c>
+      <c r="C364" t="str">
+        <v/>
+      </c>
+      <c r="D364">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B365" t="str">
+        <v>TV-Elochka1-195x165</v>
+      </c>
+      <c r="C365" t="str">
+        <v/>
+      </c>
+      <c r="D365">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B366" t="str">
+        <v>TV-LimonKorzinka1-195x165</v>
+      </c>
+      <c r="C366" t="str">
+        <v/>
+      </c>
+      <c r="D366">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B367" t="str">
+        <v>TV-Elis1-195x165</v>
+      </c>
+      <c r="C367" t="str">
+        <v/>
+      </c>
+      <c r="D367">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B368" t="str">
+        <v>TV-EchoVesni1-195x165</v>
+      </c>
+      <c r="C368" t="str">
+        <v/>
+      </c>
+      <c r="D368">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B369" t="str">
+        <v>TV-Hutoryanka1-195x165</v>
+      </c>
+      <c r="C369" t="str">
+        <v/>
+      </c>
+      <c r="D369">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B370" t="str">
+        <v>TV-VesenMelody1-195x165</v>
+      </c>
+      <c r="C370" t="str">
+        <v/>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B371" t="str">
+        <v>TV-PodCvetomRozi1-195x165</v>
+      </c>
+      <c r="C371" t="str">
+        <v/>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B372" t="str">
+        <v>TV-Lavanda1-195x165</v>
+      </c>
+      <c r="C372" t="str">
+        <v/>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>TV-SlegkimParom1-195x165</v>
+      </c>
+      <c r="C373" t="str">
+        <v/>
+      </c>
+      <c r="D373">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B374" t="str">
+        <v>TV-Mayolika1-195x165</v>
+      </c>
+      <c r="C374" t="str">
+        <v/>
+      </c>
+      <c r="D374">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B375" t="str">
+        <v>TV-Tropicana1-195x165</v>
+      </c>
+      <c r="C375" t="str">
+        <v/>
+      </c>
+      <c r="D375">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B376" t="str">
+        <v>TV-Kolyadki2-195x165</v>
+      </c>
+      <c r="C376" t="str">
+        <v/>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B377" t="str">
         <v>TV-LegkiyLepestok2-195x165</v>
       </c>
-      <c r="C353" t="str">
-        <v/>
-      </c>
-      <c r="D353">
+      <c r="C377" t="str">
+        <v/>
+      </c>
+      <c r="D377">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D353"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D377"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/td-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/td-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D582"/>
+  <dimension ref="A1:D614"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -578,7 +578,7 @@
         <v/>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -662,7 +662,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -788,7 +788,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -858,7 +858,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -900,7 +900,7 @@
         <v/>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1278,7 +1278,7 @@
         <v/>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1328,7 +1328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>TDPPKAttikaComp33</v>
+        <v>TDM-rose</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1342,7 +1342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>TDPPKBelStihOSN33</v>
+        <v>TDPPKAttikaComp33</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>TDPPKGetsbiOsn33</v>
+        <v>TDPPKBelStihOSN33</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1370,7 +1370,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>TDPPKKotofeiOsn33</v>
+        <v>TDPPKGetsbiOsn33</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1384,7 +1384,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>TDPPKabstraciaCOMP33</v>
+        <v>TDPPKKotofeiOsn33</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -1398,7 +1398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>TDM-Otbel125</v>
+        <v>TDPPKabstraciaCOMP33</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1412,7 +1412,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>TDPPKMagnoliyaComp33</v>
+        <v>TDM-Otbel125</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1426,7 +1426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>TDPPKBelBuketKomp</v>
+        <v>TDPPKMagnoliyaComp33</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1440,13 +1440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>TDPPKBelBuketOsn</v>
+        <v>TDPPK235BelBuketKOMP1</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1454,7 +1454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>TDSPK220KamillaKOMP5</v>
+        <v>TDPPK235BelBuketOSN1</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>TDSPK220SovershenstvoKOMP1</v>
+        <v>TDSPK220KamillaKOMP5</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>TDSPK220EdemOSN</v>
+        <v>TDSPK220SovershenstvoKOMP1</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>TDSPK220ZolotayaOSN</v>
+        <v>TDSPK220EdemOSN</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1510,13 +1510,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>TDSPK220AristokrOSN8</v>
+        <v>TDSPK220ZolotayaOSN</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1524,13 +1524,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>TDSPK220SolnPticOSN</v>
+        <v>TDSPK220AristokrOSN8</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -1538,7 +1538,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>TDSPK220MusikVremOSN</v>
+        <v>TDSPK220SolnPticOSN</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>TDSPK220ZolotayaKOMP</v>
+        <v>TDSPK220MusikVremOSN</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -1566,7 +1566,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>TDSPK220AdagioOSN4</v>
+        <v>TDSPK220ZolotayaKOMP</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>TDSPK220AdamOSN2</v>
+        <v>TDSPK220AdagioOSN4</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1594,13 +1594,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>TDSPK220AilaKOMP3</v>
+        <v>TDSPK220AdamOSN2</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1608,7 +1608,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>TDSPK220AilaOSN3</v>
+        <v>TDSPK220AilaKOMP3</v>
       </c>
       <c r="C87" t="str">
         <v/>
@@ -1622,13 +1622,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>TDSPK220AristokrKOMP4</v>
+        <v>TDSPK220AilaOSN3</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -1636,7 +1636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>TDSPK220AristokrKOMP8</v>
+        <v>TDSPK220AristokrKOMP4</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1650,13 +1650,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>TDSPK220AristokrOSN4</v>
+        <v>TDSPK220AristokrKOMP8</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1664,7 +1664,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>TDSPK220AsteriaOSN4</v>
+        <v>TDSPK220AristokrOSN4</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -1678,13 +1678,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>TDSPK220BalFlowersKOMP1</v>
+        <v>TDSPK220AsteriaOSN4</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1692,7 +1692,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>TDSPK220BalFlowersOSN1</v>
+        <v>TDSPK220BalFlowersKOMP1</v>
       </c>
       <c r="C93" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>TDSPK220BuketChuvstvKOMP2</v>
+        <v>TDSPK220BalFlowersOSN1</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -1720,7 +1720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>TDSPK220BuketChuvstvOSN2</v>
+        <v>TDSPK220BuketChuvstvKOMP2</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1734,7 +1734,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>TDSPK220VitragiKOMP3</v>
+        <v>TDSPK220BuketChuvstvOSN2</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -1748,7 +1748,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>TDSPK220VitragiOSN3</v>
+        <v>TDSPK220VitragiKOMP3</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -1762,13 +1762,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>TDSPK220VozdSharOSN2</v>
+        <v>TDSPK220VitragiOSN3</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -1776,13 +1776,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>TDSPK220MetamorphosaOSN2</v>
+        <v>TDSPK220VozdSharOSN2</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1790,7 +1790,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>TDSPK220PachuliKOMP1</v>
+        <v>TDSPK220MetamorphosaOSN2</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -1804,13 +1804,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>TDSPK220HugOSN2</v>
+        <v>TDSPK220PachuliKOMP1</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1818,7 +1818,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>TDSPK220GabrielKOMP3</v>
+        <v>TDSPK220HugOSN2</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>TDSPK220GabrielOSN3</v>
+        <v>TDSPK220GabrielKOMP3</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -1846,7 +1846,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>TDSPK220DavidOSN4</v>
+        <v>TDSPK220GabrielOSN3</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -1860,7 +1860,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>TDSPK220ZataivDihanieKOMP6</v>
+        <v>TDSPK220DavidOSN4</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -1874,13 +1874,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>TDSPK220ZataivDihanieOSN6</v>
+        <v>TDSPK220ZataivDihanieKOMP6</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>TDSPK220KamillaOSN5</v>
+        <v>TDSPK220ZataivDihanieOSN6</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1902,7 +1902,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>TDSPK220CaribbeanOSN2</v>
+        <v>TDSPK220KamillaOSN5</v>
       </c>
       <c r="C108" t="str">
         <v/>
@@ -1916,7 +1916,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>TDSPK220KarolinaOSN3</v>
+        <v>TDSPK220CaribbeanOSN2</v>
       </c>
       <c r="C109" t="str">
         <v/>
@@ -1930,7 +1930,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B110" t="str">
-        <v>TDSPK220Kashmir1</v>
+        <v>TDSPK220KarolinaOSN3</v>
       </c>
       <c r="C110" t="str">
         <v/>
@@ -1944,13 +1944,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B111" t="str">
-        <v>TDSPK220LegkoeDihanieOSN5</v>
+        <v>TDSPK220Kashmir1</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -1958,13 +1958,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B112" t="str">
-        <v>TDSPK220LetniyZnoiOSN2</v>
+        <v>TDSPK220LegkoeDihanieOSN5</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1972,13 +1972,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B113" t="str">
-        <v>TDSPK220Monochrome1</v>
+        <v>TDSPK220LetniyZnoiOSN2</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -1986,7 +1986,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B114" t="str">
-        <v>TDSPK220Monochrome7</v>
+        <v>TDSPK220Monochrome1</v>
       </c>
       <c r="C114" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B115" t="str">
-        <v>TDSPK220Monochrome8</v>
+        <v>TDSPK220Monochrome7</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2014,7 +2014,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B116" t="str">
-        <v>TDSPK220Monochrome12</v>
+        <v>TDSPK220Monochrome8</v>
       </c>
       <c r="C116" t="str">
         <v/>
@@ -2028,7 +2028,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B117" t="str">
-        <v>TDSPK220NostalgiKOMP4</v>
+        <v>TDSPK220Monochrome12</v>
       </c>
       <c r="C117" t="str">
         <v/>
@@ -2042,13 +2042,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B118" t="str">
-        <v>TDSPK220ObitelLoveOSN2</v>
+        <v>TDSPK220NostalgiKOMP4</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2056,13 +2056,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B119" t="str">
-        <v>TDSPK220OdaNejnostiKOMP2</v>
+        <v>TDSPK220ObitelLoveOSN2</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -2070,13 +2070,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B120" t="str">
-        <v>TDSPK220OdaNejnostiOSN2</v>
+        <v>TDSPK220OdaNejnostiKOMP2</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2084,7 +2084,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B121" t="str">
-        <v>TDSPK220Otbel120</v>
+        <v>TDSPK220OdaNejnostiOSN2</v>
       </c>
       <c r="C121" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B122" t="str">
-        <v>TDSPK220OtbleskKOMP3</v>
+        <v>TDSPK220Otbel120</v>
       </c>
       <c r="C122" t="str">
         <v/>
@@ -2112,13 +2112,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B123" t="str">
-        <v>TDSPK220HappyDaysOSN2</v>
+        <v>TDSPK220OtbleskKOMP3</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2126,13 +2126,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B124" t="str">
-        <v>TDSPK220PachuliOSN1</v>
+        <v>TDSPK220HappyDaysOSN2</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2140,7 +2140,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B125" t="str">
-        <v>TDSPK220PotokKOMP3</v>
+        <v>TDSPK220PachuliOSN1</v>
       </c>
       <c r="C125" t="str">
         <v/>
@@ -2154,7 +2154,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B126" t="str">
-        <v>TDSPK220HappyDaysKOMP2</v>
+        <v>TDSPK220PotokKOMP3</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -2168,13 +2168,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B127" t="str">
-        <v>TDSPK220PotokOSN3</v>
+        <v>TDSPK220HappyDaysKOMP2</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -2182,13 +2182,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B128" t="str">
-        <v>TDSPK220StepKOMP</v>
+        <v>TDSPK220PotokOSN3</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
@@ -2196,13 +2196,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B129" t="str">
-        <v>TDSPK220LegkoeDihanieKOMP5</v>
+        <v>TDSPK220StepKOMP</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -2210,7 +2210,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B130" t="str">
-        <v>TDSPK220OtbleskOSN3</v>
+        <v>TDSPK220LegkoeDihanieKOMP5</v>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -2224,13 +2224,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B131" t="str">
-        <v>TDSPK220StoneOSN2</v>
+        <v>TDSPK220OtbleskOSN3</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
@@ -2238,7 +2238,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B132" t="str">
-        <v>TDSPK220StoneKOMP2</v>
+        <v>TDSPK220StoneOSN2</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -2252,7 +2252,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B133" t="str">
-        <v>TDSPK220SoloKOMP1</v>
+        <v>TDSPK220StoneKOMP2</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -2266,7 +2266,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B134" t="str">
-        <v>TDSPK220EtudOSN5</v>
+        <v>TDSPK220SoloKOMP1</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -2280,7 +2280,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B135" t="str">
-        <v>TDSPK220BlossomDreamsOSN2</v>
+        <v>TDSPK220EtudOSN5</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -2294,7 +2294,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B136" t="str">
-        <v>TDSPK220TanecVetraOSN1</v>
+        <v>TDSPK220BlossomDreamsOSN2</v>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -2308,13 +2308,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B137" t="str">
-        <v>TDSPK220DavidKOMP3</v>
+        <v>TDSPK220TanecVetraOSN1</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2322,13 +2322,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B138" t="str">
-        <v>SSPK250-8-Gorchich</v>
+        <v>TDSPK220DavidKOMP3</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -2336,7 +2336,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B139" t="str">
-        <v>SSPK250-8-Otbel</v>
+        <v>SSPK250-8-Gorchich</v>
       </c>
       <c r="C139" t="str">
         <v/>
@@ -2350,7 +2350,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B140" t="str">
-        <v>SSPK250-8-Ultramarine</v>
+        <v>SSPK250-8-Otbel</v>
       </c>
       <c r="C140" t="str">
         <v/>
@@ -2364,13 +2364,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B141" t="str">
-        <v>SSPK250-8-RoseCream</v>
+        <v>SSPK250-8-Ultramarine</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -2378,13 +2378,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B142" t="str">
-        <v>SSPK250-8-BrightBlue</v>
+        <v>SSPK250-8-RoseCream</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2392,7 +2392,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B143" t="str">
-        <v>SSPK250-8-DustyRose</v>
+        <v>SSPK250-8-BrightBlue</v>
       </c>
       <c r="C143" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B144" t="str">
-        <v>SSPK250-8-Lavanda</v>
+        <v>SSPK250-8-DustyRose</v>
       </c>
       <c r="C144" t="str">
         <v/>
@@ -2420,13 +2420,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B145" t="str">
-        <v>SSPK250-8-Terrakota</v>
+        <v>SSPK250-8-Lavanda</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -2434,13 +2434,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B146" t="str">
-        <v>SSPK250-8-LightBlue</v>
+        <v>SSPK250-8-Terrakota</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
@@ -2448,13 +2448,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B147" t="str">
-        <v>SSPK250-8-KaruzoGreen</v>
+        <v>SSPK250-8-LightBlue</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -2462,7 +2462,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B148" t="str">
-        <v>SSPK250-8-Lazurn</v>
+        <v>SSPK250-8-KaruzoGreen</v>
       </c>
       <c r="C148" t="str">
         <v/>
@@ -2476,13 +2476,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B149" t="str">
-        <v>SSPK250-8-KaruzoViolet</v>
+        <v>SSPK250-8-Lazurn</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -2490,13 +2490,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B150" t="str">
-        <v>SSPK250-8-Coffee</v>
+        <v>SSPK250-8-KaruzoViolet</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -2504,13 +2504,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B151" t="str">
-        <v>SSPK250-8-Verde</v>
+        <v>SSPK250-8-Coffee</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -2518,13 +2518,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B152" t="str">
-        <v>SSPK250-8-Persik</v>
+        <v>SSPK250-8-Verde</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -2532,13 +2532,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B153" t="str">
-        <v>SSPK250-8-Pink</v>
+        <v>SSPK250-8-Persik</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -2546,13 +2546,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B154" t="str">
-        <v>SSPK250-8-Jemjug</v>
+        <v>SSPK250-8-Pink</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -2560,7 +2560,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B155" t="str">
-        <v>SSPK250-8-Nebesn</v>
+        <v>SSPK250-8-Jemjug</v>
       </c>
       <c r="C155" t="str">
         <v/>
@@ -2574,13 +2574,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B156" t="str">
-        <v>SSPK250-8-Grafit</v>
+        <v>SSPK250-8-Nebesn</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -2588,13 +2588,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B157" t="str">
-        <v>SSPK250-8-Blue</v>
+        <v>SSPK250-8-Grafit</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -2602,13 +2602,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B158" t="str">
-        <v>SSPK250-8-Grey</v>
+        <v>SSPK250-8-Blue</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
@@ -2616,7 +2616,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B159" t="str">
-        <v>SSPK250-8-Chocolate</v>
+        <v>SSPK250-8-Grey</v>
       </c>
       <c r="C159" t="str">
         <v/>
@@ -2630,13 +2630,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B160" t="str">
-        <v>SSPK250-8-Green</v>
+        <v>SSPK250-8-Chocolate</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -2644,7 +2644,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B161" t="str">
-        <v>SSPK250-8-Wine</v>
+        <v>SSPK250-8-Green</v>
       </c>
       <c r="C161" t="str">
         <v/>
@@ -2658,13 +2658,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B162" t="str">
-        <v>SSPK250-8-Black</v>
+        <v>SSPK250-8-Wine</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -2672,13 +2672,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B163" t="str">
-        <v>SSPK250-8-Bejeviy</v>
+        <v>SSPK250-8-Black</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
@@ -2686,13 +2686,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B164" t="str">
-        <v>SSPK250-8-Korall</v>
+        <v>SSPK250-8-Bejeviy</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -2700,7 +2700,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B165" t="str">
-        <v>TDSPK250DarkViolet</v>
+        <v>SSPK250-8-Korall</v>
       </c>
       <c r="C165" t="str">
         <v/>
@@ -2714,13 +2714,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B166" t="str">
-        <v>TDSPK250Green</v>
+        <v>TDSPK250DarkViolet</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -2728,13 +2728,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B167" t="str">
-        <v>TDSPK250Persikoviy</v>
+        <v>TDSPK250Green</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -2742,7 +2742,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B168" t="str">
-        <v>TDSPK250Lavanda</v>
+        <v>TDSPK250Persikoviy</v>
       </c>
       <c r="C168" t="str">
         <v/>
@@ -2756,7 +2756,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B169" t="str">
-        <v>TDSPK250Coffee</v>
+        <v>TDSPK250Lavanda</v>
       </c>
       <c r="C169" t="str">
         <v/>
@@ -2770,13 +2770,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B170" t="str">
-        <v>TDSPK250Bordo</v>
+        <v>TDSPK250Coffee</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -2784,7 +2784,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B171" t="str">
-        <v>TDSPK250LightLiliac</v>
+        <v>TDSPK250Bordo</v>
       </c>
       <c r="C171" t="str">
         <v/>
@@ -2798,13 +2798,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B172" t="str">
-        <v>TDSPK250Liliac</v>
+        <v>TDSPK250LightLiliac</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -2812,7 +2812,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B173" t="str">
-        <v>TDSPK250Blue</v>
+        <v>TDSPK250Liliac</v>
       </c>
       <c r="C173" t="str">
         <v/>
@@ -2826,7 +2826,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B174" t="str">
-        <v>TDSPK250Choco</v>
+        <v>TDSPK250Blue</v>
       </c>
       <c r="C174" t="str">
         <v/>
@@ -2840,13 +2840,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B175" t="str">
-        <v>TDSPK250Menthol</v>
+        <v>TDSPK250Choco</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -2854,7 +2854,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B176" t="str">
-        <v>TDSPK250Taup</v>
+        <v>TDSPK250Menthol</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -2868,7 +2868,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B177" t="str">
-        <v>TDSPK250Platina</v>
+        <v>TDSPK250Taup</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -2882,7 +2882,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B178" t="str">
-        <v>TDSPK250White</v>
+        <v>TDSPK250Platina</v>
       </c>
       <c r="C178" t="str">
         <v/>
@@ -2896,7 +2896,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B179" t="str">
-        <v>TDSPK250LightBlue</v>
+        <v>TDSPK250White</v>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -2910,13 +2910,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B180" t="str">
-        <v>TDSPK250PepelRose</v>
+        <v>TDSPK250LightBlue</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -2924,7 +2924,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B181" t="str">
-        <v>TDSPK250Bejeviy</v>
+        <v>TDSPK250PepelRose</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -2938,7 +2938,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B182" t="str">
-        <v>TDSPK250Jemjug</v>
+        <v>TDSPK250Bejeviy</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -2952,7 +2952,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B183" t="str">
-        <v>TDSPK250LightGreen</v>
+        <v>TDSPK250Jemjug</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -2966,7 +2966,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B184" t="str">
-        <v>TDSPK250Gold</v>
+        <v>TDSPK250LightGreen</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -2980,7 +2980,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B185" t="str">
-        <v>TDSPK250Pink</v>
+        <v>TDSPK250Gold</v>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -2994,7 +2994,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B186" t="str">
-        <v>TDSPK250Kvarc</v>
+        <v>TDSPK250Pink</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -3008,7 +3008,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B187" t="str">
-        <v>TDSPK250ToplMilk</v>
+        <v>TDSPK250Kvarc</v>
       </c>
       <c r="C187" t="str">
         <v/>
@@ -3022,7 +3022,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B188" t="str">
-        <v>TDSPK250GrafitGreen</v>
+        <v>TDSPK250ToplMilk</v>
       </c>
       <c r="C188" t="str">
         <v/>
@@ -3036,13 +3036,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B189" t="str">
-        <v>TDSPK250Sliva</v>
+        <v>TDSPK250GrafitGreen</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -3050,13 +3050,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B190" t="str">
-        <v>TDSPK220BuketChuvstvOSN2-8</v>
+        <v>TDSPK250Sliva</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191">
@@ -3064,13 +3064,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B191" t="str">
-        <v>TDSPK220Monochrome8-8</v>
+        <v>TDSPK220BuketChuvstvOSN2-8</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -3078,7 +3078,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B192" t="str">
-        <v>TDSPK220Monochrome1-8</v>
+        <v>TDSPK220Monochrome8-8</v>
       </c>
       <c r="C192" t="str">
         <v/>
@@ -3092,13 +3092,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B193" t="str">
-        <v>TDSPK220AristokrOSN8-8</v>
+        <v>TDSPK220Monochrome1-8</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -3106,7 +3106,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B194" t="str">
-        <v>TDSPK220HappyDaysOSN2-8</v>
+        <v>TDSPK220AristokrOSN8-8</v>
       </c>
       <c r="C194" t="str">
         <v/>
@@ -3120,13 +3120,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B195" t="str">
-        <v>TDSPK220AilaKOMP3-8</v>
+        <v>TDSPK220HappyDaysOSN2-8</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -3134,7 +3134,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B196" t="str">
-        <v>TDSPK220Monochrome7-8</v>
+        <v>TDSPK220AilaKOMP3-8</v>
       </c>
       <c r="C196" t="str">
         <v/>
@@ -3148,13 +3148,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B197" t="str">
-        <v>TDSPK220PotokOSN3-8</v>
+        <v>TDSPK220Monochrome7-8</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -3162,13 +3162,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B198" t="str">
-        <v>TDSPK220EdemKomp-8</v>
+        <v>TDSPK220PotokOSN3-8</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
@@ -3176,7 +3176,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B199" t="str">
-        <v>TDSPK220Monochrome12-8</v>
+        <v>TDSPK220EdemKomp-8</v>
       </c>
       <c r="C199" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B200" t="str">
-        <v>TDSPK220AsteriaOSN4-8</v>
+        <v>TDSPK220Monochrome12-8</v>
       </c>
       <c r="C200" t="str">
         <v/>
@@ -3204,13 +3204,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B201" t="str">
-        <v>TDSPK220HugOSN2-8</v>
+        <v>TDSPK220AsteriaOSN4-8</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -3218,7 +3218,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B202" t="str">
-        <v>TDSPK220KamillaKOMP5-8</v>
+        <v>TDSPK220HugOSN2-8</v>
       </c>
       <c r="C202" t="str">
         <v/>
@@ -3232,7 +3232,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B203" t="str">
-        <v>TDSPK220OttepelOSN-8</v>
+        <v>TDSPK220KamillaKOMP5-8</v>
       </c>
       <c r="C203" t="str">
         <v/>
@@ -3246,13 +3246,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B204" t="str">
-        <v>TDSPK220ObitelLoveOSN2-8</v>
+        <v>TDSPK220OttepelOSN-8</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -3260,7 +3260,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B205" t="str">
-        <v>TDSPK220OdaNejnostiOSN2-8</v>
+        <v>TDSPK220ObitelLoveOSN2-8</v>
       </c>
       <c r="C205" t="str">
         <v/>
@@ -3274,7 +3274,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B206" t="str">
-        <v>TDSPK220CaribbeanOSN2-8</v>
+        <v>TDSPK220OdaNejnostiOSN2-8</v>
       </c>
       <c r="C206" t="str">
         <v/>
@@ -3288,13 +3288,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B207" t="str">
-        <v>TDSPK220NaomiOSN-8</v>
+        <v>TDSPK220CaribbeanOSN2-8</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208">
@@ -3302,7 +3302,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B208" t="str">
-        <v>TDSPK220LegkoeDihanieOSN5-8</v>
+        <v>TDSPK220NaomiOSN-8</v>
       </c>
       <c r="C208" t="str">
         <v/>
@@ -3316,7 +3316,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B209" t="str">
-        <v>TDSPK220OdaNejnostiKOMP2-8</v>
+        <v>TDSPK220LegkoeDihanieOSN5-8</v>
       </c>
       <c r="C209" t="str">
         <v/>
@@ -3330,7 +3330,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B210" t="str">
-        <v>TDSPK220AdonisOSN2-8</v>
+        <v>TDSPK220OdaNejnostiKOMP2-8</v>
       </c>
       <c r="C210" t="str">
         <v/>
@@ -3344,7 +3344,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B211" t="str">
-        <v>TDSPK220StoneKOMP2-8</v>
+        <v>TDSPK220AdonisOSN2-8</v>
       </c>
       <c r="C211" t="str">
         <v/>
@@ -3358,7 +3358,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B212" t="str">
-        <v>TDSPK220NostalgiKOMP4-8</v>
+        <v>TDSPK220StoneKOMP2-8</v>
       </c>
       <c r="C212" t="str">
         <v/>
@@ -3372,13 +3372,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B213" t="str">
-        <v>TDSPK220PachuliKOMP1-8</v>
+        <v>TDSPK220NostalgiKOMP4-8</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -3386,13 +3386,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B214" t="str">
-        <v>TDSPK220PachuliOSN1-8</v>
+        <v>TDSPK220PachuliKOMP1-8</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -3400,7 +3400,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B215" t="str">
-        <v>TDSPK220GabrielOSN3-8</v>
+        <v>TDSPK220PachuliOSN1-8</v>
       </c>
       <c r="C215" t="str">
         <v/>
@@ -3414,7 +3414,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B216" t="str">
-        <v>TDSPK220VitragiOSN3-8</v>
+        <v>TDSPK220GabrielOSN3-8</v>
       </c>
       <c r="C216" t="str">
         <v/>
@@ -3428,13 +3428,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B217" t="str">
-        <v>TDSPK220KarolinaOSN3-8</v>
+        <v>TDSPK220VitragiOSN3-8</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -3442,13 +3442,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B218" t="str">
-        <v>TDSPK220DavidKOMP3-8</v>
+        <v>TDSPK220KarolinaOSN3-8</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -3456,7 +3456,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B219" t="str">
-        <v>TDSPK220StepKOMP-8</v>
+        <v>TDSPK220DavidKOMP3-8</v>
       </c>
       <c r="C219" t="str">
         <v/>
@@ -3470,7 +3470,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B220" t="str">
-        <v>TDSPK220Kashmir1-8</v>
+        <v>TDSPK220StepKOMP-8</v>
       </c>
       <c r="C220" t="str">
         <v/>
@@ -3484,13 +3484,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B221" t="str">
-        <v>TDSPK220SolnPticOSN-8</v>
+        <v>TDSPK220Kashmir1-8</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -3498,13 +3498,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B222" t="str">
-        <v>TDSPK220LetniyZnoiOSN2-8</v>
+        <v>TDSPK220SolnPticOSN-8</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -3512,7 +3512,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B223" t="str">
-        <v>TDSPK220BalFlowersKOMP1-8</v>
+        <v>TDSPK220LetniyZnoiOSN2-8</v>
       </c>
       <c r="C223" t="str">
         <v/>
@@ -3526,7 +3526,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B224" t="str">
-        <v>TDSPK220EtudKOMP7-8</v>
+        <v>TDSPK220BalFlowersKOMP1-8</v>
       </c>
       <c r="C224" t="str">
         <v/>
@@ -3540,13 +3540,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B225" t="str">
-        <v>TDSPK220AristokrOSN4-8</v>
+        <v>TDSPK220EtudKOMP7-8</v>
       </c>
       <c r="C225" t="str">
         <v/>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -3554,13 +3554,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B226" t="str">
-        <v>TDSPK220ZataivDihanieOSN6-8</v>
+        <v>TDSPK220AristokrOSN4-8</v>
       </c>
       <c r="C226" t="str">
         <v/>
       </c>
       <c r="D226">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -3568,7 +3568,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B227" t="str">
-        <v>TDSPK220SoloKOMP1-8</v>
+        <v>TDSPK220ZataivDihanieOSN6-8</v>
       </c>
       <c r="C227" t="str">
         <v/>
@@ -3582,7 +3582,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B228" t="str">
-        <v>TDSPK220OtbleskKOMP3-8</v>
+        <v>TDSPK220SoloKOMP1-8</v>
       </c>
       <c r="C228" t="str">
         <v/>
@@ -3596,7 +3596,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B229" t="str">
-        <v>TDSPK220ZataivDihanieKOMP6-8</v>
+        <v>TDSPK220OtbleskKOMP3-8</v>
       </c>
       <c r="C229" t="str">
         <v/>
@@ -3610,7 +3610,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B230" t="str">
-        <v>TDSPK220TanecVetraOSN1-8</v>
+        <v>TDSPK220ZataivDihanieKOMP6-8</v>
       </c>
       <c r="C230" t="str">
         <v/>
@@ -3624,13 +3624,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B231" t="str">
-        <v>TDSPK220PotokKOMP3-8</v>
+        <v>TDSPK220TanecVetraOSN1-8</v>
       </c>
       <c r="C231" t="str">
         <v/>
       </c>
       <c r="D231">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -3638,7 +3638,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B232" t="str">
-        <v>TDSPK220VitragiKOMP3-8</v>
+        <v>TDSPK220PotokKOMP3-8</v>
       </c>
       <c r="C232" t="str">
         <v/>
@@ -3652,7 +3652,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B233" t="str">
-        <v>TDSPK220AdamOSN2-8</v>
+        <v>TDSPK220VitragiKOMP3-8</v>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -3666,7 +3666,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B234" t="str">
-        <v>TDSPK220MusikVremOSN-8</v>
+        <v>TDSPK220AdamOSN2-8</v>
       </c>
       <c r="C234" t="str">
         <v/>
@@ -3680,7 +3680,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B235" t="str">
-        <v>TDSPK220SovershenstvoKOMP1-8</v>
+        <v>TDSPK220MusikVremOSN-8</v>
       </c>
       <c r="C235" t="str">
         <v/>
@@ -3694,13 +3694,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B236" t="str">
-        <v>TDSPK220LegkoeDihanieKOMP5-8</v>
+        <v>TDSPK220SovershenstvoKOMP1-8</v>
       </c>
       <c r="C236" t="str">
         <v/>
       </c>
       <c r="D236">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -3708,13 +3708,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B237" t="str">
-        <v>TDSPK220StoneOSN2-8</v>
+        <v>TDSPK220LegkoeDihanieKOMP5-8</v>
       </c>
       <c r="C237" t="str">
         <v/>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238">
@@ -3722,7 +3722,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B238" t="str">
-        <v>TDSPK220DavidOSN4-8</v>
+        <v>TDSPK220StoneOSN2-8</v>
       </c>
       <c r="C238" t="str">
         <v/>
@@ -3736,13 +3736,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B239" t="str">
-        <v>TDSPK220KamillaOSN5-8</v>
+        <v>TDSPK220DavidOSN4-8</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -3750,13 +3750,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B240" t="str">
-        <v>TDSPK220AilaOSN3-8</v>
+        <v>TDSPK220KamillaOSN5-8</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
@@ -3764,7 +3764,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B241" t="str">
-        <v>TDSPK220Otbel120-8</v>
+        <v>TDSPK220AilaOSN3-8</v>
       </c>
       <c r="C241" t="str">
         <v/>
@@ -3778,13 +3778,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B242" t="str">
-        <v>TDSPK220OtbleskOSN3-8</v>
+        <v>TDSPK220Otbel120-8</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -3792,13 +3792,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B243" t="str">
-        <v>TDSPK220AristokrKOMP8-8</v>
+        <v>TDSPK220OtbleskOSN3-8</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
@@ -3806,7 +3806,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B244" t="str">
-        <v>TDSPK220BlossomDreamsOSN2-8</v>
+        <v>TDSPK220AristokrKOMP8-8</v>
       </c>
       <c r="C244" t="str">
         <v/>
@@ -3820,7 +3820,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B245" t="str">
-        <v>TDSPK220BalFlowersOSN1-8</v>
+        <v>TDSPK220BlossomDreamsOSN2-8</v>
       </c>
       <c r="C245" t="str">
         <v/>
@@ -3834,13 +3834,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B246" t="str">
-        <v>TDSPK220MetamorphosaOSN2-8</v>
+        <v>TDSPK220BalFlowersOSN1-8</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3848,13 +3848,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B247" t="str">
-        <v>TDSPK220EdemOSN-8</v>
+        <v>TDSPK220MetamorphosaOSN2-8</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
@@ -3862,7 +3862,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B248" t="str">
-        <v>TDSPK220AdagioOSN4-8</v>
+        <v>TDSPK220EdemOSN-8</v>
       </c>
       <c r="C248" t="str">
         <v/>
@@ -3876,7 +3876,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B249" t="str">
-        <v>TDSPK220AristokrKOMP4-8</v>
+        <v>TDSPK220AdagioOSN4-8</v>
       </c>
       <c r="C249" t="str">
         <v/>
@@ -3890,7 +3890,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B250" t="str">
-        <v>TDSPK220BuketChuvstvKOMP2-8</v>
+        <v>TDSPK220AristokrKOMP4-8</v>
       </c>
       <c r="C250" t="str">
         <v/>
@@ -3904,13 +3904,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B251" t="str">
-        <v>TDSPK220GabrielKOMP3-8</v>
+        <v>TDSPK220BuketChuvstvKOMP2-8</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -3918,13 +3918,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B252" t="str">
-        <v>TDSPK220EtudOSN5-8</v>
+        <v>TDSPK220GabrielKOMP3-8</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
@@ -3932,7 +3932,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B253" t="str">
-        <v>TDSPK220ZolotayaOSN-8</v>
+        <v>TDSPK220EtudOSN5-8</v>
       </c>
       <c r="C253" t="str">
         <v/>
@@ -3946,7 +3946,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B254" t="str">
-        <v>TDSPK220ZolotayaKOMP-8</v>
+        <v>TDSPK220ZolotayaOSN-8</v>
       </c>
       <c r="C254" t="str">
         <v/>
@@ -3960,13 +3960,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B255" t="str">
-        <v>TDSPK220VozdSharOSN2-8</v>
+        <v>TDSPK220ZolotayaKOMP-8</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -3974,7 +3974,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B256" t="str">
-        <v>TDSPK220HappyDaysKOMP2-8</v>
+        <v>TDSPK220VozdSharOSN2-8</v>
       </c>
       <c r="C256" t="str">
         <v/>
@@ -3988,13 +3988,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B257" t="str">
-        <v>TDP150AngelGuard</v>
+        <v>TDSPK220HappyDaysKOMP2-8</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -4002,7 +4002,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B258" t="str">
-        <v>TDP150Balerina</v>
+        <v>TDP150AngelGuard</v>
       </c>
       <c r="C258" t="str">
         <v/>
@@ -4016,7 +4016,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B259" t="str">
-        <v>TDP150BambukoviyMishka</v>
+        <v>TDP150Balerina</v>
       </c>
       <c r="C259" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B260" t="str">
-        <v>TDP150Bike</v>
+        <v>TDP150BambukoviyMishka</v>
       </c>
       <c r="C260" t="str">
         <v/>
@@ -4044,13 +4044,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B261" t="str">
-        <v>TDP150Capybara</v>
+        <v>TDP150Bike</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262">
@@ -4058,7 +4058,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B262" t="str">
-        <v>TDP150Championat</v>
+        <v>TDP150Capybara</v>
       </c>
       <c r="C262" t="str">
         <v/>
@@ -4072,13 +4072,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B263" t="str">
-        <v>TDP150Charodeyki</v>
+        <v>TDP150Championat</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -4086,7 +4086,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B264" t="str">
-        <v>TDP150Dinosaurus</v>
+        <v>TDP150Charodeyki</v>
       </c>
       <c r="C264" t="str">
         <v/>
@@ -4100,13 +4100,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B265" t="str">
-        <v>TDP150DobroeUtro</v>
+        <v>TDP150Dinosaurus</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -4114,13 +4114,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B266" t="str">
-        <v>TDP150DorojniyPatrul</v>
+        <v>TDP150DobroeUtro</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267">
@@ -4128,13 +4128,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B267" t="str">
-        <v>TDP150Era</v>
+        <v>TDP150DorojniyPatrul</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -4142,7 +4142,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B268" t="str">
-        <v>TDP150Faline</v>
+        <v>TDP150Era</v>
       </c>
       <c r="C268" t="str">
         <v/>
@@ -4156,13 +4156,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B269" t="str">
-        <v>TDP150Gamer</v>
+        <v>TDP150Faline</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270">
@@ -4170,7 +4170,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B270" t="str">
-        <v>TDP150Gloss</v>
+        <v>TDP150Gamer</v>
       </c>
       <c r="C270" t="str">
         <v/>
@@ -4184,7 +4184,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B271" t="str">
-        <v>TDP150Gonki</v>
+        <v>TDP150Gloss</v>
       </c>
       <c r="C271" t="str">
         <v/>
@@ -4198,13 +4198,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B272" t="str">
-        <v>TDP150Graffiti</v>
+        <v>TDP150Gonki</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -4212,13 +4212,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B273" t="str">
-        <v>TDP150Harley</v>
+        <v>TDP150Graffiti</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274">
@@ -4226,13 +4226,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B274" t="str">
-        <v>TDP150Hummer</v>
+        <v>TDP150Harley</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -4240,7 +4240,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B275" t="str">
-        <v>TDP150igrok</v>
+        <v>TDP150Hummer</v>
       </c>
       <c r="C275" t="str">
         <v/>
@@ -4254,13 +4254,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B276" t="str">
-        <v>TDP150JiteliLesa</v>
+        <v>TDP150igrok</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277">
@@ -4268,13 +4268,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B277" t="str">
-        <v>TDP150Kaktus</v>
+        <v>TDP150JiteliLesa</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -4282,13 +4282,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B278" t="str">
-        <v>TDP150Konstruktor</v>
+        <v>TDP150Kaktus</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -4296,7 +4296,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B279" t="str">
-        <v>TDP150Koshki</v>
+        <v>TDP150Konstruktor</v>
       </c>
       <c r="C279" t="str">
         <v/>
@@ -4310,7 +4310,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B280" t="str">
-        <v>TDP150Kotiki</v>
+        <v>TDP150Koshki</v>
       </c>
       <c r="C280" t="str">
         <v/>
@@ -4324,7 +4324,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B281" t="str">
-        <v>TDP150KrilatieKacheli</v>
+        <v>TDP150Kotiki</v>
       </c>
       <c r="C281" t="str">
         <v/>
@@ -4338,13 +4338,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B282" t="str">
-        <v>TDP150LakomkaKOMP</v>
+        <v>TDP150KrilatieKacheli</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -4352,7 +4352,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B283" t="str">
-        <v>TDP150LesnieNimfi</v>
+        <v>TDP150LakomkaKOMP</v>
       </c>
       <c r="C283" t="str">
         <v/>
@@ -4366,7 +4366,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B284" t="str">
-        <v>TDP150Love</v>
+        <v>TDP150LesnieNimfi</v>
       </c>
       <c r="C284" t="str">
         <v/>
@@ -4380,7 +4380,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B285" t="str">
-        <v>TDP150Manhattan</v>
+        <v>TDP150Love</v>
       </c>
       <c r="C285" t="str">
         <v/>
@@ -4394,7 +4394,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B286" t="str">
-        <v>TDP150Milashki3</v>
+        <v>TDP150Manhattan</v>
       </c>
       <c r="C286" t="str">
         <v/>
@@ -4408,13 +4408,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B287" t="str">
-        <v>TDP150MirChudes</v>
+        <v>TDP150Milashki3</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -4422,7 +4422,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B288" t="str">
-        <v>TDP150MorskieObitateli</v>
+        <v>TDP150MirChudes</v>
       </c>
       <c r="C288" t="str">
         <v/>
@@ -4436,13 +4436,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B289" t="str">
-        <v>TDP150MoyaZaika</v>
+        <v>TDP150MorskieObitateli</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290">
@@ -4450,7 +4450,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B290" t="str">
-        <v>TDP150Neon</v>
+        <v>TDP150MoyaZaika</v>
       </c>
       <c r="C290" t="str">
         <v/>
@@ -4464,13 +4464,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B291" t="str">
-        <v>TDP150NochnieFonariki</v>
+        <v>TDP150Neon</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -4478,7 +4478,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B292" t="str">
-        <v>TDP150Ocean</v>
+        <v>TDP150NochnieFonariki</v>
       </c>
       <c r="C292" t="str">
         <v/>
@@ -4492,7 +4492,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B293" t="str">
-        <v>TDP150Otbelka</v>
+        <v>TDP150Ocean</v>
       </c>
       <c r="C293" t="str">
         <v/>
@@ -4506,13 +4506,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B294" t="str">
-        <v>TDP150OtVinta</v>
+        <v>TDP150Otbelka</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -4520,7 +4520,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B295" t="str">
-        <v>TDP150Pehotinec</v>
+        <v>TDP150OtVinta</v>
       </c>
       <c r="C295" t="str">
         <v/>
@@ -4534,7 +4534,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B296" t="str">
-        <v>TDP150Pingvie</v>
+        <v>TDP150Pehotinec</v>
       </c>
       <c r="C296" t="str">
         <v/>
@@ -4548,13 +4548,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B297" t="str">
-        <v>TDP150Polet</v>
+        <v>TDP150Pingvie</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298">
@@ -4562,7 +4562,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B298" t="str">
-        <v>TDP150Polosatiki</v>
+        <v>TDP150Polet</v>
       </c>
       <c r="C298" t="str">
         <v/>
@@ -4576,13 +4576,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B299" t="str">
-        <v>TDP150Princessa</v>
+        <v>TDP150Polosatiki</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -4590,13 +4590,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B300" t="str">
-        <v>TDP150Retro</v>
+        <v>TDP150Princessa</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -4604,7 +4604,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B301" t="str">
-        <v>TDP150Romantica</v>
+        <v>TDP150Retro</v>
       </c>
       <c r="C301" t="str">
         <v/>
@@ -4618,13 +4618,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B302" t="str">
-        <v>TDP150Skorost</v>
+        <v>TDP150Romantica</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -4632,7 +4632,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B303" t="str">
-        <v>TDP150SladkihSnov</v>
+        <v>TDP150Skorost</v>
       </c>
       <c r="C303" t="str">
         <v/>
@@ -4646,7 +4646,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B304" t="str">
-        <v>TDP150SonyaKOMP</v>
+        <v>TDP150SladkihSnov</v>
       </c>
       <c r="C304" t="str">
         <v/>
@@ -4660,7 +4660,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B305" t="str">
-        <v>TDP150SonyaOSNOV</v>
+        <v>TDP150SonyaKOMP</v>
       </c>
       <c r="C305" t="str">
         <v/>
@@ -4674,7 +4674,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B306" t="str">
-        <v>TDP150SovyataKOMP</v>
+        <v>TDP150SonyaOSNOV</v>
       </c>
       <c r="C306" t="str">
         <v/>
@@ -4688,7 +4688,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B307" t="str">
-        <v>TDP150Sport2</v>
+        <v>TDP150SovyataKOMP</v>
       </c>
       <c r="C307" t="str">
         <v/>
@@ -4702,7 +4702,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B308" t="str">
-        <v>TDP150StreetArt</v>
+        <v>TDP150Sport2</v>
       </c>
       <c r="C308" t="str">
         <v/>
@@ -4716,13 +4716,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B309" t="str">
-        <v>TDP150StreetRace</v>
+        <v>TDP150StreetArt</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -4730,13 +4730,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B310" t="str">
-        <v>TDP150Sumerki</v>
+        <v>TDP150StreetRace</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -4744,7 +4744,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B311" t="str">
-        <v>TDP150SuperLady</v>
+        <v>TDP150Sumerki</v>
       </c>
       <c r="C311" t="str">
         <v/>
@@ -4758,7 +4758,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B312" t="str">
-        <v>TDP150SvetliyAngel</v>
+        <v>TDP150SuperLady</v>
       </c>
       <c r="C312" t="str">
         <v/>
@@ -4772,7 +4772,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B313" t="str">
-        <v>TDP150Tank</v>
+        <v>TDP150SvetliyAngel</v>
       </c>
       <c r="C313" t="str">
         <v/>
@@ -4786,7 +4786,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B314" t="str">
-        <v>TDP150Tirex</v>
+        <v>TDP150Tank</v>
       </c>
       <c r="C314" t="str">
         <v/>
@@ -4800,13 +4800,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B315" t="str">
-        <v>TDP150TownHouse</v>
+        <v>TDP150Tirex</v>
       </c>
       <c r="C315" t="str">
         <v/>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -4814,13 +4814,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B316" t="str">
-        <v>TDP150TsvetnieSni</v>
+        <v>TDP150TownHouse</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -4828,13 +4828,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B317" t="str">
-        <v>TDP150Ulibka</v>
+        <v>TDP150TsvetnieSni</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318">
@@ -4842,13 +4842,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B318" t="str">
-        <v>TDP150Ultra</v>
+        <v>TDP150Ulibka</v>
       </c>
       <c r="C318" t="str">
         <v/>
       </c>
       <c r="D318">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -4856,13 +4856,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B319" t="str">
-        <v>TDP150VanillaSkyCOMP</v>
+        <v>TDP150Ultra</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -4870,7 +4870,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B320" t="str">
-        <v>TDP150VanillaSkyOSN</v>
+        <v>TDP150VanillaSkyCOMP</v>
       </c>
       <c r="C320" t="str">
         <v/>
@@ -4884,13 +4884,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B321" t="str">
-        <v>TDP150Volshebnici</v>
+        <v>TDP150VanillaSkyOSN</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322">
@@ -4898,7 +4898,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B322" t="str">
-        <v>TDP150Zayushki</v>
+        <v>TDP150Volshebnici</v>
       </c>
       <c r="C322" t="str">
         <v/>
@@ -4912,7 +4912,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B323" t="str">
-        <v>TDP150ZvezdnayaPil</v>
+        <v>TDP150Zayushki</v>
       </c>
       <c r="C323" t="str">
         <v/>
@@ -4926,13 +4926,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B324" t="str">
-        <v>TDP150ZvezdnoeNebo</v>
+        <v>TDP150ZvezdnayaPil</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -4940,13 +4940,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B325" t="str">
-        <v>TDP150ZvezdochkaCOMP</v>
+        <v>TDP150ZvezdnoeNebo</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -4954,13 +4954,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B326" t="str">
-        <v>TDPPKOchkiCOMP1</v>
+        <v>TDP150ZvezdochkaCOMP</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -4968,7 +4968,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B327" t="str">
-        <v>TDPPKPolnochOSN1</v>
+        <v>TDPPKOchkiCOMP1</v>
       </c>
       <c r="C327" t="str">
         <v/>
@@ -4982,7 +4982,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B328" t="str">
-        <v>TDPPKPinkFlamingoOSN1</v>
+        <v>TDPPKPolnochOSN1</v>
       </c>
       <c r="C328" t="str">
         <v/>
@@ -4996,7 +4996,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B329" t="str">
-        <v>TDPPKZacharovanFlowerOSN1</v>
+        <v>TDPPKPinkFlamingoOSN1</v>
       </c>
       <c r="C329" t="str">
         <v/>
@@ -5010,13 +5010,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B330" t="str">
-        <v>TDPPKBananasOSN1</v>
+        <v>TDPPKZacharovanFlowerOSN1</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -5024,7 +5024,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B331" t="str">
-        <v>TDPPKObnimashkiOSN1</v>
+        <v>TDPPKBananasOSN1</v>
       </c>
       <c r="C331" t="str">
         <v/>
@@ -5038,13 +5038,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B332" t="str">
-        <v>TDPPKPassiaOSN1</v>
+        <v>TDPPKObnimashkiOSN1</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333">
@@ -5052,13 +5052,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B333" t="str">
-        <v>TDPPKKawaiCOMP1</v>
+        <v>TDPPKPassiaOSN1</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -5066,7 +5066,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B334" t="str">
-        <v>TDPPKFelixCOMP1</v>
+        <v>TDPPKKawaiCOMP1</v>
       </c>
       <c r="C334" t="str">
         <v/>
@@ -5080,13 +5080,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B335" t="str">
-        <v>TDPPKBotanicCOMP1</v>
+        <v>TDPPKFelixCOMP1</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336">
@@ -5094,7 +5094,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B336" t="str">
-        <v>TDPPKTvorchestvoCOMP1</v>
+        <v>TDPPKBotanicCOMP1</v>
       </c>
       <c r="C336" t="str">
         <v/>
@@ -5108,7 +5108,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B337" t="str">
-        <v>TDPPKCharlotteOSN2</v>
+        <v>TDPPKTvorchestvoCOMP1</v>
       </c>
       <c r="C337" t="str">
         <v/>
@@ -5122,13 +5122,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B338" t="str">
-        <v>TDPPKHorizontOSN1</v>
+        <v>TDPPKCharlotteOSN2</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -5136,13 +5136,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B339" t="str">
-        <v>TDPPKMissandeyaOSN1</v>
+        <v>TDPPKHorizontOSN1</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340">
@@ -5150,7 +5150,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B340" t="str">
-        <v>TDPPKProzrachVozdOSN1</v>
+        <v>TDPPKMissandeyaOSN1</v>
       </c>
       <c r="C340" t="str">
         <v/>
@@ -5164,13 +5164,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B341" t="str">
-        <v>TDPPKKorgiOSN1</v>
+        <v>TDPPKProzrachVozdOSN1</v>
       </c>
       <c r="C341" t="str">
         <v/>
       </c>
       <c r="D341">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -5178,7 +5178,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B342" t="str">
-        <v>TDPPKBotanicaOSN1</v>
+        <v>TDPPKKorgiOSN1</v>
       </c>
       <c r="C342" t="str">
         <v/>
@@ -5192,7 +5192,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B343" t="str">
-        <v>TDPPKFelixOSN1</v>
+        <v>TDPPKBotanicaOSN1</v>
       </c>
       <c r="C343" t="str">
         <v/>
@@ -5206,13 +5206,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B344" t="str">
-        <v>TDPPKPlavnieLiniiOSN1</v>
+        <v>TDPPKFelixOSN1</v>
       </c>
       <c r="C344" t="str">
         <v/>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -5220,7 +5220,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B345" t="str">
-        <v>TDPPKOrionOSN4</v>
+        <v>TDPPKPlavnieLiniiOSN1</v>
       </c>
       <c r="C345" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B346" t="str">
-        <v>TDPPKMissandeyaCOMP1</v>
+        <v>TDPPKOrionOSN4</v>
       </c>
       <c r="C346" t="str">
         <v/>
@@ -5248,7 +5248,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B347" t="str">
-        <v>TDPPKTvorchestvoOSN1</v>
+        <v>TDPPKMissandeyaCOMP1</v>
       </c>
       <c r="C347" t="str">
         <v/>
@@ -5262,7 +5262,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B348" t="str">
-        <v>TDPPKKorgiCOMP1</v>
+        <v>TDPPKTvorchestvoOSN1</v>
       </c>
       <c r="C348" t="str">
         <v/>
@@ -5276,13 +5276,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B349" t="str">
-        <v>TDPPKKawaiOSN1</v>
+        <v>TDPPKKorgiCOMP1</v>
       </c>
       <c r="C349" t="str">
         <v/>
       </c>
       <c r="D349">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -5290,7 +5290,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B350" t="str">
-        <v>TV-Tigers1-195x165</v>
+        <v>TDPPKKawaiOSN1</v>
       </c>
       <c r="C350" t="str">
         <v/>
@@ -5304,7 +5304,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B351" t="str">
-        <v>TV-Laguna1-195x165</v>
+        <v>TV-Tigers1-195x165</v>
       </c>
       <c r="C351" t="str">
         <v/>
@@ -5318,7 +5318,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B352" t="str">
-        <v>TV-Cherepashki1-195x165</v>
+        <v>TV-Laguna1-195x165</v>
       </c>
       <c r="C352" t="str">
         <v/>
@@ -5332,7 +5332,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B353" t="str">
-        <v>TV-Nektar1-195x165</v>
+        <v>TV-Cherepashki1-195x165</v>
       </c>
       <c r="C353" t="str">
         <v/>
@@ -5346,13 +5346,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B354" t="str">
-        <v>TV-NejniyDen1-195x165</v>
+        <v>TV-Nektar1-195x165</v>
       </c>
       <c r="C354" t="str">
         <v/>
       </c>
       <c r="D354">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -5360,7 +5360,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B355" t="str">
-        <v>TV-LetnNoch1-195x165</v>
+        <v>TV-NejniyDen1-195x165</v>
       </c>
       <c r="C355" t="str">
         <v/>
@@ -5374,13 +5374,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B356" t="str">
-        <v>TV-SpelieFrukti1-195x165</v>
+        <v>TV-LetnNoch1-195x165</v>
       </c>
       <c r="C356" t="str">
         <v/>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357">
@@ -5388,13 +5388,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B357" t="str">
-        <v>TV-Ailyn1-195x165</v>
+        <v>TV-SpelieFrukti1-195x165</v>
       </c>
       <c r="C357" t="str">
         <v/>
       </c>
       <c r="D357">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -5402,7 +5402,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B358" t="str">
-        <v>TV-Pletenie2-195x165</v>
+        <v>TV-Ailyn1-195x165</v>
       </c>
       <c r="C358" t="str">
         <v/>
@@ -5416,7 +5416,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B359" t="str">
-        <v>TV-NejnoeUtro1-195x165</v>
+        <v>TV-Pletenie2-195x165</v>
       </c>
       <c r="C359" t="str">
         <v/>
@@ -5430,7 +5430,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B360" t="str">
-        <v>TV-OvoshKorzin1-195x165</v>
+        <v>TV-NejnoeUtro1-195x165</v>
       </c>
       <c r="C360" t="str">
         <v/>
@@ -5444,7 +5444,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B361" t="str">
-        <v>TV-KitayPeyzazh1-195x165</v>
+        <v>TV-OvoshKorzin1-195x165</v>
       </c>
       <c r="C361" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B362" t="str">
-        <v>TV-Ailyn2-195x165</v>
+        <v>TV-KitayPeyzazh1-195x165</v>
       </c>
       <c r="C362" t="str">
         <v/>
@@ -5472,7 +5472,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B363" t="str">
-        <v>TV-Asia1-195x165</v>
+        <v>TV-Ailyn2-195x165</v>
       </c>
       <c r="C363" t="str">
         <v/>
@@ -5486,7 +5486,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B364" t="str">
-        <v>TV-Kolyadki1-195x165</v>
+        <v>TV-Asia1-195x165</v>
       </c>
       <c r="C364" t="str">
         <v/>
@@ -5500,7 +5500,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B365" t="str">
-        <v>TV-Elochka1-195x165</v>
+        <v>TV-Kolyadki1-195x165</v>
       </c>
       <c r="C365" t="str">
         <v/>
@@ -5514,13 +5514,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B366" t="str">
-        <v>TV-LimonKorzinka1-195x165</v>
+        <v>TV-Elochka1-195x165</v>
       </c>
       <c r="C366" t="str">
         <v/>
       </c>
       <c r="D366">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367">
@@ -5528,13 +5528,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B367" t="str">
-        <v>TV-Elis1-195x165</v>
+        <v>TV-LimonKorzinka1-195x165</v>
       </c>
       <c r="C367" t="str">
         <v/>
       </c>
       <c r="D367">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -5542,7 +5542,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B368" t="str">
-        <v>TV-EchoVesni1-195x165</v>
+        <v>TV-Elis1-195x165</v>
       </c>
       <c r="C368" t="str">
         <v/>
@@ -5556,7 +5556,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B369" t="str">
-        <v>TV-Hutoryanka1-195x165</v>
+        <v>TV-EchoVesni1-195x165</v>
       </c>
       <c r="C369" t="str">
         <v/>
@@ -5570,13 +5570,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B370" t="str">
-        <v>TV-VesenMelody1-195x165</v>
+        <v>TV-Hutoryanka1-195x165</v>
       </c>
       <c r="C370" t="str">
         <v/>
       </c>
       <c r="D370">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371">
@@ -5584,7 +5584,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B371" t="str">
-        <v>TV-PodCvetomRozi1-195x165</v>
+        <v>TV-VesenMelody1-195x165</v>
       </c>
       <c r="C371" t="str">
         <v/>
@@ -5598,7 +5598,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B372" t="str">
-        <v>TV-Lavanda1-195x165</v>
+        <v>TV-PodCvetomRozi1-195x165</v>
       </c>
       <c r="C372" t="str">
         <v/>
@@ -5612,13 +5612,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B373" t="str">
-        <v>TV-SlegkimParom1-195x165</v>
+        <v>TV-Lavanda1-195x165</v>
       </c>
       <c r="C373" t="str">
         <v/>
       </c>
       <c r="D373">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -5626,7 +5626,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B374" t="str">
-        <v>TV-Mayolika1-195x165</v>
+        <v>TV-SlegkimParom1-195x165</v>
       </c>
       <c r="C374" t="str">
         <v/>
@@ -5640,7 +5640,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B375" t="str">
-        <v>TV-Tropicana1-195x165</v>
+        <v>TV-Mayolika1-195x165</v>
       </c>
       <c r="C375" t="str">
         <v/>
@@ -5654,13 +5654,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B376" t="str">
-        <v>TV-Kolyadki2-195x165</v>
+        <v>TV-Tropicana1-195x165</v>
       </c>
       <c r="C376" t="str">
         <v/>
       </c>
       <c r="D376">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
@@ -5668,13 +5668,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B377" t="str">
-        <v>TV-LegkiyLepestok2-195x165</v>
+        <v>TV-Kolyadki2-195x165</v>
       </c>
       <c r="C377" t="str">
         <v/>
       </c>
       <c r="D377">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -5682,13 +5682,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B378" t="str">
-        <v>TDPPKAllure1KOMP</v>
+        <v>TV-LegkiyLepestok2-195x165</v>
       </c>
       <c r="C378" t="str">
         <v/>
       </c>
       <c r="D378">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379">
@@ -5696,13 +5696,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B379" t="str">
-        <v>TDPPKAllure1OSN</v>
+        <v>TDPPKAllure1KOMP</v>
       </c>
       <c r="C379" t="str">
         <v/>
       </c>
       <c r="D379">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -5710,7 +5710,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B380" t="str">
-        <v>TDPPKAzul1KOMP</v>
+        <v>TDPPKAllure1OSN</v>
       </c>
       <c r="C380" t="str">
         <v/>
@@ -5724,13 +5724,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B381" t="str">
-        <v>TDPPKBelkanto6OSN</v>
+        <v>TDPPKAzul1KOMP</v>
       </c>
       <c r="C381" t="str">
         <v/>
       </c>
       <c r="D381">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382">
@@ -5738,7 +5738,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B382" t="str">
-        <v>TDPPKBelosnejCvetok1OSN</v>
+        <v>TDPPKBelkanto6OSN</v>
       </c>
       <c r="C382" t="str">
         <v/>
@@ -5752,13 +5752,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B383" t="str">
-        <v>TDPPKBriena1OSN</v>
+        <v>TDPPKBelosnejCvetok1OSN</v>
       </c>
       <c r="C383" t="str">
         <v/>
       </c>
       <c r="D383">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -5766,13 +5766,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B384" t="str">
-        <v>TDPPKEdem1OSN125</v>
+        <v>TDPPKBriena1OSN</v>
       </c>
       <c r="C384" t="str">
         <v/>
       </c>
       <c r="D384">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -5780,13 +5780,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B385" t="str">
-        <v>TDPPKEmotsii1KOMP</v>
+        <v>TDPPKEdem1OSN125</v>
       </c>
       <c r="C385" t="str">
         <v/>
       </c>
       <c r="D385">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386">
@@ -5794,7 +5794,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B386" t="str">
-        <v>TDPPKEmotsii1OSN</v>
+        <v>TDPPKEmotsii1KOMP</v>
       </c>
       <c r="C386" t="str">
         <v/>
@@ -5808,7 +5808,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B387" t="str">
-        <v>TDPPKErnesto1KOMP</v>
+        <v>TDPPKEmotsii1OSN</v>
       </c>
       <c r="C387" t="str">
         <v/>
@@ -5822,7 +5822,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B388" t="str">
-        <v>TDPPKErnesto1OSN</v>
+        <v>TDPPKErnesto1KOMP</v>
       </c>
       <c r="C388" t="str">
         <v/>
@@ -5836,13 +5836,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B389" t="str">
-        <v>TDPPKEsoterica1KOMP</v>
+        <v>TDPPKErnesto1OSN</v>
       </c>
       <c r="C389" t="str">
         <v/>
       </c>
       <c r="D389">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -5850,13 +5850,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B390" t="str">
-        <v>TDPPKFlowerTriumf1KOMP</v>
+        <v>TDPPKEsoterica1KOMP</v>
       </c>
       <c r="C390" t="str">
         <v/>
       </c>
       <c r="D390">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -5864,13 +5864,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B391" t="str">
-        <v>TDPPKFlowerTriumf1OSN</v>
+        <v>TDPPKFlowerTriumf1KOMP</v>
       </c>
       <c r="C391" t="str">
         <v/>
       </c>
       <c r="D391">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -5878,13 +5878,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B392" t="str">
-        <v>TDPPKFreilina1OSN</v>
+        <v>TDPPKFlowerTriumf1OSN</v>
       </c>
       <c r="C392" t="str">
         <v/>
       </c>
       <c r="D392">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -5892,13 +5892,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B393" t="str">
-        <v>TDPPKGavana1OSN</v>
+        <v>TDPPKFreilina1OSN</v>
       </c>
       <c r="C393" t="str">
         <v/>
       </c>
       <c r="D393">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -5906,13 +5906,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B394" t="str">
-        <v>TDPPKGossypium1OSN</v>
+        <v>TDPPKGavana1OSN</v>
       </c>
       <c r="C394" t="str">
         <v/>
       </c>
       <c r="D394">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
@@ -5920,13 +5920,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B395" t="str">
-        <v>TDPPKKaribi1OSN</v>
+        <v>TDPPKGossypium1OSN</v>
       </c>
       <c r="C395" t="str">
         <v/>
       </c>
       <c r="D395">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -5934,13 +5934,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B396" t="str">
-        <v>TDPPKKeniya4OSN</v>
+        <v>TDPPKKaribi1OSN</v>
       </c>
       <c r="C396" t="str">
         <v/>
       </c>
       <c r="D396">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -5948,7 +5948,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B397" t="str">
-        <v>TDPPKKolorit1OSN</v>
+        <v>TDPPKKeniya4OSN</v>
       </c>
       <c r="C397" t="str">
         <v/>
@@ -5962,13 +5962,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B398" t="str">
-        <v>TDPPKLetniiZnoi1OSN</v>
+        <v>TDPPKKolorit1OSN</v>
       </c>
       <c r="C398" t="str">
         <v/>
       </c>
       <c r="D398">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -5976,7 +5976,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B399" t="str">
-        <v>TDPPKLike3OSN</v>
+        <v>TDPPKLetniiZnoi1OSN</v>
       </c>
       <c r="C399" t="str">
         <v/>
@@ -5990,13 +5990,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B400" t="str">
-        <v>TDPPKMiliiMishka1KOMP</v>
+        <v>TDPPKLike3OSN</v>
       </c>
       <c r="C400" t="str">
         <v/>
       </c>
       <c r="D400">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -6004,7 +6004,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B401" t="str">
-        <v>TDPPKMonohrom15OSN</v>
+        <v>TDPPKMiliiMishka1KOMP</v>
       </c>
       <c r="C401" t="str">
         <v/>
@@ -6018,13 +6018,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B402" t="str">
-        <v>TDPPKNochnoiPolet1OSN</v>
+        <v>TDPPKMonohrom15OSN</v>
       </c>
       <c r="C402" t="str">
         <v/>
       </c>
       <c r="D402">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -6032,7 +6032,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B403" t="str">
-        <v>TDPPKOcherk1OSN</v>
+        <v>TDPPKNochnoiPolet1OSN</v>
       </c>
       <c r="C403" t="str">
         <v/>
@@ -6046,13 +6046,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B404" t="str">
-        <v>TDPPKOchki1OSN</v>
+        <v>TDPPKOcherk1OSN</v>
       </c>
       <c r="C404" t="str">
         <v/>
       </c>
       <c r="D404">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -6060,13 +6060,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B405" t="str">
-        <v>TDPPKOdaNejnosti1OSN125</v>
+        <v>TDPPKOchki1OSN</v>
       </c>
       <c r="C405" t="str">
         <v/>
       </c>
       <c r="D405">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="406">
@@ -6074,7 +6074,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B406" t="str">
-        <v>TDPPKOpavshayaListva1OSN</v>
+        <v>TDPPKOdaNejnosti1OSN125</v>
       </c>
       <c r="C406" t="str">
         <v/>
@@ -6088,13 +6088,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B407" t="str">
-        <v>TDPPKOtblesk1OSN</v>
+        <v>TDPPKOpavshayaListva1OSN</v>
       </c>
       <c r="C407" t="str">
         <v/>
       </c>
       <c r="D407">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -6102,7 +6102,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B408" t="str">
-        <v>TDPPKPalitraRadosti1OSN</v>
+        <v>TDPPKOtblesk1OSN</v>
       </c>
       <c r="C408" t="str">
         <v/>
@@ -6116,7 +6116,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B409" t="str">
-        <v>TDPPKPeisli16OSN</v>
+        <v>TDPPKPalitraRadosti1OSN</v>
       </c>
       <c r="C409" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B410" t="str">
-        <v>TDPPKPervoeSvidanie1OSN</v>
+        <v>TDPPKPeisli16OSN</v>
       </c>
       <c r="C410" t="str">
         <v/>
       </c>
       <c r="D410">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -6144,7 +6144,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B411" t="str">
-        <v>TDPPKPodvodTsarstvo1KOMP</v>
+        <v>TDPPKPervoeSvidanie1OSN</v>
       </c>
       <c r="C411" t="str">
         <v/>
@@ -6158,7 +6158,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B412" t="str">
-        <v>TDPPKPodvodTsarstvo1OSN</v>
+        <v>TDPPKPodvodTsarstvo1KOMP</v>
       </c>
       <c r="C412" t="str">
         <v/>
@@ -6172,7 +6172,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B413" t="str">
-        <v>TDPPKPotok1OSN</v>
+        <v>TDPPKPodvodTsarstvo1OSN</v>
       </c>
       <c r="C413" t="str">
         <v/>
@@ -6186,13 +6186,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B414" t="str">
-        <v>TDPPKSchastlivieDni1OSN125</v>
+        <v>TDPPKPotok1OSN</v>
       </c>
       <c r="C414" t="str">
         <v/>
       </c>
       <c r="D414">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415">
@@ -6200,7 +6200,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B415" t="str">
-        <v>TDPPKSonAfroditi1OSN</v>
+        <v>TDPPKSchastlivieDni1OSN125</v>
       </c>
       <c r="C415" t="str">
         <v/>
@@ -6214,13 +6214,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B416" t="str">
-        <v>TDPPKSozidanie1OSN</v>
+        <v>TDPPKSonAfroditi1OSN</v>
       </c>
       <c r="C416" t="str">
         <v/>
       </c>
       <c r="D416">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -6228,7 +6228,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B417" t="str">
-        <v>TDPPKTainstvSad1OSN</v>
+        <v>TDPPKSozidanie1OSN</v>
       </c>
       <c r="C417" t="str">
         <v/>
@@ -6242,13 +6242,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B418" t="str">
-        <v>TDPPKVesenSkazka1OSN</v>
+        <v>TDPPKTainstvSad1OSN</v>
       </c>
       <c r="C418" t="str">
         <v/>
       </c>
       <c r="D418">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -6256,13 +6256,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B419" t="str">
-        <v>TDPPKVesennPolyana1OSN</v>
+        <v>TDPPKVesenSkazka1OSN</v>
       </c>
       <c r="C419" t="str">
         <v/>
       </c>
       <c r="D419">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -6270,13 +6270,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B420" t="str">
-        <v>TDPPKViola1OSN</v>
+        <v>TDPPKVesennPolyana1OSN</v>
       </c>
       <c r="C420" t="str">
         <v/>
       </c>
       <c r="D420">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -6284,7 +6284,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B421" t="str">
-        <v>TDPPKViola2OSN</v>
+        <v>TDPPKViola1OSN</v>
       </c>
       <c r="C421" t="str">
         <v/>
@@ -6298,7 +6298,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B422" t="str">
-        <v>TDPPKVishnya1OSN</v>
+        <v>TDPPKViola2OSN</v>
       </c>
       <c r="C422" t="str">
         <v/>
@@ -6312,13 +6312,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B423" t="str">
-        <v>TDPPKVitragi1KOMP125</v>
+        <v>TDPPKVishnya1OSN</v>
       </c>
       <c r="C423" t="str">
         <v/>
       </c>
       <c r="D423">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -6326,13 +6326,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B424" t="str">
-        <v>TDPPKVlublenCorgi1KOMP</v>
+        <v>TDPPKVitragi1KOMP125</v>
       </c>
       <c r="C424" t="str">
         <v/>
       </c>
       <c r="D424">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="425">
@@ -6340,13 +6340,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B425" t="str">
-        <v>TDPPKVlublenCorgi1OSN</v>
+        <v>TDPPKVlublenCorgi1KOMP</v>
       </c>
       <c r="C425" t="str">
         <v/>
       </c>
       <c r="D425">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -6354,13 +6354,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B426" t="str">
-        <v>TDPPKVostochnayaSkazka1OSN</v>
+        <v>TDPPKVlublenCorgi1OSN</v>
       </c>
       <c r="C426" t="str">
         <v/>
       </c>
       <c r="D426">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427">
@@ -6368,13 +6368,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B427" t="str">
-        <v>TDPPKYlibnis1KOMP</v>
+        <v>TDPPKVostochnayaSkazka1OSN</v>
       </c>
       <c r="C427" t="str">
         <v/>
       </c>
       <c r="D427">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -6382,7 +6382,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B428" t="str">
-        <v>TDPPKYlibnis1OSN</v>
+        <v>TDPPKYlibnis1KOMP</v>
       </c>
       <c r="C428" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B429" t="str">
-        <v>TDM-greyViolet</v>
+        <v>TDPPKYlibnis1OSN</v>
       </c>
       <c r="C429" t="str">
         <v/>
@@ -6410,7 +6410,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B430" t="str">
-        <v>TDM-lightBlue</v>
+        <v>TDM-greyViolet</v>
       </c>
       <c r="C430" t="str">
         <v/>
@@ -6424,13 +6424,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B431" t="str">
-        <v>TDM-pink</v>
+        <v>TDM-lightBlue</v>
       </c>
       <c r="C431" t="str">
         <v/>
       </c>
       <c r="D431">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432">
@@ -6438,13 +6438,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B432" t="str">
-        <v>TDPPKAlfredo1OSN</v>
+        <v>TDM-pink</v>
       </c>
       <c r="C432" t="str">
         <v/>
       </c>
       <c r="D432">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -6452,13 +6452,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B433" t="str">
-        <v>TDPPKArbyzi1KOMP</v>
+        <v>TDPPKAlfredo1OSN</v>
       </c>
       <c r="C433" t="str">
         <v/>
       </c>
       <c r="D433">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -6466,7 +6466,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B434" t="str">
-        <v>TDPPKArbyzi1OSN</v>
+        <v>TDPPKArbyzi1KOMP</v>
       </c>
       <c r="C434" t="str">
         <v/>
@@ -6480,7 +6480,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B435" t="str">
-        <v>TDPPKArno1OSN</v>
+        <v>TDPPKArbyzi1OSN</v>
       </c>
       <c r="C435" t="str">
         <v/>
@@ -6494,13 +6494,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B436" t="str">
-        <v>TDPPKAura1OSN</v>
+        <v>TDPPKArno1OSN</v>
       </c>
       <c r="C436" t="str">
         <v/>
       </c>
       <c r="D436">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437">
@@ -6508,13 +6508,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B437" t="str">
-        <v>TDPPKAureliya1KOMP</v>
+        <v>TDPPKAura1OSN</v>
       </c>
       <c r="C437" t="str">
         <v/>
       </c>
       <c r="D437">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -6522,7 +6522,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B438" t="str">
-        <v>TDPPKAvokado1KOMP</v>
+        <v>TDPPKAureliya1KOMP</v>
       </c>
       <c r="C438" t="str">
         <v/>
@@ -6536,13 +6536,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B439" t="str">
-        <v>TDPPKBalCvetov3KOMP</v>
+        <v>TDPPKAvokado1KOMP</v>
       </c>
       <c r="C439" t="str">
         <v/>
       </c>
       <c r="D439">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
@@ -6550,13 +6550,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B440" t="str">
-        <v>TDPPKBalladaOLubvi1OSN</v>
+        <v>TDPPKBalCvetov3KOMP</v>
       </c>
       <c r="C440" t="str">
         <v/>
       </c>
       <c r="D440">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -6564,7 +6564,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B441" t="str">
-        <v>TDPPKBeliiSad1KOMP</v>
+        <v>TDPPKBalladaOLubvi1OSN</v>
       </c>
       <c r="C441" t="str">
         <v/>
@@ -6578,13 +6578,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B442" t="str">
-        <v>TDPPKBeliiTigr1OSN</v>
+        <v>TDPPKBeliiSad1KOMP</v>
       </c>
       <c r="C442" t="str">
         <v/>
       </c>
       <c r="D442">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -6592,7 +6592,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B443" t="str">
-        <v>TDPPKBlagoyhanie1OSN</v>
+        <v>TDPPKBeliiTigr1OSN</v>
       </c>
       <c r="C443" t="str">
         <v/>
@@ -6606,7 +6606,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B444" t="str">
-        <v>TDPPKCharodeyka1OSN</v>
+        <v>TDPPKBlagoyhanie1OSN</v>
       </c>
       <c r="C444" t="str">
         <v/>
@@ -6620,7 +6620,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B445" t="str">
-        <v>TDPPKCvetushieMechti1OSN125</v>
+        <v>TDPPKCharodeyka1OSN</v>
       </c>
       <c r="C445" t="str">
         <v/>
@@ -6634,13 +6634,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B446" t="str">
-        <v>TDPPKDebut1OSN</v>
+        <v>TDPPKCvetushieMechti1OSN125</v>
       </c>
       <c r="C446" t="str">
         <v/>
       </c>
       <c r="D446">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -6648,13 +6648,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B447" t="str">
-        <v>TDPPKDilara1OSN</v>
+        <v>TDPPKDebut1OSN</v>
       </c>
       <c r="C447" t="str">
         <v/>
       </c>
       <c r="D447">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -6662,7 +6662,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B448" t="str">
-        <v>TDPPKDrakon1OSN</v>
+        <v>TDPPKDilara1OSN</v>
       </c>
       <c r="C448" t="str">
         <v/>
@@ -6676,13 +6676,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B449" t="str">
-        <v>TDPPKEco4KOMP</v>
+        <v>TDPPKDrakon1OSN</v>
       </c>
       <c r="C449" t="str">
         <v/>
       </c>
       <c r="D449">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -6690,7 +6690,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B450" t="str">
-        <v>TDPPKEco13OSN</v>
+        <v>TDPPKEco4KOMP</v>
       </c>
       <c r="C450" t="str">
         <v/>
@@ -6704,7 +6704,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B451" t="str">
-        <v>TDPPKEco15OSN</v>
+        <v>TDPPKEco13OSN</v>
       </c>
       <c r="C451" t="str">
         <v/>
@@ -6718,7 +6718,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B452" t="str">
-        <v>TDPPKElison1KOMP</v>
+        <v>TDPPKEco15OSN</v>
       </c>
       <c r="C452" t="str">
         <v/>
@@ -6732,13 +6732,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B453" t="str">
-        <v>TDPPKFrezii1OSN</v>
+        <v>TDPPKElison1KOMP</v>
       </c>
       <c r="C453" t="str">
         <v/>
       </c>
       <c r="D453">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -6746,7 +6746,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B454" t="str">
-        <v>TDPPKGerbarii1OSN</v>
+        <v>TDPPKFrezii1OSN</v>
       </c>
       <c r="C454" t="str">
         <v/>
@@ -6760,13 +6760,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B455" t="str">
-        <v>TDPPKGystav1OSN</v>
+        <v>TDPPKGerbarii1OSN</v>
       </c>
       <c r="C455" t="str">
         <v/>
       </c>
       <c r="D455">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="456">
@@ -6774,7 +6774,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B456" t="str">
-        <v>TDPPKIlluminaciya1OSN</v>
+        <v>TDPPKGystav1OSN</v>
       </c>
       <c r="C456" t="str">
         <v/>
@@ -6788,13 +6788,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B457" t="str">
-        <v>TDPPKInteres1KOMP</v>
+        <v>TDPPKIlluminaciya1OSN</v>
       </c>
       <c r="C457" t="str">
         <v/>
       </c>
       <c r="D457">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -6802,7 +6802,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B458" t="str">
-        <v>TDPPKInteres1OSN</v>
+        <v>TDPPKInteres1KOMP</v>
       </c>
       <c r="C458" t="str">
         <v/>
@@ -6816,7 +6816,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B459" t="str">
-        <v>TDPPKIskushenie1KOMP</v>
+        <v>TDPPKInteres1OSN</v>
       </c>
       <c r="C459" t="str">
         <v/>
@@ -6830,7 +6830,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B460" t="str">
-        <v>TDPPKKessi1KOMP</v>
+        <v>TDPPKIskushenie1KOMP</v>
       </c>
       <c r="C460" t="str">
         <v/>
@@ -6844,13 +6844,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B461" t="str">
-        <v>TDPPKKvartc1OSN</v>
+        <v>TDPPKKessi1KOMP</v>
       </c>
       <c r="C461" t="str">
         <v/>
       </c>
       <c r="D461">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="462">
@@ -6858,13 +6858,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B462" t="str">
-        <v>TDPPKListopad1OSN</v>
+        <v>TDPPKKvartc1OSN</v>
       </c>
       <c r="C462" t="str">
         <v/>
       </c>
       <c r="D462">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -6872,13 +6872,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B463" t="str">
-        <v>TDPPKMarsala1OSN</v>
+        <v>TDPPKListopad1OSN</v>
       </c>
       <c r="C463" t="str">
         <v/>
       </c>
       <c r="D463">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -6886,13 +6886,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B464" t="str">
-        <v>TDPPKMuzei1KOMP</v>
+        <v>TDPPKMarsala1OSN</v>
       </c>
       <c r="C464" t="str">
         <v/>
       </c>
       <c r="D464">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -6900,7 +6900,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B465" t="str">
-        <v>TDPPKNamaste1KOMP</v>
+        <v>TDPPKMuzei1KOMP</v>
       </c>
       <c r="C465" t="str">
         <v/>
@@ -6914,7 +6914,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B466" t="str">
-        <v>TDPPKNamaste1OSN</v>
+        <v>TDPPKNamaste1KOMP</v>
       </c>
       <c r="C466" t="str">
         <v/>
@@ -6928,13 +6928,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B467" t="str">
-        <v>TDPPKObitelLubvi1KOMP</v>
+        <v>TDPPKNamaste1OSN</v>
       </c>
       <c r="C467" t="str">
         <v/>
       </c>
       <c r="D467">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -6942,7 +6942,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B468" t="str">
-        <v>TDPPKOrion1OSN</v>
+        <v>TDPPKObitelLubvi1KOMP</v>
       </c>
       <c r="C468" t="str">
         <v/>
@@ -6956,7 +6956,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B469" t="str">
-        <v>TDPPKPishnayaSiren1KOMP</v>
+        <v>TDPPKOrion1OSN</v>
       </c>
       <c r="C469" t="str">
         <v/>
@@ -6970,7 +6970,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B470" t="str">
-        <v>TDPPKSiyanieNochi3OSN</v>
+        <v>TDPPKPishnayaSiren1KOMP</v>
       </c>
       <c r="C470" t="str">
         <v/>
@@ -6984,7 +6984,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B471" t="str">
-        <v>TDPPKSnejnoeSiyanie1OSN</v>
+        <v>TDPPKSiyanieNochi3OSN</v>
       </c>
       <c r="C471" t="str">
         <v/>
@@ -6998,13 +6998,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B472" t="str">
-        <v>TDPPKSolnechniePtici2OSN</v>
+        <v>TDPPKSnejnoeSiyanie1OSN</v>
       </c>
       <c r="C472" t="str">
         <v/>
       </c>
       <c r="D472">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -7012,7 +7012,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B473" t="str">
-        <v>TDPPKTekstura1OSN</v>
+        <v>TDPPKSolnechniePtici2OSN</v>
       </c>
       <c r="C473" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B474" t="str">
-        <v>TDPPKTown1OSN</v>
+        <v>TDPPKTekstura1OSN</v>
       </c>
       <c r="C474" t="str">
         <v/>
@@ -7040,7 +7040,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B475" t="str">
-        <v>TDPPKUrban2OSN</v>
+        <v>TDPPKTown1OSN</v>
       </c>
       <c r="C475" t="str">
         <v/>
@@ -7054,13 +7054,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B476" t="str">
-        <v>TDPPKVechernieGrezi1OSN</v>
+        <v>TDPPKUrban2OSN</v>
       </c>
       <c r="C476" t="str">
         <v/>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -7068,7 +7068,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B477" t="str">
-        <v>TDPPKVeselieDruzya1OSN</v>
+        <v>TDPPKVechernieGrezi1OSN</v>
       </c>
       <c r="C477" t="str">
         <v/>
@@ -7082,7 +7082,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B478" t="str">
-        <v>TDPPKViraj1KOMP</v>
+        <v>TDPPKVeselieDruzya1OSN</v>
       </c>
       <c r="C478" t="str">
         <v/>
@@ -7096,13 +7096,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B479" t="str">
-        <v>TDPPKVivian1OSN</v>
+        <v>TDPPKViraj1KOMP</v>
       </c>
       <c r="C479" t="str">
         <v/>
       </c>
       <c r="D479">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -7110,13 +7110,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B480" t="str">
-        <v>TDPPKVoVlastiKrasoti1OSN</v>
+        <v>TDPPKVivian1OSN</v>
       </c>
       <c r="C480" t="str">
         <v/>
       </c>
       <c r="D480">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -7124,7 +7124,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B481" t="str">
-        <v>TDPPKVpechatlenie1OSN</v>
+        <v>TDPPKVoVlastiKrasoti1OSN</v>
       </c>
       <c r="C481" t="str">
         <v/>
@@ -7138,13 +7138,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B482" t="str">
-        <v>TDPPKZazerkalie1OSN</v>
+        <v>TDPPKVpechatlenie1OSN</v>
       </c>
       <c r="C482" t="str">
         <v/>
       </c>
       <c r="D482">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -7152,13 +7152,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B483" t="str">
-        <v>TDSPK220MaikoOSN4</v>
+        <v>TDPPKZazerkalie1OSN</v>
       </c>
       <c r="C483" t="str">
         <v/>
       </c>
       <c r="D483">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="484">
@@ -7166,7 +7166,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B484" t="str">
-        <v>TDSPK220EtudKOMP5</v>
+        <v>TDSPK220MaikoOSN4</v>
       </c>
       <c r="C484" t="str">
         <v/>
@@ -7180,13 +7180,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B485" t="str">
-        <v>TDSPK220GoldDayOSN2</v>
+        <v>TDSPK220EtudKOMP5</v>
       </c>
       <c r="C485" t="str">
         <v/>
       </c>
       <c r="D485">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
@@ -7194,7 +7194,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B486" t="str">
-        <v>TDSPK220MonohromOSN13</v>
+        <v>TDSPK220GoldDayOSN2</v>
       </c>
       <c r="C486" t="str">
         <v/>
@@ -7208,7 +7208,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B487" t="str">
-        <v>TDSPK220ZabvenieKOMP2</v>
+        <v>TDSPK220MonohromOSN13</v>
       </c>
       <c r="C487" t="str">
         <v/>
@@ -7222,13 +7222,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B488" t="str">
-        <v>TDSPK220ZabvenieOSN2</v>
+        <v>TDSPK220ZabvenieKOMP2</v>
       </c>
       <c r="C488" t="str">
         <v/>
       </c>
       <c r="D488">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -7236,7 +7236,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B489" t="str">
-        <v>TDSPK235BelyyBuketKOMP2</v>
+        <v>TDSPK220ZabvenieOSN2</v>
       </c>
       <c r="C489" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B490" t="str">
-        <v>TDSPK235BelyyBuketOSN2</v>
+        <v>TDSPK235BelyyBuketKOMP2</v>
       </c>
       <c r="C490" t="str">
         <v/>
@@ -7264,7 +7264,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B491" t="str">
-        <v>TDSPK235DlinnayaNochKOMP2</v>
+        <v>TDSPK235BelyyBuketOSN2</v>
       </c>
       <c r="C491" t="str">
         <v/>
@@ -7278,7 +7278,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B492" t="str">
-        <v>TDSPK235DlinnayaNochOSN2</v>
+        <v>TDSPK235DlinnayaNochKOMP2</v>
       </c>
       <c r="C492" t="str">
         <v/>
@@ -7292,7 +7292,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B493" t="str">
-        <v>TDSPK235DzhinniKOMP2</v>
+        <v>TDSPK235DlinnayaNochOSN2</v>
       </c>
       <c r="C493" t="str">
         <v/>
@@ -7306,7 +7306,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B494" t="str">
-        <v>TDSPK235DzhinniOSN2</v>
+        <v>TDSPK235DzhinniKOMP2</v>
       </c>
       <c r="C494" t="str">
         <v/>
@@ -7320,7 +7320,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B495" t="str">
-        <v>TDSPK235EstellaOSN2</v>
+        <v>TDSPK235DzhinniOSN2</v>
       </c>
       <c r="C495" t="str">
         <v/>
@@ -7334,7 +7334,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B496" t="str">
-        <v>TDSPK235GoldenKOMP2</v>
+        <v>TDSPK235EstellaOSN2</v>
       </c>
       <c r="C496" t="str">
         <v/>
@@ -7348,7 +7348,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B497" t="str">
-        <v>TDSPK235LepestokKOMP2</v>
+        <v>TDSPK235GoldenKOMP2</v>
       </c>
       <c r="C497" t="str">
         <v/>
@@ -7362,7 +7362,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B498" t="str">
-        <v>TDSPK235LepestokOSN2</v>
+        <v>TDSPK235LepestokKOMP2</v>
       </c>
       <c r="C498" t="str">
         <v/>
@@ -7376,7 +7376,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B499" t="str">
-        <v>TDSPK235LuchSolntsaKOMP2</v>
+        <v>TDSPK235LepestokOSN2</v>
       </c>
       <c r="C499" t="str">
         <v/>
@@ -7390,13 +7390,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B500" t="str">
-        <v>TDSPK235LuchSolntsaOSN2</v>
+        <v>TDSPK235LuchSolntsaKOMP2</v>
       </c>
       <c r="C500" t="str">
         <v/>
       </c>
       <c r="D500">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -7404,7 +7404,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B501" t="str">
-        <v>TDSPK235MilagrosOSN2</v>
+        <v>TDSPK235LuchSolntsaOSN2</v>
       </c>
       <c r="C501" t="str">
         <v/>
@@ -7418,7 +7418,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B502" t="str">
-        <v>TDSPK235NinelKOMP6</v>
+        <v>TDSPK235MilagrosOSN2</v>
       </c>
       <c r="C502" t="str">
         <v/>
@@ -7432,7 +7432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B503" t="str">
-        <v>TDSPK235NinelKOMP8</v>
+        <v>TDSPK235NinelKOMP6</v>
       </c>
       <c r="C503" t="str">
         <v/>
@@ -7446,7 +7446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B504" t="str">
-        <v>TDSPK235PassazhKOMP2</v>
+        <v>TDSPK235NinelKOMP8</v>
       </c>
       <c r="C504" t="str">
         <v/>
@@ -7460,7 +7460,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B505" t="str">
-        <v>TDSPK235PassazhOSN2</v>
+        <v>TDSPK235PassazhKOMP2</v>
       </c>
       <c r="C505" t="str">
         <v/>
@@ -7474,7 +7474,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B506" t="str">
-        <v>TDSPK235PlenitelnayaGratsiyaKOMP2</v>
+        <v>TDSPK235PassazhOSN2</v>
       </c>
       <c r="C506" t="str">
         <v/>
@@ -7488,7 +7488,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B507" t="str">
-        <v>TDSPK235PlenitelnayaGratsiyaOSN2</v>
+        <v>TDSPK235PlenitelnayaGratsiyaKOMP2</v>
       </c>
       <c r="C507" t="str">
         <v/>
@@ -7502,7 +7502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B508" t="str">
-        <v>TDSPK235PoeziyaKrasotiOSN2</v>
+        <v>TDSPK235PlenitelnayaGratsiyaOSN2</v>
       </c>
       <c r="C508" t="str">
         <v/>
@@ -7516,7 +7516,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B509" t="str">
-        <v>TDSPK235RavnovesieKOMP2</v>
+        <v>TDSPK235PoeziyaKrasotiOSN2</v>
       </c>
       <c r="C509" t="str">
         <v/>
@@ -7530,7 +7530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B510" t="str">
-        <v>TDSPK235RavnovesieOSN2</v>
+        <v>TDSPK235RavnovesieKOMP2</v>
       </c>
       <c r="C510" t="str">
         <v/>
@@ -7544,7 +7544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B511" t="str">
-        <v>TDSPK235SimmetriyaOSN3</v>
+        <v>TDSPK235RavnovesieOSN2</v>
       </c>
       <c r="C511" t="str">
         <v/>
@@ -7558,7 +7558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B512" t="str">
-        <v>TDSPK235TisnenieOSN3</v>
+        <v>TDSPK235SimmetriyaOSN3</v>
       </c>
       <c r="C512" t="str">
         <v/>
@@ -7572,7 +7572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B513" t="str">
-        <v>TDSPK235TsvetochnyyLugKOMP2</v>
+        <v>TDSPK235TisnenieOSN3</v>
       </c>
       <c r="C513" t="str">
         <v/>
@@ -7586,7 +7586,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B514" t="str">
-        <v>TDSPK235TsvetochnyyLugOSN2</v>
+        <v>TDSPK235TsvetochnyyLugKOMP2</v>
       </c>
       <c r="C514" t="str">
         <v/>
@@ -7600,7 +7600,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B515" t="str">
-        <v>TDSPK235TsvetushchayaMelodiyaKOMP2</v>
+        <v>TDSPK235TsvetochnyyLugOSN2</v>
       </c>
       <c r="C515" t="str">
         <v/>
@@ -7614,7 +7614,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B516" t="str">
-        <v>TDSPK235TsvetushchayaMelodiyaOSN2</v>
+        <v>TDSPK235TsvetushchayaMelodiyaKOMP2</v>
       </c>
       <c r="C516" t="str">
         <v/>
@@ -7628,7 +7628,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B517" t="str">
-        <v>TDSPK235VzmakhKistiKOMP3</v>
+        <v>TDSPK235TsvetushchayaMelodiyaOSN2</v>
       </c>
       <c r="C517" t="str">
         <v/>
@@ -7642,7 +7642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B518" t="str">
-        <v>TDSPK235VzmakhKistiOSN3</v>
+        <v>TDSPK235VzmakhKistiKOMP3</v>
       </c>
       <c r="C518" t="str">
         <v/>
@@ -7656,7 +7656,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B519" t="str">
-        <v>TDSPK235YuventaOSN3</v>
+        <v>TDSPK235VzmakhKistiOSN3</v>
       </c>
       <c r="C519" t="str">
         <v/>
@@ -7670,7 +7670,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B520" t="str">
-        <v>TDSPK235ZolotoeSiyanieOSN2</v>
+        <v>TDSPK235YuventaOSN3</v>
       </c>
       <c r="C520" t="str">
         <v/>
@@ -7684,7 +7684,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B521" t="str">
-        <v>TDSPK235ZvezdnyySvetKOMP2</v>
+        <v>TDSPK235ZolotoeSiyanieOSN2</v>
       </c>
       <c r="C521" t="str">
         <v/>
@@ -7698,7 +7698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B522" t="str">
-        <v>TDSPK235ZvezdnyySvetOSN2</v>
+        <v>TDSPK235ZvezdnyySvetKOMP2</v>
       </c>
       <c r="C522" t="str">
         <v/>
@@ -7712,7 +7712,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B523" t="str">
-        <v>TDPPK235AkvaOSN1</v>
+        <v>TDSPK235ZvezdnyySvetOSN2</v>
       </c>
       <c r="C523" t="str">
         <v/>
@@ -7726,13 +7726,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B524" t="str">
-        <v>TDPPK235AnriKOMP1-125</v>
+        <v>TDPPK235AkvaOSN1</v>
       </c>
       <c r="C524" t="str">
         <v/>
       </c>
       <c r="D524">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -7740,13 +7740,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B525" t="str">
-        <v>TDPPK235Ar-dekoOSN1</v>
+        <v>TDPPK235AnriKOMP1-125</v>
       </c>
       <c r="C525" t="str">
         <v/>
       </c>
       <c r="D525">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
@@ -7754,7 +7754,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B526" t="str">
-        <v>TDPPK235BarelefOSN1</v>
+        <v>TDPPK235Ar-dekoOSN1</v>
       </c>
       <c r="C526" t="str">
         <v/>
@@ -7768,13 +7768,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B527" t="str">
-        <v>TDPPK235DlinnayaNochOSN1-125</v>
+        <v>TDPPK235BarelefOSN1</v>
       </c>
       <c r="C527" t="str">
         <v/>
       </c>
       <c r="D527">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="528">
@@ -7782,7 +7782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B528" t="str">
-        <v>TDPPK235DushaOSN1</v>
+        <v>TDPPK235DlinnayaNochOSN1-125</v>
       </c>
       <c r="C528" t="str">
         <v/>
@@ -7796,13 +7796,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B529" t="str">
-        <v>TDPPK235DzhinniKOMP1</v>
+        <v>TDPPK235DushaOSN1</v>
       </c>
       <c r="C529" t="str">
         <v/>
       </c>
       <c r="D529">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -7810,7 +7810,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B530" t="str">
-        <v>TDPPK235EstellaKOMP1</v>
+        <v>TDPPK235DzhinniKOMP1</v>
       </c>
       <c r="C530" t="str">
         <v/>
@@ -7824,13 +7824,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B531" t="str">
-        <v>TDPPK235EstellaOSN1</v>
+        <v>TDPPK235EstellaKOMP1</v>
       </c>
       <c r="C531" t="str">
         <v/>
       </c>
       <c r="D531">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -7838,7 +7838,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B532" t="str">
-        <v>TDPPK235FloristikaOSN1</v>
+        <v>TDPPK235EstellaOSN1</v>
       </c>
       <c r="C532" t="str">
         <v/>
@@ -7852,13 +7852,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B533" t="str">
-        <v>TDPPK235GarmoniyaChuvstvOSN1</v>
+        <v>TDPPK235FloristikaOSN1</v>
       </c>
       <c r="C533" t="str">
         <v/>
       </c>
       <c r="D533">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534">
@@ -7866,13 +7866,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B534" t="str">
-        <v>TDPPK235GoldenKOMP1</v>
+        <v>TDPPK235GarmoniyaChuvstvOSN1</v>
       </c>
       <c r="C534" t="str">
         <v/>
       </c>
       <c r="D534">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -7880,7 +7880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B535" t="str">
-        <v>TDPPK235GoldenKOMP3</v>
+        <v>TDPPK235GoldenKOMP1</v>
       </c>
       <c r="C535" t="str">
         <v/>
@@ -7894,7 +7894,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B536" t="str">
-        <v>TDPPK235ImitatsiyaOSN1</v>
+        <v>TDPPK235GoldenKOMP3</v>
       </c>
       <c r="C536" t="str">
         <v/>
@@ -7908,7 +7908,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B537" t="str">
-        <v>TDPPK235InessaKOMP1</v>
+        <v>TDPPK235ImitatsiyaOSN1</v>
       </c>
       <c r="C537" t="str">
         <v/>
@@ -7922,7 +7922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B538" t="str">
-        <v>TDPPK235InessaOSN1</v>
+        <v>TDPPK235InessaKOMP1</v>
       </c>
       <c r="C538" t="str">
         <v/>
@@ -7936,7 +7936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B539" t="str">
-        <v>TDPPK235LegkayaProkhladaOSN1</v>
+        <v>TDPPK235InessaOSN1</v>
       </c>
       <c r="C539" t="str">
         <v/>
@@ -7950,7 +7950,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B540" t="str">
-        <v>TDPPK235LepestokOSN1-125</v>
+        <v>TDPPK235LegkayaProkhladaOSN1</v>
       </c>
       <c r="C540" t="str">
         <v/>
@@ -7964,13 +7964,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B541" t="str">
-        <v>TDPPK235LuchSolntsaKOMP1-125</v>
+        <v>TDPPK235LepestokOSN1-125</v>
       </c>
       <c r="C541" t="str">
         <v/>
       </c>
       <c r="D541">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="542">
@@ -7978,13 +7978,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B542" t="str">
-        <v>TDPPK235LyubimyyMotivOSN1</v>
+        <v>TDPPK235LuchSolntsaKOMP1-125</v>
       </c>
       <c r="C542" t="str">
         <v/>
       </c>
       <c r="D542">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -7992,7 +7992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B543" t="str">
-        <v>TDPPK235MilagrosOSN1</v>
+        <v>TDPPK235LyubimyyMotivOSN1</v>
       </c>
       <c r="C543" t="str">
         <v/>
@@ -8006,7 +8006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B544" t="str">
-        <v>TDPPK235MyagkayaPerinaOSN1</v>
+        <v>TDPPK235MilagrosOSN1</v>
       </c>
       <c r="C544" t="str">
         <v/>
@@ -8020,7 +8020,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B545" t="str">
-        <v>TDPPK235NapravlenieOSN1-125</v>
+        <v>TDPPK235MyagkayaPerinaOSN1</v>
       </c>
       <c r="C545" t="str">
         <v/>
@@ -8034,7 +8034,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B546" t="str">
-        <v>TDPPK235NimfeyaOSN1</v>
+        <v>TDPPK235NapravlenieOSN1-125</v>
       </c>
       <c r="C546" t="str">
         <v/>
@@ -8048,7 +8048,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B547" t="str">
-        <v>TDPPK235NinelKOMP4</v>
+        <v>TDPPK235NimfeyaOSN1</v>
       </c>
       <c r="C547" t="str">
         <v/>
@@ -8062,7 +8062,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B548" t="str">
-        <v>TDPPK235NinelOSN1-125</v>
+        <v>TDPPK235NinelKOMP4</v>
       </c>
       <c r="C548" t="str">
         <v/>
@@ -8076,7 +8076,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B549" t="str">
-        <v>TDPPK235NovyyDen2</v>
+        <v>TDPPK235NinelOSN1-125</v>
       </c>
       <c r="C549" t="str">
         <v/>
@@ -8090,7 +8090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B550" t="str">
-        <v>TDPPK235NovyyDen6</v>
+        <v>TDPPK235NovyyDen2</v>
       </c>
       <c r="C550" t="str">
         <v/>
@@ -8104,7 +8104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B551" t="str">
-        <v>TDPPK235PalmerOSN1</v>
+        <v>TDPPK235NovyyDen6</v>
       </c>
       <c r="C551" t="str">
         <v/>
@@ -8118,13 +8118,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B552" t="str">
-        <v>TDPPK235PassazhOSN1-125</v>
+        <v>TDPPK235PalmerOSN1</v>
       </c>
       <c r="C552" t="str">
         <v/>
       </c>
       <c r="D552">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553">
@@ -8132,7 +8132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B553" t="str">
-        <v>TDPPK235PlenitelnayaGratsiyaKOMP1</v>
+        <v>TDPPK235PassazhOSN1-125</v>
       </c>
       <c r="C553" t="str">
         <v/>
@@ -8146,13 +8146,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B554" t="str">
-        <v>TDPPK235PlenitelnayaGratsiyaOSN1</v>
+        <v>TDPPK235PlenitelnayaGratsiyaKOMP1</v>
       </c>
       <c r="C554" t="str">
         <v/>
       </c>
       <c r="D554">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="555">
@@ -8160,7 +8160,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B555" t="str">
-        <v>TDPPK235PoeziyaKrasotyKOMP1</v>
+        <v>TDPPK235PlenitelnayaGratsiyaOSN1</v>
       </c>
       <c r="C555" t="str">
         <v/>
@@ -8174,13 +8174,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B556" t="str">
-        <v>TDPPK235PoeziyaKrasotyOSN1</v>
+        <v>TDPPK235PoeziyaKrasotyKOMP1</v>
       </c>
       <c r="C556" t="str">
         <v/>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -8188,13 +8188,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B557" t="str">
-        <v>TDPPK235PrimaveraOSN1</v>
+        <v>TDPPK235PoeziyaKrasotyOSN1</v>
       </c>
       <c r="C557" t="str">
         <v/>
       </c>
       <c r="D557">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558">
@@ -8202,13 +8202,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B558" t="str">
-        <v>TDPPK235RenataOSN1-125</v>
+        <v>TDPPK235PrimaveraOSN1</v>
       </c>
       <c r="C558" t="str">
         <v/>
       </c>
       <c r="D558">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -8216,13 +8216,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B559" t="str">
-        <v>TDPPK235SelinOSN1</v>
+        <v>TDPPK235RenataOSN1-125</v>
       </c>
       <c r="C559" t="str">
         <v/>
       </c>
       <c r="D559">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -8230,7 +8230,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B560" t="str">
-        <v>TDPPK235SiluetySvetaOSN1</v>
+        <v>TDPPK235SelinOSN1</v>
       </c>
       <c r="C560" t="str">
         <v/>
@@ -8244,7 +8244,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B561" t="str">
-        <v>TDPPK235SintezOSN1</v>
+        <v>TDPPK235SiluetySvetaOSN1</v>
       </c>
       <c r="C561" t="str">
         <v/>
@@ -8258,7 +8258,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B562" t="str">
-        <v>TDPPK235SliyanieOSN1-125</v>
+        <v>TDPPK235SintezOSN1</v>
       </c>
       <c r="C562" t="str">
         <v/>
@@ -8272,7 +8272,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B563" t="str">
-        <v>TDPPK235SozvezdiyaKOMP1-125</v>
+        <v>TDPPK235SliyanieOSN1-125</v>
       </c>
       <c r="C563" t="str">
         <v/>
@@ -8286,13 +8286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B564" t="str">
-        <v>TDPPK235Stripe4</v>
+        <v>TDPPK235SozvezdiyaKOMP1-125</v>
       </c>
       <c r="C564" t="str">
         <v/>
       </c>
       <c r="D564">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="565">
@@ -8300,7 +8300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B565" t="str">
-        <v>TDPPK235Stripe5</v>
+        <v>TDPPK235Stripe4</v>
       </c>
       <c r="C565" t="str">
         <v/>
@@ -8314,13 +8314,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B566" t="str">
-        <v>TDPPK235TaynaPrirodyOSN1</v>
+        <v>TDPPK235Stripe5</v>
       </c>
       <c r="C566" t="str">
         <v/>
       </c>
       <c r="D566">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
@@ -8328,7 +8328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B567" t="str">
-        <v>TDPPK235TsvetenieOSN1</v>
+        <v>TDPPK235TaynaPrirodyOSN1</v>
       </c>
       <c r="C567" t="str">
         <v/>
@@ -8342,7 +8342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B568" t="str">
-        <v>TDPPK235TumannyeRassvetyKOMP3-125</v>
+        <v>TDPPK235TsvetenieOSN1</v>
       </c>
       <c r="C568" t="str">
         <v/>
@@ -8356,7 +8356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B569" t="str">
-        <v>TDPPK235TumannyeRassvetyOSN3-125</v>
+        <v>TDPPK235TumannyeRassvetyKOMP3-125</v>
       </c>
       <c r="C569" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B570" t="str">
-        <v>TDPPK235TurmalinOSN1</v>
+        <v>TDPPK235TumannyeRassvetyOSN3-125</v>
       </c>
       <c r="C570" t="str">
         <v/>
@@ -8384,7 +8384,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B571" t="str">
-        <v>TDPPK235VanessaKOMP1</v>
+        <v>TDPPK235TurmalinOSN1</v>
       </c>
       <c r="C571" t="str">
         <v/>
@@ -8398,7 +8398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B572" t="str">
-        <v>TDPPK235VanessaOSN1</v>
+        <v>TDPPK235VanessaKOMP1</v>
       </c>
       <c r="C572" t="str">
         <v/>
@@ -8412,13 +8412,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B573" t="str">
-        <v>TDPPK235VetkaSakuryOSN1</v>
+        <v>TDPPK235VanessaOSN1</v>
       </c>
       <c r="C573" t="str">
         <v/>
       </c>
       <c r="D573">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="574">
@@ -8426,7 +8426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B574" t="str">
-        <v>TDPPK235VremyaTsveteniyaOSN1</v>
+        <v>TDPPK235VetkaSakuryOSN1</v>
       </c>
       <c r="C574" t="str">
         <v/>
@@ -8440,13 +8440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B575" t="str">
-        <v>TDPPK235VyshivkaOSN1-125</v>
+        <v>TDPPK235VremyaTsveteniyaOSN1</v>
       </c>
       <c r="C575" t="str">
         <v/>
       </c>
       <c r="D575">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="576">
@@ -8454,7 +8454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B576" t="str">
-        <v>TDPPK235VzmakhKistiOSN1</v>
+        <v>TDPPK235VyshivkaOSN1-125</v>
       </c>
       <c r="C576" t="str">
         <v/>
@@ -8468,13 +8468,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B577" t="str">
-        <v>TDPPK235YaponskiyDvorikOSN1-125</v>
+        <v>TDPPK235VzmakhKistiOSN1</v>
       </c>
       <c r="C577" t="str">
         <v/>
       </c>
       <c r="D577">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578">
@@ -8482,7 +8482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B578" t="str">
-        <v>TDPPK235ZhordanOSN2-125</v>
+        <v>TDPPK235YaponskiyDvorikOSN1-125</v>
       </c>
       <c r="C578" t="str">
         <v/>
@@ -8496,7 +8496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B579" t="str">
-        <v>TDPPK235ZolotoeSiyanieOSN1</v>
+        <v>TDPPK235ZhordanOSN2-125</v>
       </c>
       <c r="C579" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B580" t="str">
-        <v>TDPPK235ZvezdnyySvetKOMP1</v>
+        <v>TDPPK235ZolotoeSiyanieOSN1</v>
       </c>
       <c r="C580" t="str">
         <v/>
@@ -8524,13 +8524,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B581" t="str">
-        <v>TDPPK235ZvezdnyySvetOSN1</v>
+        <v>TDPPK235ZvezdnyySvetKOMP1</v>
       </c>
       <c r="C581" t="str">
         <v/>
       </c>
       <c r="D581">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
@@ -8538,18 +8538,466 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B582" t="str">
+        <v>TDPPK235ZvezdnyySvetOSN1</v>
+      </c>
+      <c r="C582" t="str">
+        <v/>
+      </c>
+      <c r="D582">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B583" t="str">
         <v>TDPPK235KhloyaOSN1-125</v>
       </c>
-      <c r="C582" t="str">
-        <v/>
-      </c>
-      <c r="D582">
-        <v>0</v>
+      <c r="C583" t="str">
+        <v/>
+      </c>
+      <c r="D583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B584" t="str">
+        <v>TDM-liliac</v>
+      </c>
+      <c r="C584" t="str">
+        <v/>
+      </c>
+      <c r="D584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B585" t="str">
+        <v>TDM-karamel</v>
+      </c>
+      <c r="C585" t="str">
+        <v/>
+      </c>
+      <c r="D585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B586" t="str">
+        <v>TDM-mint</v>
+      </c>
+      <c r="C586" t="str">
+        <v/>
+      </c>
+      <c r="D586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B587" t="str">
+        <v>TR-Elochka1-195x165</v>
+      </c>
+      <c r="C587" t="str">
+        <v/>
+      </c>
+      <c r="D587">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B588" t="str">
+        <v>TR-Lavanda1-195x165</v>
+      </c>
+      <c r="C588" t="str">
+        <v/>
+      </c>
+      <c r="D588">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B589" t="str">
+        <v>TR-LetneeNastroenie1-195x165</v>
+      </c>
+      <c r="C589" t="str">
+        <v/>
+      </c>
+      <c r="D589">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B590" t="str">
+        <v>TR-LetnyaaNoch1-195x165</v>
+      </c>
+      <c r="C590" t="str">
+        <v/>
+      </c>
+      <c r="D590">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B591" t="str">
+        <v>TR-LimonnayaKorzinka1-195x165</v>
+      </c>
+      <c r="C591" t="str">
+        <v/>
+      </c>
+      <c r="D591">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B592" t="str">
+        <v>TR-NejniyDen1-195x165</v>
+      </c>
+      <c r="C592" t="str">
+        <v/>
+      </c>
+      <c r="D592">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B593" t="str">
+        <v>TR-Pascha-195x165</v>
+      </c>
+      <c r="C593" t="str">
+        <v/>
+      </c>
+      <c r="D593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B594" t="str">
+        <v>TR-Poloska1-195x165</v>
+      </c>
+      <c r="C594" t="str">
+        <v/>
+      </c>
+      <c r="D594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B595" t="str">
+        <v>TR-Rojdestvo1-195x165</v>
+      </c>
+      <c r="C595" t="str">
+        <v/>
+      </c>
+      <c r="D595">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B596" t="str">
+        <v>TR-SpelieFrukti1-195x165</v>
+      </c>
+      <c r="C596" t="str">
+        <v/>
+      </c>
+      <c r="D596">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B597" t="str">
+        <v>TR-TihiyVecher1-195x165</v>
+      </c>
+      <c r="C597" t="str">
+        <v/>
+      </c>
+      <c r="D597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B598" t="str">
+        <v>TR-Hutoryanka1-195x165</v>
+      </c>
+      <c r="C598" t="str">
+        <v/>
+      </c>
+      <c r="D598">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B599" t="str">
+        <v>TDSPK250DarkViolet-8</v>
+      </c>
+      <c r="C599" t="str">
+        <v/>
+      </c>
+      <c r="D599">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B600" t="str">
+        <v>TDSPK250Sliva-8</v>
+      </c>
+      <c r="C600" t="str">
+        <v/>
+      </c>
+      <c r="D600">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B601" t="str">
+        <v>TDSPK250Persikoviy-8</v>
+      </c>
+      <c r="C601" t="str">
+        <v/>
+      </c>
+      <c r="D601">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B602" t="str">
+        <v>TDSPK250Lavanda-8</v>
+      </c>
+      <c r="C602" t="str">
+        <v/>
+      </c>
+      <c r="D602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B603" t="str">
+        <v>TDSPK250Bordo-8</v>
+      </c>
+      <c r="C603" t="str">
+        <v/>
+      </c>
+      <c r="D603">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B604" t="str">
+        <v>TDSPK250LightLiliac-8</v>
+      </c>
+      <c r="C604" t="str">
+        <v/>
+      </c>
+      <c r="D604">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B605" t="str">
+        <v>TDSPK250Liliac-8</v>
+      </c>
+      <c r="C605" t="str">
+        <v/>
+      </c>
+      <c r="D605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B606" t="str">
+        <v>TDSPK250Blue-8</v>
+      </c>
+      <c r="C606" t="str">
+        <v/>
+      </c>
+      <c r="D606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B607" t="str">
+        <v>TDSPK250Choco-8</v>
+      </c>
+      <c r="C607" t="str">
+        <v/>
+      </c>
+      <c r="D607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B608" t="str">
+        <v>TDSPK250Menthol-8</v>
+      </c>
+      <c r="C608" t="str">
+        <v/>
+      </c>
+      <c r="D608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B609" t="str">
+        <v>TDSPK250LightBlue-8</v>
+      </c>
+      <c r="C609" t="str">
+        <v/>
+      </c>
+      <c r="D609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B610" t="str">
+        <v>TDSPK250PepelRose-8</v>
+      </c>
+      <c r="C610" t="str">
+        <v/>
+      </c>
+      <c r="D610">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B611" t="str">
+        <v>TDSPK250Bejeviy-8</v>
+      </c>
+      <c r="C611" t="str">
+        <v/>
+      </c>
+      <c r="D611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B612" t="str">
+        <v>TDSPK250Gold-8</v>
+      </c>
+      <c r="C612" t="str">
+        <v/>
+      </c>
+      <c r="D612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B613" t="str">
+        <v>TDSPK250Pink-8</v>
+      </c>
+      <c r="C613" t="str">
+        <v/>
+      </c>
+      <c r="D613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B614" t="str">
+        <v>TDSPK250Grafit-8</v>
+      </c>
+      <c r="C614" t="str">
+        <v/>
+      </c>
+      <c r="D614">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D582"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D614"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/td-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/td-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D614"/>
+  <dimension ref="A1:D613"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,7 +418,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B2" t="str">
-        <v>TDPPKMgnoveniyaComp33</v>
+        <v>TDPPKNapevOSN1</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -432,7 +432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B3" t="str">
-        <v>TDPPKNapevOSN1</v>
+        <v>TDPPKPersidskayaSirenOsn</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -446,7 +446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B4" t="str">
-        <v>TDPPKPersidskayaSirenOsn</v>
+        <v>TDPPKPesnyaZvezdOsn33</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B5" t="str">
-        <v>TDPPKPesnyaZvezdOsn33</v>
+        <v>TDPPKAsteriaCOMP33</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -474,7 +474,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B6" t="str">
-        <v>TDPPKAsteriaCOMP33</v>
+        <v>TDPPKAsteriaOSN33</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -488,7 +488,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B7" t="str">
-        <v>TDPPKAsteriaOSN33</v>
+        <v>TDPPKabstraciaOSN33</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -502,7 +502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B8" t="str">
-        <v>TDPPKabstraciaOSN33</v>
+        <v>TDPPKBornComp33</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B9" t="str">
-        <v>TDPPKBornComp33</v>
+        <v>TDPPKBornOSN33</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -530,7 +530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B10" t="str">
-        <v>TDPPKBornOSN33</v>
+        <v>TDPPKBruno33</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B11" t="str">
-        <v>TDPPKBruno33</v>
+        <v>TDPPKclassic220NovogodIgrushOsn</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B12" t="str">
-        <v>TDPPKclassic220NovogodIgrushOsn</v>
+        <v>TDPPKclassic220vetkimimozOSNOV</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -572,7 +572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B13" t="str">
-        <v>TDPPKclassic220vetkimimozOSNOV</v>
+        <v>TDPPKDavidComp33</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B14" t="str">
-        <v>TDPPKDavidComp33</v>
+        <v>TDPPKDavidOsn33</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -600,7 +600,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B15" t="str">
-        <v>TDPPKDavidOsn33</v>
+        <v>TDPPKDunovenieComp33</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -614,7 +614,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B16" t="str">
-        <v>TDPPKDunovenieComp33</v>
+        <v>TDPPKDunovenieOSN33</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -628,7 +628,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B17" t="str">
-        <v>TDPPKDunovenieOSN33</v>
+        <v>TDPPKGabrielComp331</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B18" t="str">
-        <v>TDPPKGabrielComp331</v>
+        <v>TDPPKGabrielOsn331</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B19" t="str">
-        <v>TDPPKGabrielOsn331</v>
+        <v>TDPPKJack33</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -670,7 +670,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B20" t="str">
-        <v>TDPPKJack33</v>
+        <v>TDPPKKamillaComp33</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -684,7 +684,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B21" t="str">
-        <v>TDPPKKamillaComp33</v>
+        <v>TDPPKKamillaOSN33</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -698,7 +698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B22" t="str">
-        <v>TDPPKKamillaOSN33</v>
+        <v>TDPPKLegkoeDihanieComp33</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B23" t="str">
-        <v>TDPPKLegkoeDihanieComp33</v>
+        <v>TDPPKMeditaciaComp33</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B24" t="str">
-        <v>TDPPKMeditaciaComp33</v>
+        <v>TDPPKMeditaciaOsn33</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B25" t="str">
-        <v>TDPPKMeditaciaOsn33</v>
+        <v>TDPPKMgnoveniyaOsn33</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -754,7 +754,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B26" t="str">
-        <v>TDPPKMgnoveniyaOsn33</v>
+        <v>TDPPKPrometOSN</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B27" t="str">
-        <v>TDPPKPrometOSN</v>
+        <v>TDPPKRapsodiaOsn33</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -782,7 +782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B28" t="str">
-        <v>TDPPKRapsodiaOsn33</v>
+        <v>TDPPKRomanComp33</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B29" t="str">
-        <v>TDPPKRomanComp33</v>
+        <v>TDPPKRomanOsn33</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -810,13 +810,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B30" t="str">
-        <v>TDPPKRomanOsn33</v>
+        <v>TDPPKSalomeyaComp33</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -824,13 +824,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B31" t="str">
-        <v>TDPPKSalomeyaComp33</v>
+        <v>TDPPKSalomeyaOsn33</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -838,7 +838,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B32" t="str">
-        <v>TDPPKSalomeyaOsn33</v>
+        <v>TDPPKTanecVetraOsn33</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -852,7 +852,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B33" t="str">
-        <v>TDPPKTanecVetraOsn33</v>
+        <v>TDPPKTobiasOsn33</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B34" t="str">
-        <v>TDPPKTobiasOsn33</v>
+        <v>TDPPKVenzelKomp2</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -880,7 +880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B35" t="str">
-        <v>TDPPKVenzelKomp2</v>
+        <v>TDPPKVenzelOSN33</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -894,7 +894,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B36" t="str">
-        <v>TDPPKVenzelOSN33</v>
+        <v>TDPPKVesenKapOSN33</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -908,7 +908,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B37" t="str">
-        <v>TDPPKVesenKapOSN33</v>
+        <v>TDPPKVetkiMimozKomp</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -922,7 +922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B38" t="str">
-        <v>TDPPKVetkiMimozKomp</v>
+        <v>TDPPKZataivDihanieComp33</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B39" t="str">
-        <v>TDPPKZataivDihanieComp33</v>
+        <v>TDPPKZataivDihanieOSN33</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -950,7 +950,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B40" t="str">
-        <v>TDPPKZataivDihanieOSN33</v>
+        <v>TDPPKAttikaOSN33</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -964,7 +964,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B41" t="str">
-        <v>TDPPKAttikaOSN33</v>
+        <v>TDPPKLegkoeDihanieOsn33</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B42" t="str">
-        <v>TDPPKLegkoeDihanieOsn33</v>
+        <v>TDPPKGabrielComp334</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -992,7 +992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B43" t="str">
-        <v>TDPPKGabrielComp334</v>
+        <v>TDPPKclassic220TanzaniaOsn</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1006,7 +1006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B44" t="str">
-        <v>TDPPKclassic220TanzaniaOsn</v>
+        <v>TDPPKMercLotosOsn</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1020,13 +1020,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B45" t="str">
-        <v>TDPPKMercLotosOsn</v>
+        <v>TDPPKRapsodiaComp33</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1034,7 +1034,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B46" t="str">
-        <v>TDPPKRapsodiaComp33</v>
+        <v>TDPPKTanecVetraComp33</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1048,7 +1048,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B47" t="str">
-        <v>TDPPKTanecVetraComp33</v>
+        <v>TDPPKGetsbiComp33</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1062,7 +1062,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B48" t="str">
-        <v>TDPPKGetsbiComp33</v>
+        <v>TDPPKNovolunieComp33</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B49" t="str">
-        <v>TDPPKNovolunieComp33</v>
+        <v>TDPPKVesenKapComp33</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1090,7 +1090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B50" t="str">
-        <v>TDPPKVesenKapComp33</v>
+        <v>TDPPKNovolunieOsn33</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1104,7 +1104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B51" t="str">
-        <v>TDPPKNovolunieOsn33</v>
+        <v>TDPPKAdrianOSN33</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1118,7 +1118,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B52" t="str">
-        <v>TDPPKAdrianOSN33</v>
+        <v>TDPPKKotofeiComp33</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B53" t="str">
-        <v>TDPPKKotofeiComp33</v>
+        <v>TDPPKMagnoliyaOsn33</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1146,7 +1146,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B54" t="str">
-        <v>TDPPKMagnoliyaOsn33</v>
+        <v>TDPPKlidiaKomp</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1160,7 +1160,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B55" t="str">
-        <v>TDPPKlidiaKomp</v>
+        <v>TDM-black</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1174,7 +1174,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B56" t="str">
-        <v>TDM-black</v>
+        <v>TDM-darkGrafit</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1188,7 +1188,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B57" t="str">
-        <v>TDM-darkGrafit</v>
+        <v>TDM-grey</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1202,13 +1202,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B58" t="str">
-        <v>TDM-grey</v>
+        <v>TDM-indigo</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -1216,7 +1216,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B59" t="str">
-        <v>TDM-indigo</v>
+        <v>TDM-lightLiliac</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1230,13 +1230,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B60" t="str">
-        <v>TDM-lightLiliac</v>
+        <v>TDM-lilov</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1244,7 +1244,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B61" t="str">
-        <v>TDM-lilov</v>
+        <v>TDM-molochn</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1258,7 +1258,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B62" t="str">
-        <v>TDM-molochn</v>
+        <v>TDM-morskaya</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1272,7 +1272,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B63" t="str">
-        <v>TDM-morskaya</v>
+        <v>TDM-otbel110</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1286,7 +1286,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B64" t="str">
-        <v>TDM-otbel110</v>
+        <v>TDM-platina</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1300,7 +1300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B65" t="str">
-        <v>TDM-platina</v>
+        <v>TDM-terrakot</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1314,7 +1314,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B66" t="str">
-        <v>TDM-terrakot</v>
+        <v>TDM-rose</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>TDM-rose</v>
+        <v>TDPPKAttikaComp33</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1342,7 +1342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>TDPPKAttikaComp33</v>
+        <v>TDPPKBelStihOSN33</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>TDPPKBelStihOSN33</v>
+        <v>TDPPKGetsbiOsn33</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1370,7 +1370,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>TDPPKGetsbiOsn33</v>
+        <v>TDPPKKotofeiOsn33</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1384,7 +1384,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>TDPPKKotofeiOsn33</v>
+        <v>TDPPKabstraciaCOMP33</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -1398,7 +1398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>TDPPKabstraciaCOMP33</v>
+        <v>TDM-Otbel125</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1412,7 +1412,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>TDM-Otbel125</v>
+        <v>TDPPKMagnoliyaComp33</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1426,7 +1426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>TDPPKMagnoliyaComp33</v>
+        <v>TDPPK235BelBuketKOMP1</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1440,13 +1440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>TDPPK235BelBuketKOMP1</v>
+        <v>TDPPK235BelBuketOSN1</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -1454,13 +1454,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>TDPPK235BelBuketOSN1</v>
+        <v>TDSPK220KamillaKOMP5</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1468,7 +1468,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>TDSPK220KamillaKOMP5</v>
+        <v>TDSPK220SovershenstvoKOMP1</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>TDSPK220SovershenstvoKOMP1</v>
+        <v>TDSPK220EdemOSN</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>TDSPK220EdemOSN</v>
+        <v>TDSPK220ZolotayaOSN</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1510,13 +1510,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>TDSPK220ZolotayaOSN</v>
+        <v>TDSPK220AristokrOSN8</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -1524,13 +1524,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>TDSPK220AristokrOSN8</v>
+        <v>TDSPK220SolnPticOSN</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1538,7 +1538,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>TDSPK220SolnPticOSN</v>
+        <v>TDSPK220MusikVremOSN</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>TDSPK220MusikVremOSN</v>
+        <v>TDSPK220ZolotayaKOMP</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -1566,7 +1566,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>TDSPK220ZolotayaKOMP</v>
+        <v>TDSPK220AdagioOSN4</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>TDSPK220AdagioOSN4</v>
+        <v>TDSPK220AdamOSN2</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1594,7 +1594,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>TDSPK220AdamOSN2</v>
+        <v>TDSPK220AilaKOMP3</v>
       </c>
       <c r="C86" t="str">
         <v/>
@@ -1608,13 +1608,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>TDSPK220AilaKOMP3</v>
+        <v>TDSPK220AilaOSN3</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -1622,13 +1622,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>TDSPK220AilaOSN3</v>
+        <v>TDSPK220AristokrKOMP4</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1636,7 +1636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>TDSPK220AristokrKOMP4</v>
+        <v>TDSPK220AristokrKOMP8</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>TDSPK220AristokrKOMP8</v>
+        <v>TDSPK220AristokrOSN4</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -1664,7 +1664,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>TDSPK220AristokrOSN4</v>
+        <v>TDSPK220AsteriaOSN4</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -1678,7 +1678,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>TDSPK220AsteriaOSN4</v>
+        <v>TDSPK220BalFlowersKOMP1</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -1692,7 +1692,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>TDSPK220BalFlowersKOMP1</v>
+        <v>TDSPK220BalFlowersOSN1</v>
       </c>
       <c r="C93" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>TDSPK220BalFlowersOSN1</v>
+        <v>TDSPK220BuketChuvstvKOMP2</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -1720,7 +1720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>TDSPK220BuketChuvstvKOMP2</v>
+        <v>TDSPK220BuketChuvstvOSN2</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1734,7 +1734,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>TDSPK220BuketChuvstvOSN2</v>
+        <v>TDSPK220VitragiKOMP3</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -1748,7 +1748,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>TDSPK220VitragiKOMP3</v>
+        <v>TDSPK220VitragiOSN3</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -1762,7 +1762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>TDSPK220VitragiOSN3</v>
+        <v>TDSPK220VozdSharOSN2</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1776,13 +1776,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>TDSPK220VozdSharOSN2</v>
+        <v>TDSPK220MetamorphosaOSN2</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -1790,13 +1790,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>TDSPK220MetamorphosaOSN2</v>
+        <v>TDSPK220PachuliKOMP1</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1804,13 +1804,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>TDSPK220PachuliKOMP1</v>
+        <v>TDSPK220HugOSN2</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -1818,7 +1818,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>TDSPK220HugOSN2</v>
+        <v>TDSPK220GabrielKOMP3</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -1832,13 +1832,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>TDSPK220GabrielKOMP3</v>
+        <v>TDSPK220GabrielOSN3</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1846,7 +1846,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>TDSPK220GabrielOSN3</v>
+        <v>TDSPK220DavidOSN4</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -1860,7 +1860,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>TDSPK220DavidOSN4</v>
+        <v>TDSPK220ZataivDihanieKOMP6</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>TDSPK220ZataivDihanieKOMP6</v>
+        <v>TDSPK220ZataivDihanieOSN6</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>TDSPK220ZataivDihanieOSN6</v>
+        <v>TDSPK220KamillaOSN5</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -1902,7 +1902,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>TDSPK220KamillaOSN5</v>
+        <v>TDSPK220CaribbeanOSN2</v>
       </c>
       <c r="C108" t="str">
         <v/>
@@ -1916,13 +1916,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>TDSPK220CaribbeanOSN2</v>
+        <v>TDSPK220KarolinaOSN3</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1930,13 +1930,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B110" t="str">
-        <v>TDSPK220KarolinaOSN3</v>
+        <v>TDSPK220Kashmir1</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -1944,13 +1944,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B111" t="str">
-        <v>TDSPK220Kashmir1</v>
+        <v>TDSPK220LegkoeDihanieOSN5</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1958,13 +1958,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B112" t="str">
-        <v>TDSPK220LegkoeDihanieOSN5</v>
+        <v>TDSPK220LetniyZnoiOSN2</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -1972,13 +1972,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B113" t="str">
-        <v>TDSPK220LetniyZnoiOSN2</v>
+        <v>TDSPK220Monochrome1</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1986,7 +1986,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B114" t="str">
-        <v>TDSPK220Monochrome1</v>
+        <v>TDSPK220Monochrome7</v>
       </c>
       <c r="C114" t="str">
         <v/>
@@ -2000,7 +2000,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B115" t="str">
-        <v>TDSPK220Monochrome7</v>
+        <v>TDSPK220Monochrome8</v>
       </c>
       <c r="C115" t="str">
         <v/>
@@ -2014,7 +2014,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B116" t="str">
-        <v>TDSPK220Monochrome8</v>
+        <v>TDSPK220Monochrome12</v>
       </c>
       <c r="C116" t="str">
         <v/>
@@ -2028,7 +2028,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B117" t="str">
-        <v>TDSPK220Monochrome12</v>
+        <v>TDSPK220NostalgiKOMP4</v>
       </c>
       <c r="C117" t="str">
         <v/>
@@ -2042,13 +2042,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B118" t="str">
-        <v>TDSPK220NostalgiKOMP4</v>
+        <v>TDSPK220ObitelLoveOSN2</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -2056,13 +2056,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B119" t="str">
-        <v>TDSPK220ObitelLoveOSN2</v>
+        <v>TDSPK220OdaNejnostiKOMP2</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2070,7 +2070,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B120" t="str">
-        <v>TDSPK220OdaNejnostiKOMP2</v>
+        <v>TDSPK220OdaNejnostiOSN2</v>
       </c>
       <c r="C120" t="str">
         <v/>
@@ -2084,13 +2084,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B121" t="str">
-        <v>TDSPK220OdaNejnostiOSN2</v>
+        <v>TDSPK220Otbel120</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2098,7 +2098,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B122" t="str">
-        <v>TDSPK220Otbel120</v>
+        <v>TDSPK220OtbleskKOMP3</v>
       </c>
       <c r="C122" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B123" t="str">
-        <v>TDSPK220OtbleskKOMP3</v>
+        <v>TDSPK220HappyDaysOSN2</v>
       </c>
       <c r="C123" t="str">
         <v/>
@@ -2126,13 +2126,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B124" t="str">
-        <v>TDSPK220HappyDaysOSN2</v>
+        <v>TDSPK220PachuliOSN1</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -2140,13 +2140,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B125" t="str">
-        <v>TDSPK220PachuliOSN1</v>
+        <v>TDSPK220PotokKOMP3</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2154,7 +2154,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B126" t="str">
-        <v>TDSPK220PotokKOMP3</v>
+        <v>TDSPK220HappyDaysKOMP2</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -2168,13 +2168,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B127" t="str">
-        <v>TDSPK220HappyDaysKOMP2</v>
+        <v>TDSPK220PotokOSN3</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -2182,13 +2182,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B128" t="str">
-        <v>TDSPK220PotokOSN3</v>
+        <v>TDSPK220StepKOMP</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2196,13 +2196,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B129" t="str">
-        <v>TDSPK220StepKOMP</v>
+        <v>TDSPK220LegkoeDihanieKOMP5</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -2210,7 +2210,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B130" t="str">
-        <v>TDSPK220LegkoeDihanieKOMP5</v>
+        <v>TDSPK220OtbleskOSN3</v>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -2224,13 +2224,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B131" t="str">
-        <v>TDSPK220OtbleskOSN3</v>
+        <v>TDSPK220StoneOSN2</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2238,7 +2238,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B132" t="str">
-        <v>TDSPK220StoneOSN2</v>
+        <v>TDSPK220StoneKOMP2</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -2252,7 +2252,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B133" t="str">
-        <v>TDSPK220StoneKOMP2</v>
+        <v>TDSPK220SoloKOMP1</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -2266,7 +2266,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B134" t="str">
-        <v>TDSPK220SoloKOMP1</v>
+        <v>TDSPK220EtudOSN5</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -2280,7 +2280,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B135" t="str">
-        <v>TDSPK220EtudOSN5</v>
+        <v>TDSPK220BlossomDreamsOSN2</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -2294,7 +2294,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B136" t="str">
-        <v>TDSPK220BlossomDreamsOSN2</v>
+        <v>TDSPK220TanecVetraOSN1</v>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -2308,7 +2308,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B137" t="str">
-        <v>TDSPK220TanecVetraOSN1</v>
+        <v>TDSPK220DavidKOMP3</v>
       </c>
       <c r="C137" t="str">
         <v/>
@@ -2322,13 +2322,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B138" t="str">
-        <v>TDSPK220DavidKOMP3</v>
+        <v>SSPK250-8-Gorchich</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
@@ -2336,7 +2336,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B139" t="str">
-        <v>SSPK250-8-Gorchich</v>
+        <v>SSPK250-8-Otbel</v>
       </c>
       <c r="C139" t="str">
         <v/>
@@ -2350,7 +2350,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B140" t="str">
-        <v>SSPK250-8-Otbel</v>
+        <v>SSPK250-8-Ultramarine</v>
       </c>
       <c r="C140" t="str">
         <v/>
@@ -2364,13 +2364,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B141" t="str">
-        <v>SSPK250-8-Ultramarine</v>
+        <v>SSPK250-8-RoseCream</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2378,13 +2378,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B142" t="str">
-        <v>SSPK250-8-RoseCream</v>
+        <v>SSPK250-8-BrightBlue</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -2392,13 +2392,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B143" t="str">
-        <v>SSPK250-8-BrightBlue</v>
+        <v>SSPK250-8-DustyRose</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2406,7 +2406,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B144" t="str">
-        <v>SSPK250-8-DustyRose</v>
+        <v>SSPK250-8-Lavanda</v>
       </c>
       <c r="C144" t="str">
         <v/>
@@ -2420,13 +2420,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B145" t="str">
-        <v>SSPK250-8-Lavanda</v>
+        <v>SSPK250-8-Terrakota</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -2434,13 +2434,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B146" t="str">
-        <v>SSPK250-8-Terrakota</v>
+        <v>SSPK250-8-LightBlue</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -2448,13 +2448,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B147" t="str">
-        <v>SSPK250-8-LightBlue</v>
+        <v>SSPK250-8-KaruzoGreen</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -2462,13 +2462,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B148" t="str">
-        <v>SSPK250-8-KaruzoGreen</v>
+        <v>SSPK250-8-Lazurn</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -2476,13 +2476,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B149" t="str">
-        <v>SSPK250-8-Lazurn</v>
+        <v>SSPK250-8-KaruzoViolet</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
@@ -2490,13 +2490,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B150" t="str">
-        <v>SSPK250-8-KaruzoViolet</v>
+        <v>SSPK250-8-Coffee</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -2504,13 +2504,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B151" t="str">
-        <v>SSPK250-8-Coffee</v>
+        <v>SSPK250-8-Verde</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -2518,13 +2518,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B152" t="str">
-        <v>SSPK250-8-Verde</v>
+        <v>SSPK250-8-Persik</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -2532,13 +2532,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B153" t="str">
-        <v>SSPK250-8-Persik</v>
+        <v>SSPK250-8-Pink</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -2546,13 +2546,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B154" t="str">
-        <v>SSPK250-8-Pink</v>
+        <v>SSPK250-8-Jemjug</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -2560,7 +2560,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B155" t="str">
-        <v>SSPK250-8-Jemjug</v>
+        <v>SSPK250-8-Nebesn</v>
       </c>
       <c r="C155" t="str">
         <v/>
@@ -2574,7 +2574,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B156" t="str">
-        <v>SSPK250-8-Nebesn</v>
+        <v>SSPK250-8-Grafit</v>
       </c>
       <c r="C156" t="str">
         <v/>
@@ -2588,13 +2588,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B157" t="str">
-        <v>SSPK250-8-Grafit</v>
+        <v>SSPK250-8-Blue</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
@@ -2602,13 +2602,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B158" t="str">
-        <v>SSPK250-8-Blue</v>
+        <v>SSPK250-8-Grey</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -2616,7 +2616,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B159" t="str">
-        <v>SSPK250-8-Grey</v>
+        <v>SSPK250-8-Chocolate</v>
       </c>
       <c r="C159" t="str">
         <v/>
@@ -2630,7 +2630,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B160" t="str">
-        <v>SSPK250-8-Chocolate</v>
+        <v>SSPK250-8-Green</v>
       </c>
       <c r="C160" t="str">
         <v/>
@@ -2644,7 +2644,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B161" t="str">
-        <v>SSPK250-8-Green</v>
+        <v>SSPK250-8-Wine</v>
       </c>
       <c r="C161" t="str">
         <v/>
@@ -2658,13 +2658,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B162" t="str">
-        <v>SSPK250-8-Wine</v>
+        <v>SSPK250-8-Black</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
@@ -2672,13 +2672,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B163" t="str">
-        <v>SSPK250-8-Black</v>
+        <v>SSPK250-8-Bejeviy</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -2686,13 +2686,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B164" t="str">
-        <v>SSPK250-8-Bejeviy</v>
+        <v>SSPK250-8-Korall</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
@@ -2700,7 +2700,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B165" t="str">
-        <v>SSPK250-8-Korall</v>
+        <v>TDSPK250DarkViolet</v>
       </c>
       <c r="C165" t="str">
         <v/>
@@ -2714,13 +2714,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B166" t="str">
-        <v>TDSPK250DarkViolet</v>
+        <v>TDSPK250Green</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2728,13 +2728,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B167" t="str">
-        <v>TDSPK250Green</v>
+        <v>TDSPK250Persikoviy</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -2742,13 +2742,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B168" t="str">
-        <v>TDSPK250Persikoviy</v>
+        <v>TDSPK250Lavanda</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -2756,7 +2756,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B169" t="str">
-        <v>TDSPK250Lavanda</v>
+        <v>TDSPK250Coffee</v>
       </c>
       <c r="C169" t="str">
         <v/>
@@ -2770,13 +2770,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B170" t="str">
-        <v>TDSPK250Coffee</v>
+        <v>TDSPK250Bordo</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -2784,7 +2784,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B171" t="str">
-        <v>TDSPK250Bordo</v>
+        <v>TDSPK250LightLiliac</v>
       </c>
       <c r="C171" t="str">
         <v/>
@@ -2798,13 +2798,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B172" t="str">
-        <v>TDSPK250LightLiliac</v>
+        <v>TDSPK250Liliac</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -2812,7 +2812,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B173" t="str">
-        <v>TDSPK250Liliac</v>
+        <v>TDSPK250Blue</v>
       </c>
       <c r="C173" t="str">
         <v/>
@@ -2826,7 +2826,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B174" t="str">
-        <v>TDSPK250Blue</v>
+        <v>TDSPK250Choco</v>
       </c>
       <c r="C174" t="str">
         <v/>
@@ -2840,7 +2840,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B175" t="str">
-        <v>TDSPK250Choco</v>
+        <v>TDSPK250Menthol</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -2854,7 +2854,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B176" t="str">
-        <v>TDSPK250Menthol</v>
+        <v>TDSPK250Taup</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -2868,7 +2868,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B177" t="str">
-        <v>TDSPK250Taup</v>
+        <v>TDSPK250Platina</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -2882,7 +2882,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B178" t="str">
-        <v>TDSPK250Platina</v>
+        <v>TDSPK250White</v>
       </c>
       <c r="C178" t="str">
         <v/>
@@ -2896,7 +2896,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B179" t="str">
-        <v>TDSPK250White</v>
+        <v>TDSPK250LightBlue</v>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -2910,13 +2910,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B180" t="str">
-        <v>TDSPK250LightBlue</v>
+        <v>TDSPK250PepelRose</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
@@ -2924,13 +2924,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B181" t="str">
-        <v>TDSPK250PepelRose</v>
+        <v>TDSPK250Bejeviy</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -2938,7 +2938,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B182" t="str">
-        <v>TDSPK250Bejeviy</v>
+        <v>TDSPK250Jemjug</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -2952,7 +2952,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B183" t="str">
-        <v>TDSPK250Jemjug</v>
+        <v>TDSPK250LightGreen</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -2966,7 +2966,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B184" t="str">
-        <v>TDSPK250LightGreen</v>
+        <v>TDSPK250Gold</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -2980,7 +2980,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B185" t="str">
-        <v>TDSPK250Gold</v>
+        <v>TDSPK250Pink</v>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -2994,7 +2994,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B186" t="str">
-        <v>TDSPK250Pink</v>
+        <v>TDSPK250Kvarc</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -3008,7 +3008,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B187" t="str">
-        <v>TDSPK250Kvarc</v>
+        <v>TDSPK250ToplMilk</v>
       </c>
       <c r="C187" t="str">
         <v/>
@@ -3022,7 +3022,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B188" t="str">
-        <v>TDSPK250ToplMilk</v>
+        <v>TDSPK250GrafitGreen</v>
       </c>
       <c r="C188" t="str">
         <v/>
@@ -3036,13 +3036,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B189" t="str">
-        <v>TDSPK250GrafitGreen</v>
+        <v>TDSPK250Sliva</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
@@ -3050,13 +3050,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B190" t="str">
-        <v>TDSPK250Sliva</v>
+        <v>TDSPK220BuketChuvstvOSN2-8</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -3064,7 +3064,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B191" t="str">
-        <v>TDSPK220BuketChuvstvOSN2-8</v>
+        <v>TDSPK220Monochrome8-8</v>
       </c>
       <c r="C191" t="str">
         <v/>
@@ -3078,7 +3078,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B192" t="str">
-        <v>TDSPK220Monochrome8-8</v>
+        <v>TDSPK220Monochrome1-8</v>
       </c>
       <c r="C192" t="str">
         <v/>
@@ -3092,13 +3092,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B193" t="str">
-        <v>TDSPK220Monochrome1-8</v>
+        <v>TDSPK220AristokrOSN8-8</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -3106,13 +3106,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B194" t="str">
-        <v>TDSPK220AristokrOSN8-8</v>
+        <v>TDSPK220HappyDaysOSN2-8</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -3120,7 +3120,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B195" t="str">
-        <v>TDSPK220HappyDaysOSN2-8</v>
+        <v>TDSPK220AilaKOMP3-8</v>
       </c>
       <c r="C195" t="str">
         <v/>
@@ -3134,7 +3134,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B196" t="str">
-        <v>TDSPK220AilaKOMP3-8</v>
+        <v>TDSPK220Monochrome7-8</v>
       </c>
       <c r="C196" t="str">
         <v/>
@@ -3148,13 +3148,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B197" t="str">
-        <v>TDSPK220Monochrome7-8</v>
+        <v>TDSPK220PotokOSN3-8</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
@@ -3162,13 +3162,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B198" t="str">
-        <v>TDSPK220PotokOSN3-8</v>
+        <v>TDSPK220EdemKomp-8</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -3176,7 +3176,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B199" t="str">
-        <v>TDSPK220EdemKomp-8</v>
+        <v>TDSPK220Monochrome12-8</v>
       </c>
       <c r="C199" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B200" t="str">
-        <v>TDSPK220Monochrome12-8</v>
+        <v>TDSPK220AsteriaOSN4-8</v>
       </c>
       <c r="C200" t="str">
         <v/>
@@ -3204,13 +3204,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B201" t="str">
-        <v>TDSPK220AsteriaOSN4-8</v>
+        <v>TDSPK220HugOSN2-8</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -3218,13 +3218,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B202" t="str">
-        <v>TDSPK220HugOSN2-8</v>
+        <v>TDSPK220KamillaKOMP5-8</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -3232,7 +3232,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B203" t="str">
-        <v>TDSPK220KamillaKOMP5-8</v>
+        <v>TDSPK220OttepelOSN-8</v>
       </c>
       <c r="C203" t="str">
         <v/>
@@ -3246,13 +3246,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B204" t="str">
-        <v>TDSPK220OttepelOSN-8</v>
+        <v>TDSPK220ObitelLoveOSN2-8</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -3260,13 +3260,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B205" t="str">
-        <v>TDSPK220ObitelLoveOSN2-8</v>
+        <v>TDSPK220OdaNejnostiOSN2-8</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -3274,7 +3274,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B206" t="str">
-        <v>TDSPK220OdaNejnostiOSN2-8</v>
+        <v>TDSPK220CaribbeanOSN2-8</v>
       </c>
       <c r="C206" t="str">
         <v/>
@@ -3288,13 +3288,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B207" t="str">
-        <v>TDSPK220CaribbeanOSN2-8</v>
+        <v>TDSPK220NaomiOSN-8</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -3302,7 +3302,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B208" t="str">
-        <v>TDSPK220NaomiOSN-8</v>
+        <v>TDSPK220LegkoeDihanieOSN5-8</v>
       </c>
       <c r="C208" t="str">
         <v/>
@@ -3316,7 +3316,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B209" t="str">
-        <v>TDSPK220LegkoeDihanieOSN5-8</v>
+        <v>TDSPK220OdaNejnostiKOMP2-8</v>
       </c>
       <c r="C209" t="str">
         <v/>
@@ -3330,7 +3330,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B210" t="str">
-        <v>TDSPK220OdaNejnostiKOMP2-8</v>
+        <v>TDSPK220AdonisOSN2-8</v>
       </c>
       <c r="C210" t="str">
         <v/>
@@ -3344,7 +3344,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B211" t="str">
-        <v>TDSPK220AdonisOSN2-8</v>
+        <v>TDSPK220StoneKOMP2-8</v>
       </c>
       <c r="C211" t="str">
         <v/>
@@ -3358,7 +3358,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B212" t="str">
-        <v>TDSPK220StoneKOMP2-8</v>
+        <v>TDSPK220NostalgiKOMP4-8</v>
       </c>
       <c r="C212" t="str">
         <v/>
@@ -3372,7 +3372,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B213" t="str">
-        <v>TDSPK220NostalgiKOMP4-8</v>
+        <v>TDSPK220PachuliKOMP1-8</v>
       </c>
       <c r="C213" t="str">
         <v/>
@@ -3386,13 +3386,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B214" t="str">
-        <v>TDSPK220PachuliKOMP1-8</v>
+        <v>TDSPK220PachuliOSN1-8</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215">
@@ -3400,13 +3400,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B215" t="str">
-        <v>TDSPK220PachuliOSN1-8</v>
+        <v>TDSPK220GabrielOSN3-8</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -3414,7 +3414,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B216" t="str">
-        <v>TDSPK220GabrielOSN3-8</v>
+        <v>TDSPK220VitragiOSN3-8</v>
       </c>
       <c r="C216" t="str">
         <v/>
@@ -3428,7 +3428,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B217" t="str">
-        <v>TDSPK220VitragiOSN3-8</v>
+        <v>TDSPK220KarolinaOSN3-8</v>
       </c>
       <c r="C217" t="str">
         <v/>
@@ -3442,7 +3442,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B218" t="str">
-        <v>TDSPK220KarolinaOSN3-8</v>
+        <v>TDSPK220DavidKOMP3-8</v>
       </c>
       <c r="C218" t="str">
         <v/>
@@ -3456,7 +3456,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B219" t="str">
-        <v>TDSPK220DavidKOMP3-8</v>
+        <v>TDSPK220StepKOMP-8</v>
       </c>
       <c r="C219" t="str">
         <v/>
@@ -3470,13 +3470,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B220" t="str">
-        <v>TDSPK220StepKOMP-8</v>
+        <v>TDSPK220Kashmir1-8</v>
       </c>
       <c r="C220" t="str">
         <v/>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221">
@@ -3484,13 +3484,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B221" t="str">
-        <v>TDSPK220Kashmir1-8</v>
+        <v>TDSPK220SolnPticOSN-8</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3498,13 +3498,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B222" t="str">
-        <v>TDSPK220SolnPticOSN-8</v>
+        <v>TDSPK220LetniyZnoiOSN2-8</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223">
@@ -3512,13 +3512,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B223" t="str">
-        <v>TDSPK220LetniyZnoiOSN2-8</v>
+        <v>TDSPK220BalFlowersKOMP1-8</v>
       </c>
       <c r="C223" t="str">
         <v/>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -3526,7 +3526,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B224" t="str">
-        <v>TDSPK220BalFlowersKOMP1-8</v>
+        <v>TDSPK220EtudKOMP7-8</v>
       </c>
       <c r="C224" t="str">
         <v/>
@@ -3540,7 +3540,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B225" t="str">
-        <v>TDSPK220EtudKOMP7-8</v>
+        <v>TDSPK220AristokrOSN4-8</v>
       </c>
       <c r="C225" t="str">
         <v/>
@@ -3554,7 +3554,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B226" t="str">
-        <v>TDSPK220AristokrOSN4-8</v>
+        <v>TDSPK220ZataivDihanieOSN6-8</v>
       </c>
       <c r="C226" t="str">
         <v/>
@@ -3568,7 +3568,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B227" t="str">
-        <v>TDSPK220ZataivDihanieOSN6-8</v>
+        <v>TDSPK220SoloKOMP1-8</v>
       </c>
       <c r="C227" t="str">
         <v/>
@@ -3582,7 +3582,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B228" t="str">
-        <v>TDSPK220SoloKOMP1-8</v>
+        <v>TDSPK220OtbleskKOMP3-8</v>
       </c>
       <c r="C228" t="str">
         <v/>
@@ -3596,7 +3596,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B229" t="str">
-        <v>TDSPK220OtbleskKOMP3-8</v>
+        <v>TDSPK220ZataivDihanieKOMP6-8</v>
       </c>
       <c r="C229" t="str">
         <v/>
@@ -3610,7 +3610,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B230" t="str">
-        <v>TDSPK220ZataivDihanieKOMP6-8</v>
+        <v>TDSPK220TanecVetraOSN1-8</v>
       </c>
       <c r="C230" t="str">
         <v/>
@@ -3624,7 +3624,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B231" t="str">
-        <v>TDSPK220TanecVetraOSN1-8</v>
+        <v>TDSPK220PotokKOMP3-8</v>
       </c>
       <c r="C231" t="str">
         <v/>
@@ -3638,7 +3638,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B232" t="str">
-        <v>TDSPK220PotokKOMP3-8</v>
+        <v>TDSPK220VitragiKOMP3-8</v>
       </c>
       <c r="C232" t="str">
         <v/>
@@ -3652,7 +3652,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B233" t="str">
-        <v>TDSPK220VitragiKOMP3-8</v>
+        <v>TDSPK220AdamOSN2-8</v>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -3666,7 +3666,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B234" t="str">
-        <v>TDSPK220AdamOSN2-8</v>
+        <v>TDSPK220MusikVremOSN-8</v>
       </c>
       <c r="C234" t="str">
         <v/>
@@ -3680,7 +3680,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B235" t="str">
-        <v>TDSPK220MusikVremOSN-8</v>
+        <v>TDSPK220SovershenstvoKOMP1-8</v>
       </c>
       <c r="C235" t="str">
         <v/>
@@ -3694,13 +3694,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B236" t="str">
-        <v>TDSPK220SovershenstvoKOMP1-8</v>
+        <v>TDSPK220LegkoeDihanieKOMP5-8</v>
       </c>
       <c r="C236" t="str">
         <v/>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
@@ -3708,13 +3708,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B237" t="str">
-        <v>TDSPK220LegkoeDihanieKOMP5-8</v>
+        <v>TDSPK220StoneOSN2-8</v>
       </c>
       <c r="C237" t="str">
         <v/>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -3722,7 +3722,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B238" t="str">
-        <v>TDSPK220StoneOSN2-8</v>
+        <v>TDSPK220DavidOSN4-8</v>
       </c>
       <c r="C238" t="str">
         <v/>
@@ -3736,13 +3736,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B239" t="str">
-        <v>TDSPK220DavidOSN4-8</v>
+        <v>TDSPK220KamillaOSN5-8</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
@@ -3750,7 +3750,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B240" t="str">
-        <v>TDSPK220KamillaOSN5-8</v>
+        <v>TDSPK220AilaOSN3-8</v>
       </c>
       <c r="C240" t="str">
         <v/>
@@ -3764,13 +3764,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B241" t="str">
-        <v>TDSPK220AilaOSN3-8</v>
+        <v>TDSPK220Otbel120-8</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -3778,13 +3778,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B242" t="str">
-        <v>TDSPK220Otbel120-8</v>
+        <v>TDSPK220OtbleskOSN3-8</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
@@ -3792,13 +3792,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B243" t="str">
-        <v>TDSPK220OtbleskOSN3-8</v>
+        <v>TDSPK220AristokrKOMP8-8</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -3806,7 +3806,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B244" t="str">
-        <v>TDSPK220AristokrKOMP8-8</v>
+        <v>TDSPK220BlossomDreamsOSN2-8</v>
       </c>
       <c r="C244" t="str">
         <v/>
@@ -3820,7 +3820,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B245" t="str">
-        <v>TDSPK220BlossomDreamsOSN2-8</v>
+        <v>TDSPK220BalFlowersOSN1-8</v>
       </c>
       <c r="C245" t="str">
         <v/>
@@ -3834,13 +3834,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B246" t="str">
-        <v>TDSPK220BalFlowersOSN1-8</v>
+        <v>TDSPK220MetamorphosaOSN2-8</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247">
@@ -3848,13 +3848,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B247" t="str">
-        <v>TDSPK220MetamorphosaOSN2-8</v>
+        <v>TDSPK220EdemOSN-8</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -3862,7 +3862,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B248" t="str">
-        <v>TDSPK220EdemOSN-8</v>
+        <v>TDSPK220AdagioOSN4-8</v>
       </c>
       <c r="C248" t="str">
         <v/>
@@ -3876,7 +3876,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B249" t="str">
-        <v>TDSPK220AdagioOSN4-8</v>
+        <v>TDSPK220AristokrKOMP4-8</v>
       </c>
       <c r="C249" t="str">
         <v/>
@@ -3890,7 +3890,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B250" t="str">
-        <v>TDSPK220AristokrKOMP4-8</v>
+        <v>TDSPK220BuketChuvstvKOMP2-8</v>
       </c>
       <c r="C250" t="str">
         <v/>
@@ -3904,13 +3904,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B251" t="str">
-        <v>TDSPK220BuketChuvstvKOMP2-8</v>
+        <v>TDSPK220GabrielKOMP3-8</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252">
@@ -3918,13 +3918,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B252" t="str">
-        <v>TDSPK220GabrielKOMP3-8</v>
+        <v>TDSPK220EtudOSN5-8</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -3932,7 +3932,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B253" t="str">
-        <v>TDSPK220EtudOSN5-8</v>
+        <v>TDSPK220ZolotayaOSN-8</v>
       </c>
       <c r="C253" t="str">
         <v/>
@@ -3946,7 +3946,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B254" t="str">
-        <v>TDSPK220ZolotayaOSN-8</v>
+        <v>TDSPK220ZolotayaKOMP-8</v>
       </c>
       <c r="C254" t="str">
         <v/>
@@ -3960,7 +3960,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B255" t="str">
-        <v>TDSPK220ZolotayaKOMP-8</v>
+        <v>TDSPK220VozdSharOSN2-8</v>
       </c>
       <c r="C255" t="str">
         <v/>
@@ -3974,7 +3974,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B256" t="str">
-        <v>TDSPK220VozdSharOSN2-8</v>
+        <v>TDSPK220HappyDaysKOMP2-8</v>
       </c>
       <c r="C256" t="str">
         <v/>
@@ -3988,13 +3988,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B257" t="str">
-        <v>TDSPK220HappyDaysKOMP2-8</v>
+        <v>TDP150AngelGuard</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258">
@@ -4002,7 +4002,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B258" t="str">
-        <v>TDP150AngelGuard</v>
+        <v>TDP150Balerina</v>
       </c>
       <c r="C258" t="str">
         <v/>
@@ -4016,7 +4016,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B259" t="str">
-        <v>TDP150Balerina</v>
+        <v>TDP150BambukoviyMishka</v>
       </c>
       <c r="C259" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B260" t="str">
-        <v>TDP150BambukoviyMishka</v>
+        <v>TDP150Bike</v>
       </c>
       <c r="C260" t="str">
         <v/>
@@ -4044,13 +4044,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B261" t="str">
-        <v>TDP150Bike</v>
+        <v>TDP150Capybara</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -4058,7 +4058,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B262" t="str">
-        <v>TDP150Capybara</v>
+        <v>TDP150Championat</v>
       </c>
       <c r="C262" t="str">
         <v/>
@@ -4072,13 +4072,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B263" t="str">
-        <v>TDP150Championat</v>
+        <v>TDP150Charodeyki</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264">
@@ -4086,13 +4086,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B264" t="str">
-        <v>TDP150Charodeyki</v>
+        <v>TDP150Dinosaurus</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -4100,13 +4100,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B265" t="str">
-        <v>TDP150Dinosaurus</v>
+        <v>TDP150DobroeUtro</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
@@ -4114,13 +4114,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B266" t="str">
-        <v>TDP150DobroeUtro</v>
+        <v>TDP150DorojniyPatrul</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -4128,13 +4128,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B267" t="str">
-        <v>TDP150DorojniyPatrul</v>
+        <v>TDP150Era</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268">
@@ -4142,7 +4142,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B268" t="str">
-        <v>TDP150Era</v>
+        <v>TDP150Faline</v>
       </c>
       <c r="C268" t="str">
         <v/>
@@ -4156,13 +4156,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B269" t="str">
-        <v>TDP150Faline</v>
+        <v>TDP150Gamer</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -4170,7 +4170,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B270" t="str">
-        <v>TDP150Gamer</v>
+        <v>TDP150Gloss</v>
       </c>
       <c r="C270" t="str">
         <v/>
@@ -4184,7 +4184,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B271" t="str">
-        <v>TDP150Gloss</v>
+        <v>TDP150Gonki</v>
       </c>
       <c r="C271" t="str">
         <v/>
@@ -4198,13 +4198,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B272" t="str">
-        <v>TDP150Gonki</v>
+        <v>TDP150Graffiti</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273">
@@ -4212,13 +4212,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B273" t="str">
-        <v>TDP150Graffiti</v>
+        <v>TDP150Harley</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -4226,13 +4226,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B274" t="str">
-        <v>TDP150Harley</v>
+        <v>TDP150Hummer</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275">
@@ -4240,7 +4240,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B275" t="str">
-        <v>TDP150Hummer</v>
+        <v>TDP150igrok</v>
       </c>
       <c r="C275" t="str">
         <v/>
@@ -4254,13 +4254,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B276" t="str">
-        <v>TDP150igrok</v>
+        <v>TDP150JiteliLesa</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -4268,13 +4268,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B277" t="str">
-        <v>TDP150JiteliLesa</v>
+        <v>TDP150Kaktus</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
@@ -4282,13 +4282,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B278" t="str">
-        <v>TDP150Kaktus</v>
+        <v>TDP150Konstruktor</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -4296,7 +4296,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B279" t="str">
-        <v>TDP150Konstruktor</v>
+        <v>TDP150Koshki</v>
       </c>
       <c r="C279" t="str">
         <v/>
@@ -4310,7 +4310,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B280" t="str">
-        <v>TDP150Koshki</v>
+        <v>TDP150Kotiki</v>
       </c>
       <c r="C280" t="str">
         <v/>
@@ -4324,7 +4324,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B281" t="str">
-        <v>TDP150Kotiki</v>
+        <v>TDP150KrilatieKacheli</v>
       </c>
       <c r="C281" t="str">
         <v/>
@@ -4338,13 +4338,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B282" t="str">
-        <v>TDP150KrilatieKacheli</v>
+        <v>TDP150LakomkaKOMP</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283">
@@ -4352,7 +4352,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B283" t="str">
-        <v>TDP150LakomkaKOMP</v>
+        <v>TDP150LesnieNimfi</v>
       </c>
       <c r="C283" t="str">
         <v/>
@@ -4366,13 +4366,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B284" t="str">
-        <v>TDP150LesnieNimfi</v>
+        <v>TDP150Love</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -4380,7 +4380,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B285" t="str">
-        <v>TDP150Love</v>
+        <v>TDP150Manhattan</v>
       </c>
       <c r="C285" t="str">
         <v/>
@@ -4394,7 +4394,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B286" t="str">
-        <v>TDP150Manhattan</v>
+        <v>TDP150Milashki3</v>
       </c>
       <c r="C286" t="str">
         <v/>
@@ -4408,13 +4408,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B287" t="str">
-        <v>TDP150Milashki3</v>
+        <v>TDP150MirChudes</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
@@ -4422,7 +4422,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B288" t="str">
-        <v>TDP150MirChudes</v>
+        <v>TDP150MorskieObitateli</v>
       </c>
       <c r="C288" t="str">
         <v/>
@@ -4436,13 +4436,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B289" t="str">
-        <v>TDP150MorskieObitateli</v>
+        <v>TDP150MoyaZaika</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -4450,7 +4450,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B290" t="str">
-        <v>TDP150MoyaZaika</v>
+        <v>TDP150Neon</v>
       </c>
       <c r="C290" t="str">
         <v/>
@@ -4464,13 +4464,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B291" t="str">
-        <v>TDP150Neon</v>
+        <v>TDP150NochnieFonariki</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292">
@@ -4478,13 +4478,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B292" t="str">
-        <v>TDP150NochnieFonariki</v>
+        <v>TDP150Ocean</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -4492,7 +4492,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B293" t="str">
-        <v>TDP150Ocean</v>
+        <v>TDP150Otbelka</v>
       </c>
       <c r="C293" t="str">
         <v/>
@@ -4506,13 +4506,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B294" t="str">
-        <v>TDP150Otbelka</v>
+        <v>TDP150OtVinta</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295">
@@ -4520,7 +4520,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B295" t="str">
-        <v>TDP150OtVinta</v>
+        <v>TDP150Pehotinec</v>
       </c>
       <c r="C295" t="str">
         <v/>
@@ -4534,7 +4534,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B296" t="str">
-        <v>TDP150Pehotinec</v>
+        <v>TDP150Pingvie</v>
       </c>
       <c r="C296" t="str">
         <v/>
@@ -4548,13 +4548,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B297" t="str">
-        <v>TDP150Pingvie</v>
+        <v>TDP150Polet</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -4562,7 +4562,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B298" t="str">
-        <v>TDP150Polet</v>
+        <v>TDP150Polosatiki</v>
       </c>
       <c r="C298" t="str">
         <v/>
@@ -4576,13 +4576,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B299" t="str">
-        <v>TDP150Polosatiki</v>
+        <v>TDP150Princessa</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -4590,13 +4590,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B300" t="str">
-        <v>TDP150Princessa</v>
+        <v>TDP150Retro</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -4604,7 +4604,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B301" t="str">
-        <v>TDP150Retro</v>
+        <v>TDP150Romantica</v>
       </c>
       <c r="C301" t="str">
         <v/>
@@ -4618,13 +4618,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B302" t="str">
-        <v>TDP150Romantica</v>
+        <v>TDP150Skorost</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
@@ -4632,7 +4632,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B303" t="str">
-        <v>TDP150Skorost</v>
+        <v>TDP150SladkihSnov</v>
       </c>
       <c r="C303" t="str">
         <v/>
@@ -4646,7 +4646,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B304" t="str">
-        <v>TDP150SladkihSnov</v>
+        <v>TDP150SonyaKOMP</v>
       </c>
       <c r="C304" t="str">
         <v/>
@@ -4660,7 +4660,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B305" t="str">
-        <v>TDP150SonyaKOMP</v>
+        <v>TDP150SonyaOSNOV</v>
       </c>
       <c r="C305" t="str">
         <v/>
@@ -4674,7 +4674,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B306" t="str">
-        <v>TDP150SonyaOSNOV</v>
+        <v>TDP150SovyataKOMP</v>
       </c>
       <c r="C306" t="str">
         <v/>
@@ -4688,7 +4688,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B307" t="str">
-        <v>TDP150SovyataKOMP</v>
+        <v>TDP150Sport2</v>
       </c>
       <c r="C307" t="str">
         <v/>
@@ -4702,13 +4702,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B308" t="str">
-        <v>TDP150Sport2</v>
+        <v>TDP150StreetArt</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -4716,7 +4716,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B309" t="str">
-        <v>TDP150StreetArt</v>
+        <v>TDP150StreetRace</v>
       </c>
       <c r="C309" t="str">
         <v/>
@@ -4730,13 +4730,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B310" t="str">
-        <v>TDP150StreetRace</v>
+        <v>TDP150Sumerki</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311">
@@ -4744,7 +4744,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B311" t="str">
-        <v>TDP150Sumerki</v>
+        <v>TDP150SuperLady</v>
       </c>
       <c r="C311" t="str">
         <v/>
@@ -4758,7 +4758,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B312" t="str">
-        <v>TDP150SuperLady</v>
+        <v>TDP150SvetliyAngel</v>
       </c>
       <c r="C312" t="str">
         <v/>
@@ -4772,7 +4772,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B313" t="str">
-        <v>TDP150SvetliyAngel</v>
+        <v>TDP150Tank</v>
       </c>
       <c r="C313" t="str">
         <v/>
@@ -4786,13 +4786,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B314" t="str">
-        <v>TDP150Tank</v>
+        <v>TDP150Tirex</v>
       </c>
       <c r="C314" t="str">
         <v/>
       </c>
       <c r="D314">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -4800,7 +4800,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B315" t="str">
-        <v>TDP150Tirex</v>
+        <v>TDP150TownHouse</v>
       </c>
       <c r="C315" t="str">
         <v/>
@@ -4814,13 +4814,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B316" t="str">
-        <v>TDP150TownHouse</v>
+        <v>TDP150TsvetnieSni</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
@@ -4828,13 +4828,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B317" t="str">
-        <v>TDP150TsvetnieSni</v>
+        <v>TDP150Ulibka</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -4842,7 +4842,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B318" t="str">
-        <v>TDP150Ulibka</v>
+        <v>TDP150Ultra</v>
       </c>
       <c r="C318" t="str">
         <v/>
@@ -4856,13 +4856,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B319" t="str">
-        <v>TDP150Ultra</v>
+        <v>TDP150VanillaSkyCOMP</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
@@ -4870,13 +4870,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B320" t="str">
-        <v>TDP150VanillaSkyCOMP</v>
+        <v>TDP150VanillaSkyOSN</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -4884,13 +4884,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B321" t="str">
-        <v>TDP150VanillaSkyOSN</v>
+        <v>TDP150Volshebnici</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -4898,7 +4898,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B322" t="str">
-        <v>TDP150Volshebnici</v>
+        <v>TDP150Zayushki</v>
       </c>
       <c r="C322" t="str">
         <v/>
@@ -4912,7 +4912,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B323" t="str">
-        <v>TDP150Zayushki</v>
+        <v>TDP150ZvezdnayaPil</v>
       </c>
       <c r="C323" t="str">
         <v/>
@@ -4926,13 +4926,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B324" t="str">
-        <v>TDP150ZvezdnayaPil</v>
+        <v>TDP150ZvezdnoeNebo</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
@@ -4940,13 +4940,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B325" t="str">
-        <v>TDP150ZvezdnoeNebo</v>
+        <v>TDP150ZvezdochkaCOMP</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -4954,13 +4954,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B326" t="str">
-        <v>TDP150ZvezdochkaCOMP</v>
+        <v>TDPPKOchkiCOMP1</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
@@ -4968,7 +4968,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B327" t="str">
-        <v>TDPPKOchkiCOMP1</v>
+        <v>TDPPKPolnochOSN1</v>
       </c>
       <c r="C327" t="str">
         <v/>
@@ -4982,7 +4982,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B328" t="str">
-        <v>TDPPKPolnochOSN1</v>
+        <v>TDPPKPinkFlamingoOSN1</v>
       </c>
       <c r="C328" t="str">
         <v/>
@@ -4996,13 +4996,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B329" t="str">
-        <v>TDPPKPinkFlamingoOSN1</v>
+        <v>TDPPKZacharovanFlowerOSN1</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -5010,13 +5010,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B330" t="str">
-        <v>TDPPKZacharovanFlowerOSN1</v>
+        <v>TDPPKBananasOSN1</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="331">
@@ -5024,7 +5024,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B331" t="str">
-        <v>TDPPKBananasOSN1</v>
+        <v>TDPPKObnimashkiOSN1</v>
       </c>
       <c r="C331" t="str">
         <v/>
@@ -5038,13 +5038,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B332" t="str">
-        <v>TDPPKObnimashkiOSN1</v>
+        <v>TDPPKPassiaOSN1</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -5052,13 +5052,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B333" t="str">
-        <v>TDPPKPassiaOSN1</v>
+        <v>TDPPKKawaiCOMP1</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334">
@@ -5066,7 +5066,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B334" t="str">
-        <v>TDPPKKawaiCOMP1</v>
+        <v>TDPPKFelixCOMP1</v>
       </c>
       <c r="C334" t="str">
         <v/>
@@ -5080,13 +5080,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B335" t="str">
-        <v>TDPPKFelixCOMP1</v>
+        <v>TDPPKBotanicCOMP1</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -5094,7 +5094,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B336" t="str">
-        <v>TDPPKBotanicCOMP1</v>
+        <v>TDPPKTvorchestvoCOMP1</v>
       </c>
       <c r="C336" t="str">
         <v/>
@@ -5108,7 +5108,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B337" t="str">
-        <v>TDPPKTvorchestvoCOMP1</v>
+        <v>TDPPKCharlotteOSN2</v>
       </c>
       <c r="C337" t="str">
         <v/>
@@ -5122,13 +5122,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B338" t="str">
-        <v>TDPPKCharlotteOSN2</v>
+        <v>TDPPKHorizontOSN1</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339">
@@ -5136,13 +5136,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B339" t="str">
-        <v>TDPPKHorizontOSN1</v>
+        <v>TDPPKMissandeyaOSN1</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -5150,7 +5150,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B340" t="str">
-        <v>TDPPKMissandeyaOSN1</v>
+        <v>TDPPKProzrachVozdOSN1</v>
       </c>
       <c r="C340" t="str">
         <v/>
@@ -5164,7 +5164,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B341" t="str">
-        <v>TDPPKProzrachVozdOSN1</v>
+        <v>TDPPKKorgiOSN1</v>
       </c>
       <c r="C341" t="str">
         <v/>
@@ -5178,7 +5178,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B342" t="str">
-        <v>TDPPKKorgiOSN1</v>
+        <v>TDPPKBotanicaOSN1</v>
       </c>
       <c r="C342" t="str">
         <v/>
@@ -5192,7 +5192,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B343" t="str">
-        <v>TDPPKBotanicaOSN1</v>
+        <v>TDPPKFelixOSN1</v>
       </c>
       <c r="C343" t="str">
         <v/>
@@ -5206,13 +5206,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B344" t="str">
-        <v>TDPPKFelixOSN1</v>
+        <v>TDPPKPlavnieLiniiOSN1</v>
       </c>
       <c r="C344" t="str">
         <v/>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345">
@@ -5220,13 +5220,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B345" t="str">
-        <v>TDPPKPlavnieLiniiOSN1</v>
+        <v>TDPPKOrionOSN4</v>
       </c>
       <c r="C345" t="str">
         <v/>
       </c>
       <c r="D345">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -5234,7 +5234,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B346" t="str">
-        <v>TDPPKOrionOSN4</v>
+        <v>TDPPKMissandeyaCOMP1</v>
       </c>
       <c r="C346" t="str">
         <v/>
@@ -5248,7 +5248,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B347" t="str">
-        <v>TDPPKMissandeyaCOMP1</v>
+        <v>TDPPKTvorchestvoOSN1</v>
       </c>
       <c r="C347" t="str">
         <v/>
@@ -5262,7 +5262,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B348" t="str">
-        <v>TDPPKTvorchestvoOSN1</v>
+        <v>TDPPKKorgiCOMP1</v>
       </c>
       <c r="C348" t="str">
         <v/>
@@ -5276,13 +5276,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B349" t="str">
-        <v>TDPPKKorgiCOMP1</v>
+        <v>TDPPKKawaiOSN1</v>
       </c>
       <c r="C349" t="str">
         <v/>
       </c>
       <c r="D349">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350">
@@ -5290,7 +5290,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B350" t="str">
-        <v>TDPPKKawaiOSN1</v>
+        <v>TV-Tigers1-195x165</v>
       </c>
       <c r="C350" t="str">
         <v/>
@@ -5304,7 +5304,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B351" t="str">
-        <v>TV-Tigers1-195x165</v>
+        <v>TV-Laguna1-195x165</v>
       </c>
       <c r="C351" t="str">
         <v/>
@@ -5318,7 +5318,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B352" t="str">
-        <v>TV-Laguna1-195x165</v>
+        <v>TV-Cherepashki1-195x165</v>
       </c>
       <c r="C352" t="str">
         <v/>
@@ -5332,13 +5332,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B353" t="str">
-        <v>TV-Cherepashki1-195x165</v>
+        <v>TV-Nektar1-195x165</v>
       </c>
       <c r="C353" t="str">
         <v/>
       </c>
       <c r="D353">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -5346,13 +5346,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B354" t="str">
-        <v>TV-Nektar1-195x165</v>
+        <v>TV-NejniyDen1-195x165</v>
       </c>
       <c r="C354" t="str">
         <v/>
       </c>
       <c r="D354">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355">
@@ -5360,7 +5360,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B355" t="str">
-        <v>TV-NejniyDen1-195x165</v>
+        <v>TV-LetnNoch1-195x165</v>
       </c>
       <c r="C355" t="str">
         <v/>
@@ -5374,13 +5374,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B356" t="str">
-        <v>TV-LetnNoch1-195x165</v>
+        <v>TV-SpelieFrukti1-195x165</v>
       </c>
       <c r="C356" t="str">
         <v/>
       </c>
       <c r="D356">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -5388,13 +5388,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B357" t="str">
-        <v>TV-SpelieFrukti1-195x165</v>
+        <v>TV-Ailyn1-195x165</v>
       </c>
       <c r="C357" t="str">
         <v/>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358">
@@ -5402,7 +5402,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B358" t="str">
-        <v>TV-Ailyn1-195x165</v>
+        <v>TV-Pletenie2-195x165</v>
       </c>
       <c r="C358" t="str">
         <v/>
@@ -5416,7 +5416,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B359" t="str">
-        <v>TV-Pletenie2-195x165</v>
+        <v>TV-NejnoeUtro1-195x165</v>
       </c>
       <c r="C359" t="str">
         <v/>
@@ -5430,7 +5430,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B360" t="str">
-        <v>TV-NejnoeUtro1-195x165</v>
+        <v>TV-OvoshKorzin1-195x165</v>
       </c>
       <c r="C360" t="str">
         <v/>
@@ -5444,7 +5444,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B361" t="str">
-        <v>TV-OvoshKorzin1-195x165</v>
+        <v>TV-KitayPeyzazh1-195x165</v>
       </c>
       <c r="C361" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B362" t="str">
-        <v>TV-KitayPeyzazh1-195x165</v>
+        <v>TV-Ailyn2-195x165</v>
       </c>
       <c r="C362" t="str">
         <v/>
@@ -5472,7 +5472,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B363" t="str">
-        <v>TV-Ailyn2-195x165</v>
+        <v>TV-Asia1-195x165</v>
       </c>
       <c r="C363" t="str">
         <v/>
@@ -5486,7 +5486,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B364" t="str">
-        <v>TV-Asia1-195x165</v>
+        <v>TV-Kolyadki1-195x165</v>
       </c>
       <c r="C364" t="str">
         <v/>
@@ -5500,7 +5500,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B365" t="str">
-        <v>TV-Kolyadki1-195x165</v>
+        <v>TV-Elochka1-195x165</v>
       </c>
       <c r="C365" t="str">
         <v/>
@@ -5514,13 +5514,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B366" t="str">
-        <v>TV-Elochka1-195x165</v>
+        <v>TV-LimonKorzinka1-195x165</v>
       </c>
       <c r="C366" t="str">
         <v/>
       </c>
       <c r="D366">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -5528,13 +5528,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B367" t="str">
-        <v>TV-LimonKorzinka1-195x165</v>
+        <v>TV-Elis1-195x165</v>
       </c>
       <c r="C367" t="str">
         <v/>
       </c>
       <c r="D367">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
@@ -5542,7 +5542,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B368" t="str">
-        <v>TV-Elis1-195x165</v>
+        <v>TV-EchoVesni1-195x165</v>
       </c>
       <c r="C368" t="str">
         <v/>
@@ -5556,7 +5556,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B369" t="str">
-        <v>TV-EchoVesni1-195x165</v>
+        <v>TV-Hutoryanka1-195x165</v>
       </c>
       <c r="C369" t="str">
         <v/>
@@ -5570,13 +5570,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B370" t="str">
-        <v>TV-Hutoryanka1-195x165</v>
+        <v>TV-VesenMelody1-195x165</v>
       </c>
       <c r="C370" t="str">
         <v/>
       </c>
       <c r="D370">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -5584,7 +5584,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B371" t="str">
-        <v>TV-VesenMelody1-195x165</v>
+        <v>TV-PodCvetomRozi1-195x165</v>
       </c>
       <c r="C371" t="str">
         <v/>
@@ -5598,7 +5598,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B372" t="str">
-        <v>TV-PodCvetomRozi1-195x165</v>
+        <v>TV-Lavanda1-195x165</v>
       </c>
       <c r="C372" t="str">
         <v/>
@@ -5612,13 +5612,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B373" t="str">
-        <v>TV-Lavanda1-195x165</v>
+        <v>TV-SlegkimParom1-195x165</v>
       </c>
       <c r="C373" t="str">
         <v/>
       </c>
       <c r="D373">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374">
@@ -5626,7 +5626,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B374" t="str">
-        <v>TV-SlegkimParom1-195x165</v>
+        <v>TV-Mayolika1-195x165</v>
       </c>
       <c r="C374" t="str">
         <v/>
@@ -5640,7 +5640,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B375" t="str">
-        <v>TV-Mayolika1-195x165</v>
+        <v>TV-Tropicana1-195x165</v>
       </c>
       <c r="C375" t="str">
         <v/>
@@ -5654,13 +5654,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B376" t="str">
-        <v>TV-Tropicana1-195x165</v>
+        <v>TV-Kolyadki2-195x165</v>
       </c>
       <c r="C376" t="str">
         <v/>
       </c>
       <c r="D376">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -5668,13 +5668,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B377" t="str">
-        <v>TV-Kolyadki2-195x165</v>
+        <v>TV-LegkiyLepestok2-195x165</v>
       </c>
       <c r="C377" t="str">
         <v/>
       </c>
       <c r="D377">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378">
@@ -5682,13 +5682,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B378" t="str">
-        <v>TV-LegkiyLepestok2-195x165</v>
+        <v>TDPPKAllure1KOMP</v>
       </c>
       <c r="C378" t="str">
         <v/>
       </c>
       <c r="D378">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -5696,13 +5696,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B379" t="str">
-        <v>TDPPKAllure1KOMP</v>
+        <v>TDPPKAllure1OSN</v>
       </c>
       <c r="C379" t="str">
         <v/>
       </c>
       <c r="D379">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380">
@@ -5710,7 +5710,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B380" t="str">
-        <v>TDPPKAllure1OSN</v>
+        <v>TDPPKAzul1KOMP</v>
       </c>
       <c r="C380" t="str">
         <v/>
@@ -5724,13 +5724,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B381" t="str">
-        <v>TDPPKAzul1KOMP</v>
+        <v>TDPPKBelkanto6OSN</v>
       </c>
       <c r="C381" t="str">
         <v/>
       </c>
       <c r="D381">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -5738,7 +5738,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B382" t="str">
-        <v>TDPPKBelkanto6OSN</v>
+        <v>TDPPKBelosnejCvetok1OSN</v>
       </c>
       <c r="C382" t="str">
         <v/>
@@ -5752,7 +5752,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B383" t="str">
-        <v>TDPPKBelosnejCvetok1OSN</v>
+        <v>TDPPKBriena1OSN</v>
       </c>
       <c r="C383" t="str">
         <v/>
@@ -5766,7 +5766,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B384" t="str">
-        <v>TDPPKBriena1OSN</v>
+        <v>TDPPKEdem1OSN125</v>
       </c>
       <c r="C384" t="str">
         <v/>
@@ -5780,13 +5780,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B385" t="str">
-        <v>TDPPKEdem1OSN125</v>
+        <v>TDPPKEmotsii1KOMP</v>
       </c>
       <c r="C385" t="str">
         <v/>
       </c>
       <c r="D385">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -5794,7 +5794,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B386" t="str">
-        <v>TDPPKEmotsii1KOMP</v>
+        <v>TDPPKEmotsii1OSN</v>
       </c>
       <c r="C386" t="str">
         <v/>
@@ -5808,7 +5808,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B387" t="str">
-        <v>TDPPKEmotsii1OSN</v>
+        <v>TDPPKErnesto1KOMP</v>
       </c>
       <c r="C387" t="str">
         <v/>
@@ -5822,7 +5822,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B388" t="str">
-        <v>TDPPKErnesto1KOMP</v>
+        <v>TDPPKErnesto1OSN</v>
       </c>
       <c r="C388" t="str">
         <v/>
@@ -5836,7 +5836,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B389" t="str">
-        <v>TDPPKErnesto1OSN</v>
+        <v>TDPPKEsoterica1KOMP</v>
       </c>
       <c r="C389" t="str">
         <v/>
@@ -5850,7 +5850,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B390" t="str">
-        <v>TDPPKEsoterica1KOMP</v>
+        <v>TDPPKFlowerTriumf1KOMP</v>
       </c>
       <c r="C390" t="str">
         <v/>
@@ -5864,7 +5864,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B391" t="str">
-        <v>TDPPKFlowerTriumf1KOMP</v>
+        <v>TDPPKFlowerTriumf1OSN</v>
       </c>
       <c r="C391" t="str">
         <v/>
@@ -5878,7 +5878,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B392" t="str">
-        <v>TDPPKFlowerTriumf1OSN</v>
+        <v>TDPPKFreilina1OSN</v>
       </c>
       <c r="C392" t="str">
         <v/>
@@ -5892,7 +5892,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B393" t="str">
-        <v>TDPPKFreilina1OSN</v>
+        <v>TDPPKGavana1OSN</v>
       </c>
       <c r="C393" t="str">
         <v/>
@@ -5906,13 +5906,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B394" t="str">
-        <v>TDPPKGavana1OSN</v>
+        <v>TDPPKGossypium1OSN</v>
       </c>
       <c r="C394" t="str">
         <v/>
       </c>
       <c r="D394">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -5920,7 +5920,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B395" t="str">
-        <v>TDPPKGossypium1OSN</v>
+        <v>TDPPKKaribi1OSN</v>
       </c>
       <c r="C395" t="str">
         <v/>
@@ -5934,7 +5934,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B396" t="str">
-        <v>TDPPKKaribi1OSN</v>
+        <v>TDPPKKeniya4OSN</v>
       </c>
       <c r="C396" t="str">
         <v/>
@@ -5948,7 +5948,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B397" t="str">
-        <v>TDPPKKeniya4OSN</v>
+        <v>TDPPKKolorit1OSN</v>
       </c>
       <c r="C397" t="str">
         <v/>
@@ -5962,13 +5962,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B398" t="str">
-        <v>TDPPKKolorit1OSN</v>
+        <v>TDPPKLetniiZnoi1OSN</v>
       </c>
       <c r="C398" t="str">
         <v/>
       </c>
       <c r="D398">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
@@ -5976,13 +5976,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B399" t="str">
-        <v>TDPPKLetniiZnoi1OSN</v>
+        <v>TDPPKLike3OSN</v>
       </c>
       <c r="C399" t="str">
         <v/>
       </c>
       <c r="D399">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -5990,13 +5990,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B400" t="str">
-        <v>TDPPKLike3OSN</v>
+        <v>TDPPKMiliiMishka1KOMP</v>
       </c>
       <c r="C400" t="str">
         <v/>
       </c>
       <c r="D400">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401">
@@ -6004,13 +6004,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B401" t="str">
-        <v>TDPPKMiliiMishka1KOMP</v>
+        <v>TDPPKMonohrom15OSN</v>
       </c>
       <c r="C401" t="str">
         <v/>
       </c>
       <c r="D401">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -6018,13 +6018,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B402" t="str">
-        <v>TDPPKMonohrom15OSN</v>
+        <v>TDPPKNochnoiPolet1OSN</v>
       </c>
       <c r="C402" t="str">
         <v/>
       </c>
       <c r="D402">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403">
@@ -6032,13 +6032,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B403" t="str">
-        <v>TDPPKNochnoiPolet1OSN</v>
+        <v>TDPPKOcherk1OSN</v>
       </c>
       <c r="C403" t="str">
         <v/>
       </c>
       <c r="D403">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -6046,13 +6046,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B404" t="str">
-        <v>TDPPKOcherk1OSN</v>
+        <v>TDPPKOchki1OSN</v>
       </c>
       <c r="C404" t="str">
         <v/>
       </c>
       <c r="D404">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405">
@@ -6060,13 +6060,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B405" t="str">
-        <v>TDPPKOchki1OSN</v>
+        <v>TDPPKOdaNejnosti1OSN125</v>
       </c>
       <c r="C405" t="str">
         <v/>
       </c>
       <c r="D405">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -6074,7 +6074,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B406" t="str">
-        <v>TDPPKOdaNejnosti1OSN125</v>
+        <v>TDPPKOpavshayaListva1OSN</v>
       </c>
       <c r="C406" t="str">
         <v/>
@@ -6088,13 +6088,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B407" t="str">
-        <v>TDPPKOpavshayaListva1OSN</v>
+        <v>TDPPKOtblesk1OSN</v>
       </c>
       <c r="C407" t="str">
         <v/>
       </c>
       <c r="D407">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408">
@@ -6102,13 +6102,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B408" t="str">
-        <v>TDPPKOtblesk1OSN</v>
+        <v>TDPPKPalitraRadosti1OSN</v>
       </c>
       <c r="C408" t="str">
         <v/>
       </c>
       <c r="D408">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -6116,7 +6116,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B409" t="str">
-        <v>TDPPKPalitraRadosti1OSN</v>
+        <v>TDPPKPeisli16OSN</v>
       </c>
       <c r="C409" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B410" t="str">
-        <v>TDPPKPeisli16OSN</v>
+        <v>TDPPKPervoeSvidanie1OSN</v>
       </c>
       <c r="C410" t="str">
         <v/>
       </c>
       <c r="D410">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411">
@@ -6144,7 +6144,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B411" t="str">
-        <v>TDPPKPervoeSvidanie1OSN</v>
+        <v>TDPPKPodvodTsarstvo1KOMP</v>
       </c>
       <c r="C411" t="str">
         <v/>
@@ -6158,7 +6158,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B412" t="str">
-        <v>TDPPKPodvodTsarstvo1KOMP</v>
+        <v>TDPPKPodvodTsarstvo1OSN</v>
       </c>
       <c r="C412" t="str">
         <v/>
@@ -6172,7 +6172,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B413" t="str">
-        <v>TDPPKPodvodTsarstvo1OSN</v>
+        <v>TDPPKPotok1OSN</v>
       </c>
       <c r="C413" t="str">
         <v/>
@@ -6186,13 +6186,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B414" t="str">
-        <v>TDPPKPotok1OSN</v>
+        <v>TDPPKSchastlivieDni1OSN125</v>
       </c>
       <c r="C414" t="str">
         <v/>
       </c>
       <c r="D414">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -6200,7 +6200,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B415" t="str">
-        <v>TDPPKSchastlivieDni1OSN125</v>
+        <v>TDPPKSonAfroditi1OSN</v>
       </c>
       <c r="C415" t="str">
         <v/>
@@ -6214,13 +6214,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B416" t="str">
-        <v>TDPPKSonAfroditi1OSN</v>
+        <v>TDPPKSozidanie1OSN</v>
       </c>
       <c r="C416" t="str">
         <v/>
       </c>
       <c r="D416">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417">
@@ -6228,13 +6228,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B417" t="str">
-        <v>TDPPKSozidanie1OSN</v>
+        <v>TDPPKTainstvSad1OSN</v>
       </c>
       <c r="C417" t="str">
         <v/>
       </c>
       <c r="D417">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -6242,7 +6242,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B418" t="str">
-        <v>TDPPKTainstvSad1OSN</v>
+        <v>TDPPKVesenSkazka1OSN</v>
       </c>
       <c r="C418" t="str">
         <v/>
@@ -6256,7 +6256,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B419" t="str">
-        <v>TDPPKVesenSkazka1OSN</v>
+        <v>TDPPKVesennPolyana1OSN</v>
       </c>
       <c r="C419" t="str">
         <v/>
@@ -6270,13 +6270,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B420" t="str">
-        <v>TDPPKVesennPolyana1OSN</v>
+        <v>TDPPKViola1OSN</v>
       </c>
       <c r="C420" t="str">
         <v/>
       </c>
       <c r="D420">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421">
@@ -6284,7 +6284,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B421" t="str">
-        <v>TDPPKViola1OSN</v>
+        <v>TDPPKViola2OSN</v>
       </c>
       <c r="C421" t="str">
         <v/>
@@ -6298,13 +6298,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B422" t="str">
-        <v>TDPPKViola2OSN</v>
+        <v>TDPPKVishnya1OSN</v>
       </c>
       <c r="C422" t="str">
         <v/>
       </c>
       <c r="D422">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -6312,13 +6312,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B423" t="str">
-        <v>TDPPKVishnya1OSN</v>
+        <v>TDPPKVitragi1KOMP125</v>
       </c>
       <c r="C423" t="str">
         <v/>
       </c>
       <c r="D423">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424">
@@ -6326,13 +6326,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B424" t="str">
-        <v>TDPPKVitragi1KOMP125</v>
+        <v>TDPPKVlublenCorgi1KOMP</v>
       </c>
       <c r="C424" t="str">
         <v/>
       </c>
       <c r="D424">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -6340,13 +6340,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B425" t="str">
-        <v>TDPPKVlublenCorgi1KOMP</v>
+        <v>TDPPKVlublenCorgi1OSN</v>
       </c>
       <c r="C425" t="str">
         <v/>
       </c>
       <c r="D425">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426">
@@ -6354,13 +6354,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B426" t="str">
-        <v>TDPPKVlublenCorgi1OSN</v>
+        <v>TDPPKVostochnayaSkazka1OSN</v>
       </c>
       <c r="C426" t="str">
         <v/>
       </c>
       <c r="D426">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -6368,13 +6368,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B427" t="str">
-        <v>TDPPKVostochnayaSkazka1OSN</v>
+        <v>TDPPKYlibnis1KOMP</v>
       </c>
       <c r="C427" t="str">
         <v/>
       </c>
       <c r="D427">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="428">
@@ -6382,7 +6382,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B428" t="str">
-        <v>TDPPKYlibnis1KOMP</v>
+        <v>TDPPKYlibnis1OSN</v>
       </c>
       <c r="C428" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B429" t="str">
-        <v>TDPPKYlibnis1OSN</v>
+        <v>TDM-greyViolet</v>
       </c>
       <c r="C429" t="str">
         <v/>
@@ -6410,7 +6410,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B430" t="str">
-        <v>TDM-greyViolet</v>
+        <v>TDM-lightBlue</v>
       </c>
       <c r="C430" t="str">
         <v/>
@@ -6424,13 +6424,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B431" t="str">
-        <v>TDM-lightBlue</v>
+        <v>TDM-pink</v>
       </c>
       <c r="C431" t="str">
         <v/>
       </c>
       <c r="D431">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -6438,7 +6438,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B432" t="str">
-        <v>TDM-pink</v>
+        <v>TDPPKAlfredo1OSN</v>
       </c>
       <c r="C432" t="str">
         <v/>
@@ -6452,13 +6452,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B433" t="str">
-        <v>TDPPKAlfredo1OSN</v>
+        <v>TDPPKArbyzi1KOMP</v>
       </c>
       <c r="C433" t="str">
         <v/>
       </c>
       <c r="D433">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434">
@@ -6466,7 +6466,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B434" t="str">
-        <v>TDPPKArbyzi1KOMP</v>
+        <v>TDPPKArbyzi1OSN</v>
       </c>
       <c r="C434" t="str">
         <v/>
@@ -6480,7 +6480,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B435" t="str">
-        <v>TDPPKArbyzi1OSN</v>
+        <v>TDPPKArno1OSN</v>
       </c>
       <c r="C435" t="str">
         <v/>
@@ -6494,13 +6494,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B436" t="str">
-        <v>TDPPKArno1OSN</v>
+        <v>TDPPKAura1OSN</v>
       </c>
       <c r="C436" t="str">
         <v/>
       </c>
       <c r="D436">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -6508,7 +6508,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B437" t="str">
-        <v>TDPPKAura1OSN</v>
+        <v>TDPPKAureliya1KOMP</v>
       </c>
       <c r="C437" t="str">
         <v/>
@@ -6522,7 +6522,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B438" t="str">
-        <v>TDPPKAureliya1KOMP</v>
+        <v>TDPPKAvokado1KOMP</v>
       </c>
       <c r="C438" t="str">
         <v/>
@@ -6536,13 +6536,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B439" t="str">
-        <v>TDPPKAvokado1KOMP</v>
+        <v>TDPPKBalCvetov3KOMP</v>
       </c>
       <c r="C439" t="str">
         <v/>
       </c>
       <c r="D439">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -6550,7 +6550,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B440" t="str">
-        <v>TDPPKBalCvetov3KOMP</v>
+        <v>TDPPKBalladaOLubvi1OSN</v>
       </c>
       <c r="C440" t="str">
         <v/>
@@ -6564,7 +6564,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B441" t="str">
-        <v>TDPPKBalladaOLubvi1OSN</v>
+        <v>TDPPKBeliiSad1KOMP</v>
       </c>
       <c r="C441" t="str">
         <v/>
@@ -6578,13 +6578,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B442" t="str">
-        <v>TDPPKBeliiSad1KOMP</v>
+        <v>TDPPKBeliiTigr1OSN</v>
       </c>
       <c r="C442" t="str">
         <v/>
       </c>
       <c r="D442">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443">
@@ -6592,13 +6592,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B443" t="str">
-        <v>TDPPKBeliiTigr1OSN</v>
+        <v>TDPPKBlagoyhanie1OSN</v>
       </c>
       <c r="C443" t="str">
         <v/>
       </c>
       <c r="D443">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -6606,7 +6606,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B444" t="str">
-        <v>TDPPKBlagoyhanie1OSN</v>
+        <v>TDPPKCharodeyka1OSN</v>
       </c>
       <c r="C444" t="str">
         <v/>
@@ -6620,7 +6620,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B445" t="str">
-        <v>TDPPKCharodeyka1OSN</v>
+        <v>TDPPKCvetushieMechti1OSN125</v>
       </c>
       <c r="C445" t="str">
         <v/>
@@ -6634,7 +6634,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B446" t="str">
-        <v>TDPPKCvetushieMechti1OSN125</v>
+        <v>TDPPKDebut1OSN</v>
       </c>
       <c r="C446" t="str">
         <v/>
@@ -6648,7 +6648,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B447" t="str">
-        <v>TDPPKDebut1OSN</v>
+        <v>TDPPKDilara1OSN</v>
       </c>
       <c r="C447" t="str">
         <v/>
@@ -6662,7 +6662,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B448" t="str">
-        <v>TDPPKDilara1OSN</v>
+        <v>TDPPKDrakon1OSN</v>
       </c>
       <c r="C448" t="str">
         <v/>
@@ -6676,7 +6676,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B449" t="str">
-        <v>TDPPKDrakon1OSN</v>
+        <v>TDPPKEco4KOMP</v>
       </c>
       <c r="C449" t="str">
         <v/>
@@ -6690,7 +6690,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B450" t="str">
-        <v>TDPPKEco4KOMP</v>
+        <v>TDPPKEco13OSN</v>
       </c>
       <c r="C450" t="str">
         <v/>
@@ -6704,7 +6704,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B451" t="str">
-        <v>TDPPKEco13OSN</v>
+        <v>TDPPKEco15OSN</v>
       </c>
       <c r="C451" t="str">
         <v/>
@@ -6718,7 +6718,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B452" t="str">
-        <v>TDPPKEco15OSN</v>
+        <v>TDPPKElison1KOMP</v>
       </c>
       <c r="C452" t="str">
         <v/>
@@ -6732,7 +6732,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B453" t="str">
-        <v>TDPPKElison1KOMP</v>
+        <v>TDPPKFrezii1OSN</v>
       </c>
       <c r="C453" t="str">
         <v/>
@@ -6746,7 +6746,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B454" t="str">
-        <v>TDPPKFrezii1OSN</v>
+        <v>TDPPKGerbarii1OSN</v>
       </c>
       <c r="C454" t="str">
         <v/>
@@ -6760,13 +6760,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B455" t="str">
-        <v>TDPPKGerbarii1OSN</v>
+        <v>TDPPKGystav1OSN</v>
       </c>
       <c r="C455" t="str">
         <v/>
       </c>
       <c r="D455">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -6774,7 +6774,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B456" t="str">
-        <v>TDPPKGystav1OSN</v>
+        <v>TDPPKIlluminaciya1OSN</v>
       </c>
       <c r="C456" t="str">
         <v/>
@@ -6788,7 +6788,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B457" t="str">
-        <v>TDPPKIlluminaciya1OSN</v>
+        <v>TDPPKInteres1KOMP</v>
       </c>
       <c r="C457" t="str">
         <v/>
@@ -6802,7 +6802,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B458" t="str">
-        <v>TDPPKInteres1KOMP</v>
+        <v>TDPPKInteres1OSN</v>
       </c>
       <c r="C458" t="str">
         <v/>
@@ -6816,7 +6816,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B459" t="str">
-        <v>TDPPKInteres1OSN</v>
+        <v>TDPPKIskushenie1KOMP</v>
       </c>
       <c r="C459" t="str">
         <v/>
@@ -6830,7 +6830,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B460" t="str">
-        <v>TDPPKIskushenie1KOMP</v>
+        <v>TDPPKKessi1KOMP</v>
       </c>
       <c r="C460" t="str">
         <v/>
@@ -6844,13 +6844,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B461" t="str">
-        <v>TDPPKKessi1KOMP</v>
+        <v>TDPPKKvartc1OSN</v>
       </c>
       <c r="C461" t="str">
         <v/>
       </c>
       <c r="D461">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -6858,7 +6858,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B462" t="str">
-        <v>TDPPKKvartc1OSN</v>
+        <v>TDPPKListopad1OSN</v>
       </c>
       <c r="C462" t="str">
         <v/>
@@ -6872,7 +6872,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B463" t="str">
-        <v>TDPPKListopad1OSN</v>
+        <v>TDPPKMarsala1OSN</v>
       </c>
       <c r="C463" t="str">
         <v/>
@@ -6886,13 +6886,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B464" t="str">
-        <v>TDPPKMarsala1OSN</v>
+        <v>TDPPKMuzei1KOMP</v>
       </c>
       <c r="C464" t="str">
         <v/>
       </c>
       <c r="D464">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465">
@@ -6900,13 +6900,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B465" t="str">
-        <v>TDPPKMuzei1KOMP</v>
+        <v>TDPPKNamaste1KOMP</v>
       </c>
       <c r="C465" t="str">
         <v/>
       </c>
       <c r="D465">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -6914,7 +6914,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B466" t="str">
-        <v>TDPPKNamaste1KOMP</v>
+        <v>TDPPKNamaste1OSN</v>
       </c>
       <c r="C466" t="str">
         <v/>
@@ -6928,7 +6928,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B467" t="str">
-        <v>TDPPKNamaste1OSN</v>
+        <v>TDPPKObitelLubvi1KOMP</v>
       </c>
       <c r="C467" t="str">
         <v/>
@@ -6942,7 +6942,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B468" t="str">
-        <v>TDPPKObitelLubvi1KOMP</v>
+        <v>TDPPKOrion1OSN</v>
       </c>
       <c r="C468" t="str">
         <v/>
@@ -6956,7 +6956,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B469" t="str">
-        <v>TDPPKOrion1OSN</v>
+        <v>TDPPKPishnayaSiren1KOMP</v>
       </c>
       <c r="C469" t="str">
         <v/>
@@ -6970,7 +6970,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B470" t="str">
-        <v>TDPPKPishnayaSiren1KOMP</v>
+        <v>TDPPKSiyanieNochi3OSN</v>
       </c>
       <c r="C470" t="str">
         <v/>
@@ -6984,7 +6984,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B471" t="str">
-        <v>TDPPKSiyanieNochi3OSN</v>
+        <v>TDPPKSnejnoeSiyanie1OSN</v>
       </c>
       <c r="C471" t="str">
         <v/>
@@ -6998,7 +6998,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B472" t="str">
-        <v>TDPPKSnejnoeSiyanie1OSN</v>
+        <v>TDPPKSolnechniePtici2OSN</v>
       </c>
       <c r="C472" t="str">
         <v/>
@@ -7012,7 +7012,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B473" t="str">
-        <v>TDPPKSolnechniePtici2OSN</v>
+        <v>TDPPKTekstura1OSN</v>
       </c>
       <c r="C473" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B474" t="str">
-        <v>TDPPKTekstura1OSN</v>
+        <v>TDPPKTown1OSN</v>
       </c>
       <c r="C474" t="str">
         <v/>
@@ -7040,7 +7040,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B475" t="str">
-        <v>TDPPKTown1OSN</v>
+        <v>TDPPKUrban2OSN</v>
       </c>
       <c r="C475" t="str">
         <v/>
@@ -7054,13 +7054,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B476" t="str">
-        <v>TDPPKUrban2OSN</v>
+        <v>TDPPKVechernieGrezi1OSN</v>
       </c>
       <c r="C476" t="str">
         <v/>
       </c>
       <c r="D476">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
@@ -7068,7 +7068,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B477" t="str">
-        <v>TDPPKVechernieGrezi1OSN</v>
+        <v>TDPPKVeselieDruzya1OSN</v>
       </c>
       <c r="C477" t="str">
         <v/>
@@ -7082,13 +7082,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B478" t="str">
-        <v>TDPPKVeselieDruzya1OSN</v>
+        <v>TDPPKViraj1KOMP</v>
       </c>
       <c r="C478" t="str">
         <v/>
       </c>
       <c r="D478">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -7096,7 +7096,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B479" t="str">
-        <v>TDPPKViraj1KOMP</v>
+        <v>TDPPKVivian1OSN</v>
       </c>
       <c r="C479" t="str">
         <v/>
@@ -7110,13 +7110,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B480" t="str">
-        <v>TDPPKVivian1OSN</v>
+        <v>TDPPKVoVlastiKrasoti1OSN</v>
       </c>
       <c r="C480" t="str">
         <v/>
       </c>
       <c r="D480">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="481">
@@ -7124,13 +7124,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B481" t="str">
-        <v>TDPPKVoVlastiKrasoti1OSN</v>
+        <v>TDPPKVpechatlenie1OSN</v>
       </c>
       <c r="C481" t="str">
         <v/>
       </c>
       <c r="D481">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -7138,13 +7138,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B482" t="str">
-        <v>TDPPKVpechatlenie1OSN</v>
+        <v>TDPPKZazerkalie1OSN</v>
       </c>
       <c r="C482" t="str">
         <v/>
       </c>
       <c r="D482">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="483">
@@ -7152,13 +7152,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B483" t="str">
-        <v>TDPPKZazerkalie1OSN</v>
+        <v>TDSPK220MaikoOSN4</v>
       </c>
       <c r="C483" t="str">
         <v/>
       </c>
       <c r="D483">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484">
@@ -7166,7 +7166,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B484" t="str">
-        <v>TDSPK220MaikoOSN4</v>
+        <v>TDSPK220EtudKOMP5</v>
       </c>
       <c r="C484" t="str">
         <v/>
@@ -7180,7 +7180,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B485" t="str">
-        <v>TDSPK220EtudKOMP5</v>
+        <v>TDSPK220GoldDayOSN2</v>
       </c>
       <c r="C485" t="str">
         <v/>
@@ -7194,7 +7194,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B486" t="str">
-        <v>TDSPK220GoldDayOSN2</v>
+        <v>TDSPK220MonohromOSN13</v>
       </c>
       <c r="C486" t="str">
         <v/>
@@ -7208,7 +7208,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B487" t="str">
-        <v>TDSPK220MonohromOSN13</v>
+        <v>TDSPK220ZabvenieKOMP2</v>
       </c>
       <c r="C487" t="str">
         <v/>
@@ -7222,13 +7222,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B488" t="str">
-        <v>TDSPK220ZabvenieKOMP2</v>
+        <v>TDSPK220ZabvenieOSN2</v>
       </c>
       <c r="C488" t="str">
         <v/>
       </c>
       <c r="D488">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="489">
@@ -7236,7 +7236,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B489" t="str">
-        <v>TDSPK220ZabvenieOSN2</v>
+        <v>TDSPK235BelyyBuketKOMP2</v>
       </c>
       <c r="C489" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B490" t="str">
-        <v>TDSPK235BelyyBuketKOMP2</v>
+        <v>TDSPK235BelyyBuketOSN2</v>
       </c>
       <c r="C490" t="str">
         <v/>
@@ -7264,7 +7264,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B491" t="str">
-        <v>TDSPK235BelyyBuketOSN2</v>
+        <v>TDSPK235DlinnayaNochKOMP2</v>
       </c>
       <c r="C491" t="str">
         <v/>
@@ -7278,7 +7278,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B492" t="str">
-        <v>TDSPK235DlinnayaNochKOMP2</v>
+        <v>TDSPK235DlinnayaNochOSN2</v>
       </c>
       <c r="C492" t="str">
         <v/>
@@ -7292,7 +7292,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B493" t="str">
-        <v>TDSPK235DlinnayaNochOSN2</v>
+        <v>TDSPK235DzhinniKOMP2</v>
       </c>
       <c r="C493" t="str">
         <v/>
@@ -7306,7 +7306,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B494" t="str">
-        <v>TDSPK235DzhinniKOMP2</v>
+        <v>TDSPK235DzhinniOSN2</v>
       </c>
       <c r="C494" t="str">
         <v/>
@@ -7320,7 +7320,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B495" t="str">
-        <v>TDSPK235DzhinniOSN2</v>
+        <v>TDSPK235EstellaOSN2</v>
       </c>
       <c r="C495" t="str">
         <v/>
@@ -7334,7 +7334,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B496" t="str">
-        <v>TDSPK235EstellaOSN2</v>
+        <v>TDSPK235GoldenKOMP2</v>
       </c>
       <c r="C496" t="str">
         <v/>
@@ -7348,7 +7348,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B497" t="str">
-        <v>TDSPK235GoldenKOMP2</v>
+        <v>TDSPK235LepestokKOMP2</v>
       </c>
       <c r="C497" t="str">
         <v/>
@@ -7362,7 +7362,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B498" t="str">
-        <v>TDSPK235LepestokKOMP2</v>
+        <v>TDSPK235LepestokOSN2</v>
       </c>
       <c r="C498" t="str">
         <v/>
@@ -7376,13 +7376,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B499" t="str">
-        <v>TDSPK235LepestokOSN2</v>
+        <v>TDSPK235LuchSolntsaKOMP2</v>
       </c>
       <c r="C499" t="str">
         <v/>
       </c>
       <c r="D499">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -7390,13 +7390,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B500" t="str">
-        <v>TDSPK235LuchSolntsaKOMP2</v>
+        <v>TDSPK235LuchSolntsaOSN2</v>
       </c>
       <c r="C500" t="str">
         <v/>
       </c>
       <c r="D500">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="501">
@@ -7404,7 +7404,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B501" t="str">
-        <v>TDSPK235LuchSolntsaOSN2</v>
+        <v>TDSPK235MilagrosOSN2</v>
       </c>
       <c r="C501" t="str">
         <v/>
@@ -7418,7 +7418,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B502" t="str">
-        <v>TDSPK235MilagrosOSN2</v>
+        <v>TDSPK235NinelKOMP6</v>
       </c>
       <c r="C502" t="str">
         <v/>
@@ -7432,7 +7432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B503" t="str">
-        <v>TDSPK235NinelKOMP6</v>
+        <v>TDSPK235NinelKOMP8</v>
       </c>
       <c r="C503" t="str">
         <v/>
@@ -7446,7 +7446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B504" t="str">
-        <v>TDSPK235NinelKOMP8</v>
+        <v>TDSPK235PassazhKOMP2</v>
       </c>
       <c r="C504" t="str">
         <v/>
@@ -7460,7 +7460,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B505" t="str">
-        <v>TDSPK235PassazhKOMP2</v>
+        <v>TDSPK235PassazhOSN2</v>
       </c>
       <c r="C505" t="str">
         <v/>
@@ -7474,7 +7474,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B506" t="str">
-        <v>TDSPK235PassazhOSN2</v>
+        <v>TDSPK235PlenitelnayaGratsiyaKOMP2</v>
       </c>
       <c r="C506" t="str">
         <v/>
@@ -7488,7 +7488,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B507" t="str">
-        <v>TDSPK235PlenitelnayaGratsiyaKOMP2</v>
+        <v>TDSPK235PlenitelnayaGratsiyaOSN2</v>
       </c>
       <c r="C507" t="str">
         <v/>
@@ -7502,7 +7502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B508" t="str">
-        <v>TDSPK235PlenitelnayaGratsiyaOSN2</v>
+        <v>TDSPK235PoeziyaKrasotiOSN2</v>
       </c>
       <c r="C508" t="str">
         <v/>
@@ -7516,7 +7516,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B509" t="str">
-        <v>TDSPK235PoeziyaKrasotiOSN2</v>
+        <v>TDSPK235RavnovesieKOMP2</v>
       </c>
       <c r="C509" t="str">
         <v/>
@@ -7530,7 +7530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B510" t="str">
-        <v>TDSPK235RavnovesieKOMP2</v>
+        <v>TDSPK235RavnovesieOSN2</v>
       </c>
       <c r="C510" t="str">
         <v/>
@@ -7544,7 +7544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B511" t="str">
-        <v>TDSPK235RavnovesieOSN2</v>
+        <v>TDSPK235SimmetriyaOSN3</v>
       </c>
       <c r="C511" t="str">
         <v/>
@@ -7558,7 +7558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B512" t="str">
-        <v>TDSPK235SimmetriyaOSN3</v>
+        <v>TDSPK235TisnenieOSN3</v>
       </c>
       <c r="C512" t="str">
         <v/>
@@ -7572,7 +7572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B513" t="str">
-        <v>TDSPK235TisnenieOSN3</v>
+        <v>TDSPK235TsvetochnyyLugKOMP2</v>
       </c>
       <c r="C513" t="str">
         <v/>
@@ -7586,7 +7586,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B514" t="str">
-        <v>TDSPK235TsvetochnyyLugKOMP2</v>
+        <v>TDSPK235TsvetochnyyLugOSN2</v>
       </c>
       <c r="C514" t="str">
         <v/>
@@ -7600,7 +7600,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B515" t="str">
-        <v>TDSPK235TsvetochnyyLugOSN2</v>
+        <v>TDSPK235TsvetushchayaMelodiyaKOMP2</v>
       </c>
       <c r="C515" t="str">
         <v/>
@@ -7614,7 +7614,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B516" t="str">
-        <v>TDSPK235TsvetushchayaMelodiyaKOMP2</v>
+        <v>TDSPK235TsvetushchayaMelodiyaOSN2</v>
       </c>
       <c r="C516" t="str">
         <v/>
@@ -7628,7 +7628,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B517" t="str">
-        <v>TDSPK235TsvetushchayaMelodiyaOSN2</v>
+        <v>TDSPK235VzmakhKistiKOMP3</v>
       </c>
       <c r="C517" t="str">
         <v/>
@@ -7642,7 +7642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B518" t="str">
-        <v>TDSPK235VzmakhKistiKOMP3</v>
+        <v>TDSPK235VzmakhKistiOSN3</v>
       </c>
       <c r="C518" t="str">
         <v/>
@@ -7656,7 +7656,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B519" t="str">
-        <v>TDSPK235VzmakhKistiOSN3</v>
+        <v>TDSPK235YuventaOSN3</v>
       </c>
       <c r="C519" t="str">
         <v/>
@@ -7670,7 +7670,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B520" t="str">
-        <v>TDSPK235YuventaOSN3</v>
+        <v>TDSPK235ZolotoeSiyanieOSN2</v>
       </c>
       <c r="C520" t="str">
         <v/>
@@ -7684,7 +7684,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B521" t="str">
-        <v>TDSPK235ZolotoeSiyanieOSN2</v>
+        <v>TDSPK235ZvezdnyySvetKOMP2</v>
       </c>
       <c r="C521" t="str">
         <v/>
@@ -7698,7 +7698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B522" t="str">
-        <v>TDSPK235ZvezdnyySvetKOMP2</v>
+        <v>TDSPK235ZvezdnyySvetOSN2</v>
       </c>
       <c r="C522" t="str">
         <v/>
@@ -7712,7 +7712,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B523" t="str">
-        <v>TDSPK235ZvezdnyySvetOSN2</v>
+        <v>TDPPK235AkvaOSN1</v>
       </c>
       <c r="C523" t="str">
         <v/>
@@ -7726,13 +7726,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B524" t="str">
-        <v>TDPPK235AkvaOSN1</v>
+        <v>TDPPK235AnriKOMP1-125</v>
       </c>
       <c r="C524" t="str">
         <v/>
       </c>
       <c r="D524">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -7740,13 +7740,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B525" t="str">
-        <v>TDPPK235AnriKOMP1-125</v>
+        <v>TDPPK235Ar-dekoOSN1</v>
       </c>
       <c r="C525" t="str">
         <v/>
       </c>
       <c r="D525">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="526">
@@ -7754,7 +7754,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B526" t="str">
-        <v>TDPPK235Ar-dekoOSN1</v>
+        <v>TDPPK235BarelefOSN1</v>
       </c>
       <c r="C526" t="str">
         <v/>
@@ -7768,13 +7768,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B527" t="str">
-        <v>TDPPK235BarelefOSN1</v>
+        <v>TDPPK235DlinnayaNochOSN1-125</v>
       </c>
       <c r="C527" t="str">
         <v/>
       </c>
       <c r="D527">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -7782,7 +7782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B528" t="str">
-        <v>TDPPK235DlinnayaNochOSN1-125</v>
+        <v>TDPPK235DushaOSN1</v>
       </c>
       <c r="C528" t="str">
         <v/>
@@ -7796,13 +7796,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B529" t="str">
-        <v>TDPPK235DushaOSN1</v>
+        <v>TDPPK235DzhinniKOMP1</v>
       </c>
       <c r="C529" t="str">
         <v/>
       </c>
       <c r="D529">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="530">
@@ -7810,13 +7810,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B530" t="str">
-        <v>TDPPK235DzhinniKOMP1</v>
+        <v>TDPPK235EstellaKOMP1</v>
       </c>
       <c r="C530" t="str">
         <v/>
       </c>
       <c r="D530">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -7824,13 +7824,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B531" t="str">
-        <v>TDPPK235EstellaKOMP1</v>
+        <v>TDPPK235EstellaOSN1</v>
       </c>
       <c r="C531" t="str">
         <v/>
       </c>
       <c r="D531">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="532">
@@ -7838,7 +7838,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B532" t="str">
-        <v>TDPPK235EstellaOSN1</v>
+        <v>TDPPK235FloristikaOSN1</v>
       </c>
       <c r="C532" t="str">
         <v/>
@@ -7852,13 +7852,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B533" t="str">
-        <v>TDPPK235FloristikaOSN1</v>
+        <v>TDPPK235GarmoniyaChuvstvOSN1</v>
       </c>
       <c r="C533" t="str">
         <v/>
       </c>
       <c r="D533">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -7866,13 +7866,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B534" t="str">
-        <v>TDPPK235GarmoniyaChuvstvOSN1</v>
+        <v>TDPPK235GoldenKOMP1</v>
       </c>
       <c r="C534" t="str">
         <v/>
       </c>
       <c r="D534">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
@@ -7880,7 +7880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B535" t="str">
-        <v>TDPPK235GoldenKOMP1</v>
+        <v>TDPPK235GoldenKOMP3</v>
       </c>
       <c r="C535" t="str">
         <v/>
@@ -7894,7 +7894,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B536" t="str">
-        <v>TDPPK235GoldenKOMP3</v>
+        <v>TDPPK235ImitatsiyaOSN1</v>
       </c>
       <c r="C536" t="str">
         <v/>
@@ -7908,7 +7908,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B537" t="str">
-        <v>TDPPK235ImitatsiyaOSN1</v>
+        <v>TDPPK235InessaKOMP1</v>
       </c>
       <c r="C537" t="str">
         <v/>
@@ -7922,7 +7922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B538" t="str">
-        <v>TDPPK235InessaKOMP1</v>
+        <v>TDPPK235InessaOSN1</v>
       </c>
       <c r="C538" t="str">
         <v/>
@@ -7936,7 +7936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B539" t="str">
-        <v>TDPPK235InessaOSN1</v>
+        <v>TDPPK235LegkayaProkhladaOSN1</v>
       </c>
       <c r="C539" t="str">
         <v/>
@@ -7950,7 +7950,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B540" t="str">
-        <v>TDPPK235LegkayaProkhladaOSN1</v>
+        <v>TDPPK235LepestokOSN1-125</v>
       </c>
       <c r="C540" t="str">
         <v/>
@@ -7964,13 +7964,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B541" t="str">
-        <v>TDPPK235LepestokOSN1-125</v>
+        <v>TDPPK235LuchSolntsaKOMP1-125</v>
       </c>
       <c r="C541" t="str">
         <v/>
       </c>
       <c r="D541">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -7978,13 +7978,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B542" t="str">
-        <v>TDPPK235LuchSolntsaKOMP1-125</v>
+        <v>TDPPK235LyubimyyMotivOSN1</v>
       </c>
       <c r="C542" t="str">
         <v/>
       </c>
       <c r="D542">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543">
@@ -7992,7 +7992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B543" t="str">
-        <v>TDPPK235LyubimyyMotivOSN1</v>
+        <v>TDPPK235MilagrosOSN1</v>
       </c>
       <c r="C543" t="str">
         <v/>
@@ -8006,7 +8006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B544" t="str">
-        <v>TDPPK235MilagrosOSN1</v>
+        <v>TDPPK235MyagkayaPerinaOSN1</v>
       </c>
       <c r="C544" t="str">
         <v/>
@@ -8020,7 +8020,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B545" t="str">
-        <v>TDPPK235MyagkayaPerinaOSN1</v>
+        <v>TDPPK235NapravlenieOSN1-125</v>
       </c>
       <c r="C545" t="str">
         <v/>
@@ -8034,7 +8034,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B546" t="str">
-        <v>TDPPK235NapravlenieOSN1-125</v>
+        <v>TDPPK235NimfeyaOSN1</v>
       </c>
       <c r="C546" t="str">
         <v/>
@@ -8048,7 +8048,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B547" t="str">
-        <v>TDPPK235NimfeyaOSN1</v>
+        <v>TDPPK235NinelKOMP4</v>
       </c>
       <c r="C547" t="str">
         <v/>
@@ -8062,7 +8062,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B548" t="str">
-        <v>TDPPK235NinelKOMP4</v>
+        <v>TDPPK235NinelOSN1-125</v>
       </c>
       <c r="C548" t="str">
         <v/>
@@ -8076,7 +8076,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B549" t="str">
-        <v>TDPPK235NinelOSN1-125</v>
+        <v>TDPPK235NovyyDen2</v>
       </c>
       <c r="C549" t="str">
         <v/>
@@ -8090,7 +8090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B550" t="str">
-        <v>TDPPK235NovyyDen2</v>
+        <v>TDPPK235NovyyDen6</v>
       </c>
       <c r="C550" t="str">
         <v/>
@@ -8104,7 +8104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B551" t="str">
-        <v>TDPPK235NovyyDen6</v>
+        <v>TDPPK235PalmerOSN1</v>
       </c>
       <c r="C551" t="str">
         <v/>
@@ -8118,13 +8118,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B552" t="str">
-        <v>TDPPK235PalmerOSN1</v>
+        <v>TDPPK235PassazhOSN1-125</v>
       </c>
       <c r="C552" t="str">
         <v/>
       </c>
       <c r="D552">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -8132,7 +8132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B553" t="str">
-        <v>TDPPK235PassazhOSN1-125</v>
+        <v>TDPPK235PlenitelnayaGratsiyaKOMP1</v>
       </c>
       <c r="C553" t="str">
         <v/>
@@ -8146,13 +8146,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B554" t="str">
-        <v>TDPPK235PlenitelnayaGratsiyaKOMP1</v>
+        <v>TDPPK235PlenitelnayaGratsiyaOSN1</v>
       </c>
       <c r="C554" t="str">
         <v/>
       </c>
       <c r="D554">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555">
@@ -8160,13 +8160,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B555" t="str">
-        <v>TDPPK235PlenitelnayaGratsiyaOSN1</v>
+        <v>TDPPK235PoeziyaKrasotyKOMP1</v>
       </c>
       <c r="C555" t="str">
         <v/>
       </c>
       <c r="D555">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556">
@@ -8174,13 +8174,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B556" t="str">
-        <v>TDPPK235PoeziyaKrasotyKOMP1</v>
+        <v>TDPPK235PoeziyaKrasotyOSN1</v>
       </c>
       <c r="C556" t="str">
         <v/>
       </c>
       <c r="D556">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -8188,13 +8188,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B557" t="str">
-        <v>TDPPK235PoeziyaKrasotyOSN1</v>
+        <v>TDPPK235PrimaveraOSN1</v>
       </c>
       <c r="C557" t="str">
         <v/>
       </c>
       <c r="D557">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -8202,7 +8202,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B558" t="str">
-        <v>TDPPK235PrimaveraOSN1</v>
+        <v>TDPPK235RenataOSN1-125</v>
       </c>
       <c r="C558" t="str">
         <v/>
@@ -8216,13 +8216,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B559" t="str">
-        <v>TDPPK235RenataOSN1-125</v>
+        <v>TDPPK235SelinOSN1</v>
       </c>
       <c r="C559" t="str">
         <v/>
       </c>
       <c r="D559">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="560">
@@ -8230,7 +8230,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B560" t="str">
-        <v>TDPPK235SelinOSN1</v>
+        <v>TDPPK235SiluetySvetaOSN1</v>
       </c>
       <c r="C560" t="str">
         <v/>
@@ -8244,7 +8244,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B561" t="str">
-        <v>TDPPK235SiluetySvetaOSN1</v>
+        <v>TDPPK235SintezOSN1</v>
       </c>
       <c r="C561" t="str">
         <v/>
@@ -8258,7 +8258,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B562" t="str">
-        <v>TDPPK235SintezOSN1</v>
+        <v>TDPPK235SliyanieOSN1-125</v>
       </c>
       <c r="C562" t="str">
         <v/>
@@ -8272,7 +8272,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B563" t="str">
-        <v>TDPPK235SliyanieOSN1-125</v>
+        <v>TDPPK235SozvezdiyaKOMP1-125</v>
       </c>
       <c r="C563" t="str">
         <v/>
@@ -8286,13 +8286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B564" t="str">
-        <v>TDPPK235SozvezdiyaKOMP1-125</v>
+        <v>TDPPK235Stripe4</v>
       </c>
       <c r="C564" t="str">
         <v/>
       </c>
       <c r="D564">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565">
@@ -8300,7 +8300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B565" t="str">
-        <v>TDPPK235Stripe4</v>
+        <v>TDPPK235Stripe5</v>
       </c>
       <c r="C565" t="str">
         <v/>
@@ -8314,13 +8314,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B566" t="str">
-        <v>TDPPK235Stripe5</v>
+        <v>TDPPK235TaynaPrirodyOSN1</v>
       </c>
       <c r="C566" t="str">
         <v/>
       </c>
       <c r="D566">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="567">
@@ -8328,7 +8328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B567" t="str">
-        <v>TDPPK235TaynaPrirodyOSN1</v>
+        <v>TDPPK235TsvetenieOSN1</v>
       </c>
       <c r="C567" t="str">
         <v/>
@@ -8342,7 +8342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B568" t="str">
-        <v>TDPPK235TsvetenieOSN1</v>
+        <v>TDPPK235TumannyeRassvetyKOMP3-125</v>
       </c>
       <c r="C568" t="str">
         <v/>
@@ -8356,7 +8356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B569" t="str">
-        <v>TDPPK235TumannyeRassvetyKOMP3-125</v>
+        <v>TDPPK235TumannyeRassvetyOSN3-125</v>
       </c>
       <c r="C569" t="str">
         <v/>
@@ -8370,13 +8370,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B570" t="str">
-        <v>TDPPK235TumannyeRassvetyOSN3-125</v>
+        <v>TDPPK235TurmalinOSN1</v>
       </c>
       <c r="C570" t="str">
         <v/>
       </c>
       <c r="D570">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="571">
@@ -8384,13 +8384,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B571" t="str">
-        <v>TDPPK235TurmalinOSN1</v>
+        <v>TDPPK235VanessaKOMP1</v>
       </c>
       <c r="C571" t="str">
         <v/>
       </c>
       <c r="D571">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572">
@@ -8398,7 +8398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B572" t="str">
-        <v>TDPPK235VanessaKOMP1</v>
+        <v>TDPPK235VanessaOSN1</v>
       </c>
       <c r="C572" t="str">
         <v/>
@@ -8412,13 +8412,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B573" t="str">
-        <v>TDPPK235VanessaOSN1</v>
+        <v>TDPPK235VetkaSakuryOSN1</v>
       </c>
       <c r="C573" t="str">
         <v/>
       </c>
       <c r="D573">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="574">
@@ -8426,7 +8426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B574" t="str">
-        <v>TDPPK235VetkaSakuryOSN1</v>
+        <v>TDPPK235VremyaTsveteniyaOSN1</v>
       </c>
       <c r="C574" t="str">
         <v/>
@@ -8440,13 +8440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B575" t="str">
-        <v>TDPPK235VremyaTsveteniyaOSN1</v>
+        <v>TDPPK235VyshivkaOSN1-125</v>
       </c>
       <c r="C575" t="str">
         <v/>
       </c>
       <c r="D575">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="576">
@@ -8454,7 +8454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B576" t="str">
-        <v>TDPPK235VyshivkaOSN1-125</v>
+        <v>TDPPK235VzmakhKistiOSN1</v>
       </c>
       <c r="C576" t="str">
         <v/>
@@ -8468,13 +8468,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B577" t="str">
-        <v>TDPPK235VzmakhKistiOSN1</v>
+        <v>TDPPK235YaponskiyDvorikOSN1-125</v>
       </c>
       <c r="C577" t="str">
         <v/>
       </c>
       <c r="D577">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="578">
@@ -8482,7 +8482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B578" t="str">
-        <v>TDPPK235YaponskiyDvorikOSN1-125</v>
+        <v>TDPPK235ZhordanOSN2-125</v>
       </c>
       <c r="C578" t="str">
         <v/>
@@ -8496,7 +8496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B579" t="str">
-        <v>TDPPK235ZhordanOSN2-125</v>
+        <v>TDPPK235ZolotoeSiyanieOSN1</v>
       </c>
       <c r="C579" t="str">
         <v/>
@@ -8510,13 +8510,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B580" t="str">
-        <v>TDPPK235ZolotoeSiyanieOSN1</v>
+        <v>TDPPK235ZvezdnyySvetKOMP1</v>
       </c>
       <c r="C580" t="str">
         <v/>
       </c>
       <c r="D580">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581">
@@ -8524,13 +8524,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B581" t="str">
-        <v>TDPPK235ZvezdnyySvetKOMP1</v>
+        <v>TDPPK235ZvezdnyySvetOSN1</v>
       </c>
       <c r="C581" t="str">
         <v/>
       </c>
       <c r="D581">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="582">
@@ -8538,13 +8538,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B582" t="str">
-        <v>TDPPK235ZvezdnyySvetOSN1</v>
+        <v>TDPPK235KhloyaOSN1-125</v>
       </c>
       <c r="C582" t="str">
         <v/>
       </c>
       <c r="D582">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583">
@@ -8552,7 +8552,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B583" t="str">
-        <v>TDPPK235KhloyaOSN1-125</v>
+        <v>TDM-liliac</v>
       </c>
       <c r="C583" t="str">
         <v/>
@@ -8566,7 +8566,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B584" t="str">
-        <v>TDM-liliac</v>
+        <v>TDM-karamel</v>
       </c>
       <c r="C584" t="str">
         <v/>
@@ -8580,7 +8580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B585" t="str">
-        <v>TDM-karamel</v>
+        <v>TDM-mint</v>
       </c>
       <c r="C585" t="str">
         <v/>
@@ -8594,13 +8594,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B586" t="str">
-        <v>TDM-mint</v>
+        <v>TR-Elochka1-195x165</v>
       </c>
       <c r="C586" t="str">
         <v/>
       </c>
       <c r="D586">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="587">
@@ -8608,7 +8608,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B587" t="str">
-        <v>TR-Elochka1-195x165</v>
+        <v>TR-Lavanda1-195x165</v>
       </c>
       <c r="C587" t="str">
         <v/>
@@ -8622,7 +8622,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B588" t="str">
-        <v>TR-Lavanda1-195x165</v>
+        <v>TR-LetneeNastroenie1-195x165</v>
       </c>
       <c r="C588" t="str">
         <v/>
@@ -8636,7 +8636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B589" t="str">
-        <v>TR-LetneeNastroenie1-195x165</v>
+        <v>TR-LetnyaaNoch1-195x165</v>
       </c>
       <c r="C589" t="str">
         <v/>
@@ -8650,7 +8650,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B590" t="str">
-        <v>TR-LetnyaaNoch1-195x165</v>
+        <v>TR-LimonnayaKorzinka1-195x165</v>
       </c>
       <c r="C590" t="str">
         <v/>
@@ -8664,7 +8664,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B591" t="str">
-        <v>TR-LimonnayaKorzinka1-195x165</v>
+        <v>TR-NejniyDen1-195x165</v>
       </c>
       <c r="C591" t="str">
         <v/>
@@ -8678,13 +8678,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B592" t="str">
-        <v>TR-NejniyDen1-195x165</v>
+        <v>TR-Pascha-195x165</v>
       </c>
       <c r="C592" t="str">
         <v/>
       </c>
       <c r="D592">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="593">
@@ -8692,7 +8692,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B593" t="str">
-        <v>TR-Pascha-195x165</v>
+        <v>TR-Poloska1-195x165</v>
       </c>
       <c r="C593" t="str">
         <v/>
@@ -8706,13 +8706,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B594" t="str">
-        <v>TR-Poloska1-195x165</v>
+        <v>TR-Rojdestvo1-195x165</v>
       </c>
       <c r="C594" t="str">
         <v/>
       </c>
       <c r="D594">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="595">
@@ -8720,7 +8720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B595" t="str">
-        <v>TR-Rojdestvo1-195x165</v>
+        <v>TR-SpelieFrukti1-195x165</v>
       </c>
       <c r="C595" t="str">
         <v/>
@@ -8734,13 +8734,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B596" t="str">
-        <v>TR-SpelieFrukti1-195x165</v>
+        <v>TR-TihiyVecher1-195x165</v>
       </c>
       <c r="C596" t="str">
         <v/>
       </c>
       <c r="D596">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
@@ -8748,13 +8748,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B597" t="str">
-        <v>TR-TihiyVecher1-195x165</v>
+        <v>TR-Hutoryanka1-195x165</v>
       </c>
       <c r="C597" t="str">
         <v/>
       </c>
       <c r="D597">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="598">
@@ -8762,7 +8762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B598" t="str">
-        <v>TR-Hutoryanka1-195x165</v>
+        <v>TDSPK250DarkViolet-8</v>
       </c>
       <c r="C598" t="str">
         <v/>
@@ -8776,7 +8776,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B599" t="str">
-        <v>TDSPK250DarkViolet-8</v>
+        <v>TDSPK250Sliva-8</v>
       </c>
       <c r="C599" t="str">
         <v/>
@@ -8790,7 +8790,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B600" t="str">
-        <v>TDSPK250Sliva-8</v>
+        <v>TDSPK250Persikoviy-8</v>
       </c>
       <c r="C600" t="str">
         <v/>
@@ -8804,13 +8804,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B601" t="str">
-        <v>TDSPK250Persikoviy-8</v>
+        <v>TDSPK250Lavanda-8</v>
       </c>
       <c r="C601" t="str">
         <v/>
       </c>
       <c r="D601">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="602">
@@ -8818,13 +8818,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B602" t="str">
-        <v>TDSPK250Lavanda-8</v>
+        <v>TDSPK250Bordo-8</v>
       </c>
       <c r="C602" t="str">
         <v/>
       </c>
       <c r="D602">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="603">
@@ -8832,7 +8832,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B603" t="str">
-        <v>TDSPK250Bordo-8</v>
+        <v>TDSPK250LightLiliac-8</v>
       </c>
       <c r="C603" t="str">
         <v/>
@@ -8846,13 +8846,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B604" t="str">
-        <v>TDSPK250LightLiliac-8</v>
+        <v>TDSPK250Liliac-8</v>
       </c>
       <c r="C604" t="str">
         <v/>
       </c>
       <c r="D604">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="605">
@@ -8860,7 +8860,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B605" t="str">
-        <v>TDSPK250Liliac-8</v>
+        <v>TDSPK250Blue-8</v>
       </c>
       <c r="C605" t="str">
         <v/>
@@ -8874,7 +8874,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B606" t="str">
-        <v>TDSPK250Blue-8</v>
+        <v>TDSPK250Choco-8</v>
       </c>
       <c r="C606" t="str">
         <v/>
@@ -8888,7 +8888,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B607" t="str">
-        <v>TDSPK250Choco-8</v>
+        <v>TDSPK250Menthol-8</v>
       </c>
       <c r="C607" t="str">
         <v/>
@@ -8902,7 +8902,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B608" t="str">
-        <v>TDSPK250Menthol-8</v>
+        <v>TDSPK250LightBlue-8</v>
       </c>
       <c r="C608" t="str">
         <v/>
@@ -8916,13 +8916,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B609" t="str">
-        <v>TDSPK250LightBlue-8</v>
+        <v>TDSPK250PepelRose-8</v>
       </c>
       <c r="C609" t="str">
         <v/>
       </c>
       <c r="D609">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="610">
@@ -8930,13 +8930,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B610" t="str">
-        <v>TDSPK250PepelRose-8</v>
+        <v>TDSPK250Bejeviy-8</v>
       </c>
       <c r="C610" t="str">
         <v/>
       </c>
       <c r="D610">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -8944,7 +8944,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B611" t="str">
-        <v>TDSPK250Bejeviy-8</v>
+        <v>TDSPK250Gold-8</v>
       </c>
       <c r="C611" t="str">
         <v/>
@@ -8958,7 +8958,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B612" t="str">
-        <v>TDSPK250Gold-8</v>
+        <v>TDSPK250Pink-8</v>
       </c>
       <c r="C612" t="str">
         <v/>
@@ -8972,32 +8972,18 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B613" t="str">
-        <v>TDSPK250Pink-8</v>
+        <v>TDSPK250Grafit-8</v>
       </c>
       <c r="C613" t="str">
         <v/>
       </c>
       <c r="D613">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="str">
-        <v>СЦ (Коляново) (1020002072018000)</v>
-      </c>
-      <c r="B614" t="str">
-        <v>TDSPK250Grafit-8</v>
-      </c>
-      <c r="C614" t="str">
-        <v/>
-      </c>
-      <c r="D614">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D614"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D613"/>
   </ignoredErrors>
 </worksheet>
 </file>